--- a/uzbekistan_pop_grp.xlsx
+++ b/uzbekistan_pop_grp.xlsx
@@ -8,25 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/timursabitov/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA35ED21-4636-F84B-858D-57EF7B153359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FFF9E878-791A-024A-A85C-7C841359B262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11300" yWindow="1440" windowWidth="18100" windowHeight="15360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16480" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Population Data" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
     <sheet name="Sources" sheetId="2" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$B$23</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$B$24</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Sheet1!$C$23:$J$23</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Sheet1!$C$24:$J$24</definedName>
-    <definedName name="_xlchart.v2.0" hidden="1">Sheet1!$B$23</definedName>
-    <definedName name="_xlchart.v2.1" hidden="1">Sheet1!$B$24</definedName>
-    <definedName name="_xlchart.v2.2" hidden="1">Sheet1!$C$23:$J$23</definedName>
-    <definedName name="_xlchart.v2.3" hidden="1">Sheet1!$C$24:$J$24</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -44,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="85">
   <si>
     <t>Uzbekistan Population by Region (2024–2025)</t>
   </si>
@@ -259,16 +249,10 @@
     <t>18.7% 32%</t>
   </si>
   <si>
-    <t>Population</t>
-  </si>
-  <si>
     <t>Total+unallocated</t>
   </si>
   <si>
     <t>GDP/Year</t>
-  </si>
-  <si>
-    <t>GRP (Jan-Sep)</t>
   </si>
   <si>
     <t>Jan-Dec</t>
@@ -288,6 +272,24 @@
   <si>
     <t>GDP per Capita*</t>
   </si>
+  <si>
+    <t xml:space="preserve">City population </t>
+  </si>
+  <si>
+    <t>Regions population</t>
+  </si>
+  <si>
+    <t>GDP Volume (bil sum)</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>Services</t>
+  </si>
+  <si>
+    <t>https://stat.uz/en/quarterly-reports/5870-2018#january-september</t>
+  </si>
 </sst>
 </file>
 
@@ -295,7 +297,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -427,7 +429,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -449,15 +451,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3838,7 +3838,7 @@
         <v>5.8</v>
       </c>
       <c r="F4" s="7">
-        <f t="shared" ref="F3:F16" si="0">(((E4*100)/$E$18))*$A$19/100</f>
+        <f t="shared" ref="F4:F16" si="0">(((E4*100)/$E$18))*$A$19/100</f>
         <v>3102.5327014218014</v>
       </c>
       <c r="G4" s="7" t="s">
@@ -5745,35 +5745,35 @@
     <col min="13" max="13" width="20.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C1" s="18" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G1" s="18" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H1" s="18" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I1" s="18" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J1" s="18" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A2" s="18" t="s">
-        <v>74</v>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B2" s="18" t="s">
+        <v>81</v>
       </c>
       <c r="C2" s="18">
         <v>2017</v>
@@ -5799,34 +5799,9 @@
       <c r="J2" s="18">
         <v>2024</v>
       </c>
-      <c r="N2" s="18">
-        <v>2017</v>
-      </c>
-      <c r="O2" s="18">
-        <v>2018</v>
-      </c>
-      <c r="P2" s="18">
-        <v>2019</v>
-      </c>
-      <c r="Q2" s="18">
-        <v>2020</v>
-      </c>
-      <c r="R2" s="18">
-        <v>2021</v>
-      </c>
-      <c r="S2" s="18">
-        <v>2022</v>
-      </c>
-      <c r="T2" s="18">
-        <v>2023</v>
-      </c>
-      <c r="U2" s="18">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A3" s="24"/>
-      <c r="B3" s="25" t="s">
+    </row>
+    <row r="3" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="20">
@@ -5853,13 +5828,36 @@
       <c r="J3" s="14">
         <v>45658.5</v>
       </c>
-      <c r="M3" s="7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A4" s="24"/>
-      <c r="B4" s="25" t="s">
+      <c r="M3" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="N3" s="18">
+        <v>2017</v>
+      </c>
+      <c r="O3" s="18">
+        <v>2018</v>
+      </c>
+      <c r="P3" s="18">
+        <v>2019</v>
+      </c>
+      <c r="Q3" s="18">
+        <v>2020</v>
+      </c>
+      <c r="R3" s="18">
+        <v>2021</v>
+      </c>
+      <c r="S3" s="18">
+        <v>2022</v>
+      </c>
+      <c r="T3" s="18">
+        <v>2023</v>
+      </c>
+      <c r="U3" s="18">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="4" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B4" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="20">
@@ -5887,12 +5885,35 @@
         <v>90522.1</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A5" s="24"/>
-      <c r="B5" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="N4">
+        <v>15.2</v>
+      </c>
+      <c r="O4">
+        <v>27.8</v>
+      </c>
+      <c r="P4">
+        <v>28.1</v>
+      </c>
+      <c r="Q4">
+        <v>29.6</v>
+      </c>
+      <c r="R4">
+        <v>29.4</v>
+      </c>
+      <c r="S4">
+        <v>24.9</v>
+      </c>
+      <c r="T4">
+        <v>25.2</v>
+      </c>
+      <c r="U4">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B5" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="20">
@@ -5920,12 +5941,35 @@
         <v>71560.399999999994</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A6" s="24"/>
-      <c r="B6" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="N5">
+        <v>33.4</v>
+      </c>
+      <c r="O5">
+        <v>44.7</v>
+      </c>
+      <c r="P5">
+        <v>43.2</v>
+      </c>
+      <c r="Q5">
+        <v>42.7</v>
+      </c>
+      <c r="R5">
+        <v>43.3</v>
+      </c>
+      <c r="S5">
+        <v>35.700000000000003</v>
+      </c>
+      <c r="T5">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="U5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B6" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="20">
@@ -5953,12 +5997,35 @@
         <v>43057.9</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A7" s="24"/>
-      <c r="B7" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="N6">
+        <v>31</v>
+      </c>
+      <c r="O6">
+        <v>48.7</v>
+      </c>
+      <c r="P6">
+        <v>43.2</v>
+      </c>
+      <c r="Q6">
+        <v>46.2</v>
+      </c>
+      <c r="R6">
+        <v>45.5</v>
+      </c>
+      <c r="S6">
+        <v>39.1</v>
+      </c>
+      <c r="T6">
+        <v>37.4</v>
+      </c>
+      <c r="U6">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B7" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="20">
@@ -5986,12 +6053,35 @@
         <v>80658.3</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A8" s="24"/>
-      <c r="B8" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="N7">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="O7">
+        <v>55.7</v>
+      </c>
+      <c r="P7">
+        <v>53.2</v>
+      </c>
+      <c r="Q7">
+        <v>53.8</v>
+      </c>
+      <c r="R7">
+        <v>53.5</v>
+      </c>
+      <c r="S7">
+        <v>47</v>
+      </c>
+      <c r="T7">
+        <v>43.3</v>
+      </c>
+      <c r="U7">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="20">
@@ -6019,12 +6109,35 @@
         <v>117297.8</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A9" s="24"/>
-      <c r="B9" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="N8">
+        <v>22.6</v>
+      </c>
+      <c r="O8">
+        <v>42.7</v>
+      </c>
+      <c r="P8">
+        <v>41.1</v>
+      </c>
+      <c r="Q8">
+        <v>42.4</v>
+      </c>
+      <c r="R8">
+        <v>42.1</v>
+      </c>
+      <c r="S8">
+        <v>35.5</v>
+      </c>
+      <c r="T8">
+        <v>34.6</v>
+      </c>
+      <c r="U8">
+        <v>32.700000000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B9" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="20">
@@ -6052,12 +6165,35 @@
         <v>68915.7</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A10" s="24"/>
-      <c r="B10" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="N9">
+        <v>18.5</v>
+      </c>
+      <c r="O9">
+        <v>23.1</v>
+      </c>
+      <c r="P9">
+        <v>16.3</v>
+      </c>
+      <c r="Q9">
+        <v>14</v>
+      </c>
+      <c r="R9">
+        <v>14.9</v>
+      </c>
+      <c r="S9">
+        <v>13.2</v>
+      </c>
+      <c r="T9">
+        <v>13</v>
+      </c>
+      <c r="U9">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B10" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="20">
@@ -6085,12 +6221,35 @@
         <v>99866.1</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A11" s="24"/>
-      <c r="B11" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="N10">
+        <v>30.9</v>
+      </c>
+      <c r="O10">
+        <v>45.5</v>
+      </c>
+      <c r="P10">
+        <v>43.2</v>
+      </c>
+      <c r="Q10">
+        <v>42.4</v>
+      </c>
+      <c r="R10">
+        <v>41.4</v>
+      </c>
+      <c r="S10">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="T10">
+        <v>32.5</v>
+      </c>
+      <c r="U10">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="11" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B11" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="20">
@@ -6118,12 +6277,35 @@
         <v>54354.1</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A12" s="24"/>
-      <c r="B12" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="N11">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="O11">
+        <v>47.6</v>
+      </c>
+      <c r="P11">
+        <v>44.8</v>
+      </c>
+      <c r="Q11">
+        <v>45.7</v>
+      </c>
+      <c r="R11">
+        <v>43.8</v>
+      </c>
+      <c r="S11">
+        <v>35.1</v>
+      </c>
+      <c r="T11">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="U11">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="12" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B12" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="20">
@@ -6151,12 +6333,35 @@
         <v>28003.3</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A13" s="24"/>
-      <c r="B13" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="N12">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="O12">
+        <v>50.8</v>
+      </c>
+      <c r="P12">
+        <v>49.9</v>
+      </c>
+      <c r="Q12">
+        <v>48.5</v>
+      </c>
+      <c r="R12">
+        <v>47.6</v>
+      </c>
+      <c r="S12">
+        <v>41.6</v>
+      </c>
+      <c r="T12">
+        <v>41.6</v>
+      </c>
+      <c r="U12">
+        <v>39.1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B13" s="7" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="20">
@@ -6184,12 +6389,35 @@
         <v>146385.20000000001</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A14" s="24"/>
-      <c r="B14" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="N13">
+        <v>36.9</v>
+      </c>
+      <c r="O13">
+        <v>43.4</v>
+      </c>
+      <c r="P13">
+        <v>41.1</v>
+      </c>
+      <c r="Q13">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="R13">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="S13">
+        <v>36.4</v>
+      </c>
+      <c r="T13">
+        <v>34.4</v>
+      </c>
+      <c r="U13">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="14" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B14" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="20">
@@ -6217,12 +6445,35 @@
         <v>91333</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A15" s="24"/>
-      <c r="B15" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="N14">
+        <v>23.1</v>
+      </c>
+      <c r="O14">
+        <v>29.2</v>
+      </c>
+      <c r="P14">
+        <v>24.3</v>
+      </c>
+      <c r="Q14">
+        <v>23.5</v>
+      </c>
+      <c r="R14">
+        <v>22.5</v>
+      </c>
+      <c r="S14">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="T14">
+        <v>19.8</v>
+      </c>
+      <c r="U14">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="15" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B15" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C15" s="20">
@@ -6250,12 +6501,35 @@
         <v>51261</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A16" s="24"/>
-      <c r="B16" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="N15">
+        <v>23.4</v>
+      </c>
+      <c r="O15">
+        <v>39.1</v>
+      </c>
+      <c r="P15">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="Q15">
+        <v>34.9</v>
+      </c>
+      <c r="R15">
+        <v>35</v>
+      </c>
+      <c r="S15">
+        <v>30.5</v>
+      </c>
+      <c r="T15">
+        <v>29.7</v>
+      </c>
+      <c r="U15">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B16" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="20">
@@ -6283,77 +6557,103 @@
         <v>281147.40000000002</v>
       </c>
       <c r="M16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="N16">
+        <v>30.4</v>
+      </c>
+      <c r="O16">
+        <v>48.4</v>
+      </c>
+      <c r="P16">
+        <v>46</v>
+      </c>
+      <c r="Q16">
+        <v>47.3</v>
+      </c>
+      <c r="R16">
+        <v>46.1</v>
+      </c>
+      <c r="S16">
+        <v>39.4</v>
+      </c>
+      <c r="T16">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="U16">
+        <v>34.799999999999997</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="B17" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17">
+        <f t="shared" ref="C17:J17" si="0">SUM(C3:C16)</f>
+        <v>252035.10000000003</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="0"/>
+        <v>351725.10000000003</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="0"/>
+        <v>453417.69999999995</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>521080.79999999993</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="0"/>
+        <v>648912.10000000009</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="0"/>
+        <v>865769.2</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="0"/>
+        <v>1042535.5</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="0"/>
+        <v>1270020.8000000003</v>
+      </c>
+      <c r="M17" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="N16" s="20">
-        <v>40720.400000000001</v>
-      </c>
-      <c r="O16" s="20">
-        <v>63509.2</v>
-      </c>
-      <c r="P16" s="19">
-        <v>84720.4</v>
-      </c>
-      <c r="Q16" s="19">
-        <v>95247.8</v>
-      </c>
-      <c r="R16" s="19">
-        <v>121779.8</v>
-      </c>
-      <c r="S16" s="19">
-        <v>172469.3</v>
-      </c>
-      <c r="T16" s="19">
-        <v>215099.2</v>
-      </c>
-      <c r="U16" s="23">
-        <v>281147.40000000002</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A17" s="24"/>
-      <c r="B17" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="24">
-        <f>SUM(C3:C16)</f>
-        <v>252035.10000000003</v>
-      </c>
-      <c r="D17" s="24">
-        <f>SUM(D3:D16)</f>
-        <v>351725.10000000003</v>
-      </c>
-      <c r="E17" s="24">
-        <f>SUM(E3:E16)</f>
-        <v>453417.69999999995</v>
-      </c>
-      <c r="F17" s="24">
-        <f>SUM(F3:F16)</f>
-        <v>521080.79999999993</v>
-      </c>
-      <c r="G17" s="24">
-        <f>SUM(G3:G16)</f>
-        <v>648912.10000000009</v>
-      </c>
-      <c r="H17" s="24">
-        <f>SUM(H3:H16)</f>
-        <v>865769.2</v>
-      </c>
-      <c r="I17" s="24">
-        <f>SUM(I3:I16)</f>
-        <v>1042535.5</v>
-      </c>
-      <c r="J17" s="24">
-        <f>SUM(J3:J16)</f>
-        <v>1270020.8000000003</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A18" s="18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C18" s="21">
         <v>356453.84090000001</v>
@@ -6380,9 +6680,9 @@
         <v>1454573.8673999999</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A19" s="18" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C19" s="19">
         <v>5113</v>
@@ -6409,9 +6709,9 @@
         <v>12652</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A20" s="10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C20" s="18">
         <f>C18/C19</f>
@@ -6422,33 +6722,33 @@
         <v>58.627651120188141</v>
       </c>
       <c r="E20" s="18">
-        <f t="shared" ref="E20:J20" si="0">E18/E19</f>
+        <f t="shared" ref="E20:J20" si="1">E18/E19</f>
         <v>67.414079469447913</v>
       </c>
       <c r="F20" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>66.617267092142001</v>
       </c>
       <c r="G20" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>77.31429497785733</v>
       </c>
       <c r="H20" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>90.08080804379297</v>
       </c>
       <c r="I20" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>102.57049773482072</v>
       </c>
       <c r="J20" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>114.96789973126778</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B23" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C23" s="18">
         <v>2017</v>
@@ -6474,8 +6774,35 @@
       <c r="J23" s="18">
         <v>2024</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M23" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="N23" s="18">
+        <v>2017</v>
+      </c>
+      <c r="O23" s="18">
+        <v>2018</v>
+      </c>
+      <c r="P23" s="18">
+        <v>2019</v>
+      </c>
+      <c r="Q23" s="18">
+        <v>2020</v>
+      </c>
+      <c r="R23" s="18">
+        <v>2021</v>
+      </c>
+      <c r="S23" s="18">
+        <v>2022</v>
+      </c>
+      <c r="T23" s="18">
+        <v>2023</v>
+      </c>
+      <c r="U23" s="18">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B24" s="7" t="s">
         <v>3</v>
       </c>
@@ -6484,523 +6811,901 @@
         <v>1558.9034981724869</v>
       </c>
       <c r="D24" s="14">
-        <f t="shared" ref="D24:J24" si="1">(D$18/D$17)*(D3/D$19)/D44*1000000</f>
+        <f t="shared" ref="D24:J24" si="2">(D$18/D$17)*(D3/D$19)/D44*1000000</f>
         <v>1413.4878969382414</v>
       </c>
       <c r="E24" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1555.1032154998952</v>
       </c>
       <c r="F24" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1458.8594060936991</v>
       </c>
       <c r="G24" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1590.6038970010447</v>
       </c>
       <c r="H24" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1897.8710727214789</v>
       </c>
       <c r="I24" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1949.8991636011572</v>
       </c>
       <c r="J24" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2063.8185218166236</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M24" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="O24">
+        <v>30</v>
+      </c>
+      <c r="P24">
+        <v>28.1</v>
+      </c>
+      <c r="Q24">
+        <v>26.4</v>
+      </c>
+      <c r="R24">
+        <v>25.6</v>
+      </c>
+      <c r="S24">
+        <v>21.5</v>
+      </c>
+      <c r="T24">
+        <v>20</v>
+      </c>
+      <c r="U24">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B25" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C25" s="14">
-        <f t="shared" ref="C25:J25" si="2">(C$18/C$17)*(C4/C$19)/C45*1000000</f>
+        <f t="shared" ref="C25:J25" si="3">(C$18/C$17)*(C4/C$19)/C45*1000000</f>
         <v>1793.2673606015076</v>
       </c>
       <c r="D25" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1495.3257053552124</v>
       </c>
       <c r="E25" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1627.9836093962751</v>
       </c>
       <c r="F25" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1553.5934495743256</v>
       </c>
       <c r="G25" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1619.4059774803452</v>
       </c>
       <c r="H25" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2014.1492122298459</v>
       </c>
       <c r="I25" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2289.986143424504</v>
       </c>
       <c r="J25" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2414.1117262796542</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M25" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="N25">
+        <v>20.8</v>
+      </c>
+      <c r="O25">
+        <v>22.4</v>
+      </c>
+      <c r="P25">
+        <v>23.6</v>
+      </c>
+      <c r="Q25">
+        <v>22.9</v>
+      </c>
+      <c r="R25">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="S25">
+        <v>23.9</v>
+      </c>
+      <c r="T25">
+        <v>27.8</v>
+      </c>
+      <c r="U25">
+        <v>28.8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B26" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C26" s="14">
-        <f t="shared" ref="C26:J26" si="3">(C$18/C$17)*(C5/C$19)/C46*1000000</f>
+        <f t="shared" ref="C26:J26" si="4">(C$18/C$17)*(C5/C$19)/C46*1000000</f>
         <v>2476.3980064145239</v>
       </c>
       <c r="D26" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1944.5274327511358</v>
       </c>
       <c r="E26" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2194.197075531486</v>
       </c>
       <c r="F26" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2082.1780191302905</v>
       </c>
       <c r="G26" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2346.6708118097863</v>
       </c>
       <c r="H26" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2722.6580287452334</v>
       </c>
       <c r="I26" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2998.1544249936396</v>
       </c>
       <c r="J26" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3169.2582670540764</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M26" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="N26">
+        <v>19.7</v>
+      </c>
+      <c r="O26">
+        <v>12.9</v>
+      </c>
+      <c r="P26">
+        <v>19</v>
+      </c>
+      <c r="Q26">
+        <v>16.8</v>
+      </c>
+      <c r="R26">
+        <v>16.5</v>
+      </c>
+      <c r="S26">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="T26">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="U26">
+        <v>19.899999999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B27" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C27" s="14">
-        <f t="shared" ref="C27:J27" si="4">(C$18/C$17)*(C6/C$19)/C47*1000000</f>
+        <f t="shared" ref="C27:J27" si="5">(C$18/C$17)*(C6/C$19)/C47*1000000</f>
         <v>1945.0021475861897</v>
       </c>
       <c r="D27" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1599.6321067356387</v>
       </c>
       <c r="E27" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1765.1720465693713</v>
       </c>
       <c r="F27" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1705.859376054588</v>
       </c>
       <c r="G27" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1965.9726197128794</v>
       </c>
       <c r="H27" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2188.9978254300713</v>
       </c>
       <c r="I27" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2492.6934416506879</v>
       </c>
       <c r="J27" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2585.7712219585069</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M27" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="N27">
+        <v>14.3</v>
+      </c>
+      <c r="O27">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="P27">
+        <v>10.1</v>
+      </c>
+      <c r="Q27">
+        <v>11.1</v>
+      </c>
+      <c r="R27">
+        <v>12.2</v>
+      </c>
+      <c r="S27">
+        <v>13.4</v>
+      </c>
+      <c r="T27">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="U27">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B28" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="14">
-        <f t="shared" ref="C28:J28" si="5">(C$18/C$17)*(C7/C$19)/C48*1000000</f>
+        <f t="shared" ref="C28:J28" si="6">(C$18/C$17)*(C7/C$19)/C48*1000000</f>
         <v>2026.8727717737411</v>
       </c>
       <c r="D28" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1399.7568822911689</v>
       </c>
       <c r="E28" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1491.0557031778328</v>
       </c>
       <c r="F28" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1377.7257763165551</v>
       </c>
       <c r="G28" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1520.3012875800346</v>
       </c>
       <c r="H28" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1759.2767542378567</v>
       </c>
       <c r="I28" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1939.532729116341</v>
       </c>
       <c r="J28" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2050.6504642756436</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M28" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="N28">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="O28">
+        <v>17.7</v>
+      </c>
+      <c r="P28">
+        <v>17.8</v>
+      </c>
+      <c r="Q28">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="R28">
+        <v>17</v>
+      </c>
+      <c r="S28">
+        <v>16.5</v>
+      </c>
+      <c r="T28">
+        <v>16.8</v>
+      </c>
+      <c r="U28">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B29" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C29" s="14">
-        <f t="shared" ref="C29:J29" si="6">(C$18/C$17)*(C8/C$19)/C49*1000000</f>
+        <f t="shared" ref="C29:J29" si="7">(C$18/C$17)*(C8/C$19)/C49*1000000</f>
         <v>4175.6005168445727</v>
       </c>
       <c r="D29" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3927.612896136347</v>
       </c>
       <c r="E29" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5498.5439485723437</v>
       </c>
       <c r="F29" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6382.6555355449027</v>
       </c>
       <c r="G29" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6903.5034304091896</v>
       </c>
       <c r="H29" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7245.1688838834689</v>
       </c>
       <c r="I29" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>8222.7631460062767</v>
       </c>
       <c r="J29" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>9874.747166791929</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="N29">
+        <v>53.9</v>
+      </c>
+      <c r="O29">
+        <v>54.6</v>
+      </c>
+      <c r="P29">
+        <v>65.2</v>
+      </c>
+      <c r="Q29">
+        <v>70.900000000000006</v>
+      </c>
+      <c r="R29">
+        <v>69</v>
+      </c>
+      <c r="S29">
+        <v>67.8</v>
+      </c>
+      <c r="T29">
+        <v>68.400000000000006</v>
+      </c>
+      <c r="U29">
+        <v>72.099999999999994</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B30" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C30" s="14">
-        <f t="shared" ref="C30:J30" si="7">(C$18/C$17)*(C9/C$19)/C50*1000000</f>
+        <f t="shared" ref="C30:J30" si="8">(C$18/C$17)*(C9/C$19)/C50*1000000</f>
         <v>1512.2771896089218</v>
       </c>
       <c r="D30" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1161.3931858463741</v>
       </c>
       <c r="E30" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1283.4567753923004</v>
       </c>
       <c r="F30" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1267.3006892411047</v>
       </c>
       <c r="G30" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1707.6281374904838</v>
       </c>
       <c r="H30" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1722.1219587410842</v>
       </c>
       <c r="I30" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1909.4096179788285</v>
       </c>
       <c r="J30" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2034.6870477661403</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M30" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="N30">
+        <v>14.9</v>
+      </c>
+      <c r="O30">
+        <v>12.6</v>
+      </c>
+      <c r="P30">
+        <v>12.7</v>
+      </c>
+      <c r="Q30">
+        <v>13.7</v>
+      </c>
+      <c r="R30">
+        <v>14.6</v>
+      </c>
+      <c r="S30">
+        <v>13.9</v>
+      </c>
+      <c r="T30">
+        <v>15.1</v>
+      </c>
+      <c r="U30">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B31" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C31" s="14">
-        <f t="shared" ref="C31:J31" si="8">(C$18/C$17)*(C10/C$19)/C51*1000000</f>
+        <f t="shared" ref="C31:J31" si="9">(C$18/C$17)*(C10/C$19)/C51*1000000</f>
         <v>1936.862175533475</v>
       </c>
       <c r="D31" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1464.3643849782807</v>
       </c>
       <c r="E31" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1517.2045923677015</v>
       </c>
       <c r="F31" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1418.5473749752528</v>
       </c>
       <c r="G31" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1596.3676288292686</v>
       </c>
       <c r="H31" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1780.5835421953993</v>
       </c>
       <c r="I31" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1986.4782688406128</v>
       </c>
       <c r="J31" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2148.1100271712821</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M31" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="N31">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="O31">
+        <v>14.7</v>
+      </c>
+      <c r="P31">
+        <v>13.8</v>
+      </c>
+      <c r="Q31">
+        <v>14.7</v>
+      </c>
+      <c r="R31">
+        <v>14.2</v>
+      </c>
+      <c r="S31">
+        <v>15.9</v>
+      </c>
+      <c r="T31">
+        <v>15.6</v>
+      </c>
+      <c r="U31">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B32" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="14">
-        <f t="shared" ref="C32:J32" si="9">(C$18/C$17)*(C11/C$19)/C52*1000000</f>
+        <f t="shared" ref="C32:J32" si="10">(C$18/C$17)*(C11/C$19)/C52*1000000</f>
         <v>1539.2735813187867</v>
       </c>
       <c r="D32" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1232.642396480361</v>
       </c>
       <c r="E32" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1289.4632296366331</v>
       </c>
       <c r="F32" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1197.4612173503103</v>
       </c>
       <c r="G32" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1319.6735621178859</v>
       </c>
       <c r="H32" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1486.8894438270841</v>
       </c>
       <c r="I32" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1647.6199037884928</v>
       </c>
       <c r="J32" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1710.1850904150283</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M32" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="N32">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="O32">
+        <v>6.6</v>
+      </c>
+      <c r="P32">
+        <v>6.5</v>
+      </c>
+      <c r="Q32">
+        <v>7</v>
+      </c>
+      <c r="R32">
+        <v>7.3</v>
+      </c>
+      <c r="S32">
+        <v>7.3</v>
+      </c>
+      <c r="T32">
+        <v>8.1</v>
+      </c>
+      <c r="U32">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B33" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="14">
-        <f t="shared" ref="C33:J33" si="10">(C$18/C$17)*(C12/C$19)/C53*1000000</f>
+        <f t="shared" ref="C33:J33" si="11">(C$18/C$17)*(C12/C$19)/C53*1000000</f>
         <v>2215.421633294588</v>
       </c>
       <c r="D33" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1743.2058572423773</v>
       </c>
       <c r="E33" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2125.6973814510502</v>
       </c>
       <c r="F33" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1934.1772991275543</v>
       </c>
       <c r="G33" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2085.8241797004421</v>
       </c>
       <c r="H33" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2386.9024686956704</v>
       </c>
       <c r="I33" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2633.7520053098474</v>
       </c>
       <c r="J33" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2773.5039016068818</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M33" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="N33">
+        <v>24.7</v>
+      </c>
+      <c r="O33">
+        <v>21.3</v>
+      </c>
+      <c r="P33">
+        <v>24.1</v>
+      </c>
+      <c r="Q33">
+        <v>23.6</v>
+      </c>
+      <c r="R33">
+        <v>23.8</v>
+      </c>
+      <c r="S33">
+        <v>23.2</v>
+      </c>
+      <c r="T33">
+        <v>26.1</v>
+      </c>
+      <c r="U33">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B34" s="7" t="s">
         <v>13</v>
       </c>
       <c r="C34" s="14">
-        <f t="shared" ref="C34:J34" si="11">(C$18/C$17)*(C13/C$19)/C54*1000000</f>
+        <f t="shared" ref="C34:J34" si="12">(C$18/C$17)*(C13/C$19)/C54*1000000</f>
         <v>2722.5461548310445</v>
       </c>
       <c r="D34" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2329.7066254182428</v>
       </c>
       <c r="E34" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2808.9028720369943</v>
       </c>
       <c r="F34" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2798.9230017084446</v>
       </c>
       <c r="G34" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3291.8692289089049</v>
       </c>
       <c r="H34" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3651.9891302911674</v>
       </c>
       <c r="I34" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3991.5163533815598</v>
       </c>
       <c r="J34" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4342.1704309470588</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M34" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="N34">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="O34">
+        <v>40.6</v>
+      </c>
+      <c r="P34">
+        <v>45.9</v>
+      </c>
+      <c r="Q34">
+        <v>47.6</v>
+      </c>
+      <c r="R34">
+        <v>49.2</v>
+      </c>
+      <c r="S34">
+        <v>45.5</v>
+      </c>
+      <c r="T34">
+        <v>44.3</v>
+      </c>
+      <c r="U34">
+        <v>44.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B35" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C35" s="14">
-        <f t="shared" ref="C35:J35" si="12">(C$18/C$17)*(C14/C$19)/C55*1000000</f>
+        <f t="shared" ref="C35:J35" si="13">(C$18/C$17)*(C14/C$19)/C55*1000000</f>
         <v>1539.282206123567</v>
       </c>
       <c r="D35" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1267.2915533958596</v>
       </c>
       <c r="E35" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1312.7325880967542</v>
       </c>
       <c r="F35" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1268.0925124512239</v>
       </c>
       <c r="G35" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1489.6334963359204</v>
       </c>
       <c r="H35" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1749.5241715918828</v>
       </c>
       <c r="I35" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1930.1771863011968</v>
       </c>
       <c r="J35" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2035.668373272789</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M35" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="N35">
+        <v>24.6</v>
+      </c>
+      <c r="O35">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="P35">
+        <v>20.6</v>
+      </c>
+      <c r="Q35">
+        <v>20.8</v>
+      </c>
+      <c r="R35">
+        <v>20.7</v>
+      </c>
+      <c r="S35">
+        <v>18.8</v>
+      </c>
+      <c r="T35">
+        <v>19.3</v>
+      </c>
+      <c r="U35">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B36" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C36" s="14">
-        <f t="shared" ref="C36:J36" si="13">(C$18/C$17)*(C15/C$19)/C56*1000000</f>
+        <f t="shared" ref="C36:J36" si="14">(C$18/C$17)*(C15/C$19)/C56*1000000</f>
         <v>1783.7372030183981</v>
       </c>
       <c r="D36" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1468.3236113010753</v>
       </c>
       <c r="E36" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1549.3337042529031</v>
       </c>
       <c r="F36" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1459.981099787233</v>
       </c>
       <c r="G36" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1665.3859782240534</v>
       </c>
       <c r="H36" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2024.3446346801513</v>
       </c>
       <c r="I36" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2194.0530072489773</v>
       </c>
       <c r="J36" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2325.3018800328973</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M36" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="N36">
+        <v>17.3</v>
+      </c>
+      <c r="O36">
+        <v>12.8</v>
+      </c>
+      <c r="P36">
+        <v>12.4</v>
+      </c>
+      <c r="Q36">
+        <v>12.2</v>
+      </c>
+      <c r="R36">
+        <v>13</v>
+      </c>
+      <c r="S36">
+        <v>15.2</v>
+      </c>
+      <c r="T36">
+        <v>15.1</v>
+      </c>
+      <c r="U36">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B37" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C37" s="14">
-        <f t="shared" ref="C37:J37" si="14">(C$18/C$17)*(C16/C$19)/C57*1000000</f>
+        <f t="shared" ref="C37:J37" si="15">(C$18/C$17)*(C16/C$19)/C57*1000000</f>
         <v>4646.5218348172457</v>
       </c>
       <c r="D37" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>4294.7359771626143</v>
       </c>
       <c r="E37" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5018.6131250561448</v>
       </c>
       <c r="F37" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>4734.9608163934499</v>
       </c>
       <c r="G37" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5385.017441306577</v>
       </c>
       <c r="H37" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6273.1375167536953</v>
       </c>
       <c r="I37" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7158.2557734097409</v>
       </c>
       <c r="J37" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>8369.7402253810706</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M37" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="N37" s="20">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="O37" s="20">
+        <v>34.299999999999997</v>
+      </c>
+      <c r="P37" s="19">
+        <v>35.4</v>
+      </c>
+      <c r="Q37" s="19">
+        <v>34.5</v>
+      </c>
+      <c r="R37" s="19">
+        <v>35.1</v>
+      </c>
+      <c r="S37" s="19">
+        <v>31.2</v>
+      </c>
+      <c r="T37" s="19">
+        <v>28.2</v>
+      </c>
+      <c r="U37" s="23">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B38" s="10" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B43" s="18" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C43" s="18">
         <v>2017</v>
@@ -7026,8 +7731,35 @@
       <c r="J43" s="18">
         <v>2024</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M43" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="N43" s="18">
+        <v>2017</v>
+      </c>
+      <c r="O43" s="18">
+        <v>2018</v>
+      </c>
+      <c r="P43" s="18">
+        <v>2019</v>
+      </c>
+      <c r="Q43" s="18">
+        <v>2020</v>
+      </c>
+      <c r="R43" s="18">
+        <v>2021</v>
+      </c>
+      <c r="S43" s="18">
+        <v>2022</v>
+      </c>
+      <c r="T43" s="18">
+        <v>2023</v>
+      </c>
+      <c r="U43" s="18">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>1</v>
       </c>
@@ -7058,8 +7790,35 @@
       <c r="J44">
         <v>2002.7</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M44" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44">
+        <v>7.5</v>
+      </c>
+      <c r="O44">
+        <v>6.7</v>
+      </c>
+      <c r="P44">
+        <v>8.1</v>
+      </c>
+      <c r="Q44">
+        <v>8.6</v>
+      </c>
+      <c r="R44">
+        <v>8</v>
+      </c>
+      <c r="S44">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="T44">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="U44">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>2</v>
       </c>
@@ -7090,8 +7849,35 @@
       <c r="J45">
         <v>3394.4</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M45" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45">
+        <v>5.6</v>
+      </c>
+      <c r="O45">
+        <v>4.8</v>
+      </c>
+      <c r="P45">
+        <v>4.8</v>
+      </c>
+      <c r="Q45">
+        <v>5.6</v>
+      </c>
+      <c r="R45">
+        <v>5.8</v>
+      </c>
+      <c r="S45">
+        <v>6.8</v>
+      </c>
+      <c r="T45">
+        <v>5.7</v>
+      </c>
+      <c r="U45">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>3</v>
       </c>
@@ -7122,8 +7908,35 @@
       <c r="J46">
         <v>2044</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M46" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="N46">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="O46">
+        <v>7.7</v>
+      </c>
+      <c r="P46">
+        <v>7.4</v>
+      </c>
+      <c r="Q46">
+        <v>8</v>
+      </c>
+      <c r="R46">
+        <v>8.5</v>
+      </c>
+      <c r="S46">
+        <v>10</v>
+      </c>
+      <c r="T46">
+        <v>9.5</v>
+      </c>
+      <c r="U46">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>4</v>
       </c>
@@ -7154,8 +7967,35 @@
       <c r="J47">
         <v>1507.4</v>
       </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M47" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="N47">
+        <v>8.1</v>
+      </c>
+      <c r="O47">
+        <v>5.7</v>
+      </c>
+      <c r="P47">
+        <v>7.2</v>
+      </c>
+      <c r="Q47">
+        <v>6.6</v>
+      </c>
+      <c r="R47">
+        <v>5.9</v>
+      </c>
+      <c r="S47">
+        <v>7</v>
+      </c>
+      <c r="T47">
+        <v>6.4</v>
+      </c>
+      <c r="U47">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>5</v>
       </c>
@@ -7186,8 +8026,35 @@
       <c r="J48">
         <v>3560.6</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M48" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="N48">
+        <v>7.6</v>
+      </c>
+      <c r="O48">
+        <v>6.5</v>
+      </c>
+      <c r="P48">
+        <v>6.4</v>
+      </c>
+      <c r="Q48">
+        <v>6.2</v>
+      </c>
+      <c r="R48">
+        <v>6.6</v>
+      </c>
+      <c r="S48">
+        <v>7.9</v>
+      </c>
+      <c r="T48">
+        <v>8.1</v>
+      </c>
+      <c r="U48">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>6</v>
       </c>
@@ -7218,8 +8085,35 @@
       <c r="J49">
         <v>1075.3</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M49" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="N49">
+        <v>4.8</v>
+      </c>
+      <c r="O49">
+        <v>4.5</v>
+      </c>
+      <c r="P49">
+        <v>4.2</v>
+      </c>
+      <c r="Q49">
+        <v>3.4</v>
+      </c>
+      <c r="R49">
+        <v>3.8</v>
+      </c>
+      <c r="S49">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="T49">
+        <v>4.7</v>
+      </c>
+      <c r="U49">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>7</v>
       </c>
@@ -7250,8 +8144,35 @@
       <c r="J50">
         <v>3066.1</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M50" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="N50">
+        <v>6.8</v>
+      </c>
+      <c r="O50">
+        <v>5.5</v>
+      </c>
+      <c r="P50">
+        <v>6.7</v>
+      </c>
+      <c r="Q50">
+        <v>7.5</v>
+      </c>
+      <c r="R50">
+        <v>7.3</v>
+      </c>
+      <c r="S50">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="T50">
+        <v>8</v>
+      </c>
+      <c r="U50">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>8</v>
       </c>
@@ -7282,8 +8203,35 @@
       <c r="J51">
         <v>4208.5</v>
       </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M51" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="N51">
+        <v>5.9</v>
+      </c>
+      <c r="O51">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="P51">
+        <v>5.3</v>
+      </c>
+      <c r="Q51">
+        <v>5.9</v>
+      </c>
+      <c r="R51">
+        <v>6.1</v>
+      </c>
+      <c r="S51">
+        <v>6.5</v>
+      </c>
+      <c r="T51">
+        <v>6.2</v>
+      </c>
+      <c r="U51">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>9</v>
       </c>
@@ -7314,8 +8262,35 @@
       <c r="J52">
         <v>2877.1</v>
       </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M52" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="N52">
+        <v>7.7</v>
+      </c>
+      <c r="O52">
+        <v>6.9</v>
+      </c>
+      <c r="P52">
+        <v>8</v>
+      </c>
+      <c r="Q52">
+        <v>8.6</v>
+      </c>
+      <c r="R52">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="S52">
+        <v>10.6</v>
+      </c>
+      <c r="T52">
+        <v>9.9</v>
+      </c>
+      <c r="U52">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>10</v>
       </c>
@@ -7346,8 +8321,35 @@
       <c r="J53">
         <v>914</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M53" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="N53">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="O53">
+        <v>5.5</v>
+      </c>
+      <c r="P53">
+        <v>7.6</v>
+      </c>
+      <c r="Q53">
+        <v>8.5</v>
+      </c>
+      <c r="R53">
+        <v>7.9</v>
+      </c>
+      <c r="S53">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="T53">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="U53">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>11</v>
       </c>
@@ -7378,8 +8380,35 @@
       <c r="J54">
         <v>3051.8</v>
       </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M54" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="N54">
+        <v>3.7</v>
+      </c>
+      <c r="O54">
+        <v>3.4</v>
+      </c>
+      <c r="P54">
+        <v>4.7</v>
+      </c>
+      <c r="Q54">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="R54">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="S54">
+        <v>7.1</v>
+      </c>
+      <c r="T54">
+        <v>7.2</v>
+      </c>
+      <c r="U54">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>12</v>
       </c>
@@ -7410,8 +8439,35 @@
       <c r="J55">
         <v>4061.5</v>
       </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M55" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="N55">
+        <v>6.2</v>
+      </c>
+      <c r="O55">
+        <v>5</v>
+      </c>
+      <c r="P55">
+        <v>5.9</v>
+      </c>
+      <c r="Q55">
+        <v>6.6</v>
+      </c>
+      <c r="R55">
+        <v>6.5</v>
+      </c>
+      <c r="S55">
+        <v>8</v>
+      </c>
+      <c r="T55">
+        <v>7.7</v>
+      </c>
+      <c r="U55">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>13</v>
       </c>
@@ -7442,8 +8498,35 @@
       <c r="J56">
         <v>1995.6</v>
       </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M56" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="N56">
+        <v>7.2</v>
+      </c>
+      <c r="O56">
+        <v>5.4</v>
+      </c>
+      <c r="P56">
+        <v>6</v>
+      </c>
+      <c r="Q56">
+        <v>6</v>
+      </c>
+      <c r="R56">
+        <v>7.1</v>
+      </c>
+      <c r="S56">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="T56">
+        <v>8.5</v>
+      </c>
+      <c r="U56">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>14</v>
       </c>
@@ -7474,47 +8557,74 @@
       <c r="J57">
         <v>3040.8</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M57" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="N57" s="20">
+        <v>7.4</v>
+      </c>
+      <c r="O57" s="20">
+        <v>8.1</v>
+      </c>
+      <c r="P57" s="19">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="Q57" s="19">
+        <v>9.5</v>
+      </c>
+      <c r="R57" s="19">
+        <v>10.1</v>
+      </c>
+      <c r="S57" s="19">
+        <v>11.5</v>
+      </c>
+      <c r="T57" s="19">
+        <v>10.4</v>
+      </c>
+      <c r="U57" s="23">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B58" s="7" t="s">
         <v>48</v>
       </c>
       <c r="C58" s="7">
-        <f>SUM(C44:C57)</f>
+        <f t="shared" ref="C58:J58" si="16">SUM(C44:C57)</f>
         <v>32120.499999999993</v>
       </c>
       <c r="D58" s="7">
-        <f>SUM(D44:D57)</f>
+        <f t="shared" si="16"/>
         <v>32656.700000000004</v>
       </c>
       <c r="E58" s="7">
-        <f>SUM(E44:E57)</f>
+        <f t="shared" si="16"/>
         <v>33255.5</v>
       </c>
       <c r="F58" s="7">
-        <f>SUM(F44:F57)</f>
+        <f t="shared" si="16"/>
         <v>33905.199999999997</v>
       </c>
       <c r="G58" s="7">
-        <f>SUM(G44:G57)</f>
+        <f t="shared" si="16"/>
         <v>34558.9</v>
       </c>
       <c r="H58" s="7">
-        <f>SUM(H44:H57)</f>
+        <f t="shared" si="16"/>
         <v>35271.300000000003</v>
       </c>
       <c r="I58" s="7">
-        <f>SUM(I44:I57)</f>
+        <f t="shared" si="16"/>
         <v>36024.9</v>
       </c>
       <c r="J58" s="7">
-        <f>SUM(J44:J57)</f>
+        <f t="shared" si="16"/>
         <v>36799.800000000003</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B62" s="18" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="C62" s="18">
         <v>2017</v>
@@ -7541,7 +8651,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>1</v>
       </c>
@@ -7573,8 +8683,35 @@
         <v>480.8</v>
       </c>
       <c r="K63" s="20"/>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M63" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="N63" s="18">
+        <v>2017</v>
+      </c>
+      <c r="O63" s="19">
+        <v>2018</v>
+      </c>
+      <c r="P63" s="19">
+        <v>2019</v>
+      </c>
+      <c r="Q63" s="19">
+        <v>2020</v>
+      </c>
+      <c r="R63" s="19">
+        <v>2021</v>
+      </c>
+      <c r="S63" s="19">
+        <v>2022</v>
+      </c>
+      <c r="T63" s="19">
+        <v>2023</v>
+      </c>
+      <c r="U63" s="19">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>2</v>
       </c>
@@ -7606,8 +8743,35 @@
         <v>294.5</v>
       </c>
       <c r="K64" s="20"/>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="N64" s="14">
+        <v>44.6</v>
+      </c>
+      <c r="O64" s="20">
+        <v>35.5</v>
+      </c>
+      <c r="P64" s="20">
+        <v>35.700000000000003</v>
+      </c>
+      <c r="Q64" s="20">
+        <v>35.4</v>
+      </c>
+      <c r="R64" s="20">
+        <v>37</v>
+      </c>
+      <c r="S64" s="20">
+        <v>44.3</v>
+      </c>
+      <c r="T64" s="20">
+        <v>46.5</v>
+      </c>
+      <c r="U64" s="20">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>3</v>
       </c>
@@ -7639,8 +8803,35 @@
         <v>195.8</v>
       </c>
       <c r="K65" s="20"/>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="N65" s="20">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="O65" s="20">
+        <v>28.1</v>
+      </c>
+      <c r="P65" s="20">
+        <v>28.4</v>
+      </c>
+      <c r="Q65" s="20">
+        <v>28.8</v>
+      </c>
+      <c r="R65" s="20">
+        <v>30.8</v>
+      </c>
+      <c r="S65" s="20">
+        <v>33.6</v>
+      </c>
+      <c r="T65" s="20">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="U65" s="20">
+        <v>34.299999999999997</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>4</v>
       </c>
@@ -7672,8 +8863,35 @@
         <v>295.60000000000002</v>
       </c>
       <c r="K66" s="20"/>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M66" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="N66" s="20">
+        <v>39.6</v>
+      </c>
+      <c r="O66" s="20">
+        <v>30.7</v>
+      </c>
+      <c r="P66" s="20">
+        <v>30.4</v>
+      </c>
+      <c r="Q66" s="20">
+        <v>29</v>
+      </c>
+      <c r="R66" s="20">
+        <v>29.5</v>
+      </c>
+      <c r="S66" s="20">
+        <v>33.5</v>
+      </c>
+      <c r="T66" s="20">
+        <v>34</v>
+      </c>
+      <c r="U66" s="20">
+        <v>35.200000000000003</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>5</v>
       </c>
@@ -7705,8 +8923,35 @@
         <v>161.30000000000001</v>
       </c>
       <c r="K67" s="20"/>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M67" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="N67" s="20">
+        <v>42.4</v>
+      </c>
+      <c r="O67" s="20">
+        <v>29.4</v>
+      </c>
+      <c r="P67" s="20">
+        <v>29.5</v>
+      </c>
+      <c r="Q67" s="20">
+        <v>28.5</v>
+      </c>
+      <c r="R67" s="20">
+        <v>28.4</v>
+      </c>
+      <c r="S67" s="20">
+        <v>32.6</v>
+      </c>
+      <c r="T67" s="20">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="U67" s="20">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>6</v>
       </c>
@@ -7738,8 +8983,35 @@
         <v>696.5</v>
       </c>
       <c r="K68" s="20"/>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="N68" s="20">
+        <v>34.6</v>
+      </c>
+      <c r="O68" s="20">
+        <v>33.1</v>
+      </c>
+      <c r="P68" s="20">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="Q68" s="20">
+        <v>34.5</v>
+      </c>
+      <c r="R68" s="20">
+        <v>34.299999999999997</v>
+      </c>
+      <c r="S68" s="20">
+        <v>40.1</v>
+      </c>
+      <c r="T68" s="20">
+        <v>40.5</v>
+      </c>
+      <c r="U68" s="20">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>7</v>
       </c>
@@ -7771,8 +9043,35 @@
         <v>585.20000000000005</v>
       </c>
       <c r="K69" s="20"/>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="N69" s="20">
+        <v>22.8</v>
+      </c>
+      <c r="O69" s="20">
+        <v>17.8</v>
+      </c>
+      <c r="P69" s="20">
+        <v>14.3</v>
+      </c>
+      <c r="Q69" s="20">
+        <v>11.7</v>
+      </c>
+      <c r="R69" s="20">
+        <v>12.3</v>
+      </c>
+      <c r="S69" s="20">
+        <v>14.1</v>
+      </c>
+      <c r="T69" s="20">
+        <v>13.9</v>
+      </c>
+      <c r="U69" s="20">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>8</v>
       </c>
@@ -7804,8 +9103,35 @@
         <v>201.6</v>
       </c>
       <c r="K70" s="20"/>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="N70" s="20">
+        <v>47.4</v>
+      </c>
+      <c r="O70" s="20">
+        <v>36.4</v>
+      </c>
+      <c r="P70" s="20">
+        <v>37.4</v>
+      </c>
+      <c r="Q70" s="20">
+        <v>36.4</v>
+      </c>
+      <c r="R70" s="20">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="S70" s="20">
+        <v>43.6</v>
+      </c>
+      <c r="T70" s="20">
+        <v>44.4</v>
+      </c>
+      <c r="U70" s="20">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>9</v>
       </c>
@@ -7837,8 +9163,35 @@
         <v>99.3</v>
       </c>
       <c r="K71" s="20"/>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="N71" s="20">
+        <v>43.3</v>
+      </c>
+      <c r="O71" s="20">
+        <v>33.1</v>
+      </c>
+      <c r="P71" s="20">
+        <v>36.1</v>
+      </c>
+      <c r="Q71" s="20">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="R71" s="20">
+        <v>35.9</v>
+      </c>
+      <c r="S71" s="20">
+        <v>42.5</v>
+      </c>
+      <c r="T71" s="20">
+        <v>43.5</v>
+      </c>
+      <c r="U71" s="20">
+        <v>44.9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>10</v>
       </c>
@@ -7870,8 +9223,35 @@
         <v>153.1</v>
       </c>
       <c r="K72" s="20"/>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M72" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="N72" s="20">
+        <v>43.8</v>
+      </c>
+      <c r="O72" s="20">
+        <v>35.700000000000003</v>
+      </c>
+      <c r="P72" s="20">
+        <v>35.6</v>
+      </c>
+      <c r="Q72" s="20">
+        <v>35.9</v>
+      </c>
+      <c r="R72" s="20">
+        <v>36.4</v>
+      </c>
+      <c r="S72" s="20">
+        <v>40.5</v>
+      </c>
+      <c r="T72" s="20">
+        <v>40.4</v>
+      </c>
+      <c r="U72" s="20">
+        <v>41.9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>11</v>
       </c>
@@ -7903,8 +9283,35 @@
         <v>3040.8</v>
       </c>
       <c r="K73" s="20"/>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="N73" s="20">
+        <v>33.5</v>
+      </c>
+      <c r="O73" s="20">
+        <v>29.8</v>
+      </c>
+      <c r="P73" s="20">
+        <v>27.2</v>
+      </c>
+      <c r="Q73" s="20">
+        <v>28.1</v>
+      </c>
+      <c r="R73" s="20">
+        <v>28</v>
+      </c>
+      <c r="S73" s="20">
+        <v>31.7</v>
+      </c>
+      <c r="T73" s="20">
+        <v>31.3</v>
+      </c>
+      <c r="U73" s="20">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>12</v>
       </c>
@@ -7936,8 +9343,35 @@
         <v>56.2</v>
       </c>
       <c r="K74" s="20"/>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="N74" s="20">
+        <v>34.5</v>
+      </c>
+      <c r="O74" s="20">
+        <v>26.8</v>
+      </c>
+      <c r="P74" s="20">
+        <v>25.1</v>
+      </c>
+      <c r="Q74" s="20">
+        <v>24</v>
+      </c>
+      <c r="R74" s="20">
+        <v>23.2</v>
+      </c>
+      <c r="S74" s="20">
+        <v>27.3</v>
+      </c>
+      <c r="T74" s="20">
+        <v>28.7</v>
+      </c>
+      <c r="U74" s="20">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>13</v>
       </c>
@@ -7969,23 +9403,108 @@
         <v>339.2</v>
       </c>
       <c r="K75" s="20"/>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="N75" s="20">
+        <v>45.8</v>
+      </c>
+      <c r="O75" s="20">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="P75" s="20">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="Q75" s="20">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="R75" s="20">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="S75" s="20">
+        <v>42.7</v>
+      </c>
+      <c r="T75" s="20">
+        <v>43.3</v>
+      </c>
+      <c r="U75" s="20">
+        <v>44.7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.2">
       <c r="J76">
         <f>SUM(J63:J75)</f>
         <v>6599.9</v>
       </c>
-      <c r="L76">
+      <c r="M76" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="N76" s="20">
+        <v>45.1</v>
+      </c>
+      <c r="O76" s="20">
+        <v>33.4</v>
+      </c>
+      <c r="P76" s="20">
+        <v>35.6</v>
+      </c>
+      <c r="Q76" s="20">
+        <v>34.5</v>
+      </c>
+      <c r="R76" s="20">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="S76" s="20">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="T76" s="20">
+        <v>38.6</v>
+      </c>
+      <c r="U76" s="20">
+        <v>40.299999999999997</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="M77" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="N77" s="20">
+        <v>60.4</v>
+      </c>
+      <c r="O77" s="20">
+        <v>57.6</v>
+      </c>
+      <c r="P77" s="19">
+        <v>55.4</v>
+      </c>
+      <c r="Q77" s="19">
+        <v>56</v>
+      </c>
+      <c r="R77" s="19">
+        <v>54.8</v>
+      </c>
+      <c r="S77" s="19">
+        <v>57.3</v>
+      </c>
+      <c r="T77" s="19">
+        <v>61.4</v>
+      </c>
+      <c r="U77" s="23">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="I80">
         <f>J76/J58*100</f>
         <v>17.934608340262717</v>
       </c>
-      <c r="M76" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="M77" t="s">
-        <v>77</v>
+      <c r="J80" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="81" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="J81" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="82" spans="2:16" x14ac:dyDescent="0.2">
@@ -8238,7 +9757,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" ht="19" x14ac:dyDescent="0.25">
@@ -8266,6 +9785,11 @@
       </c>
       <c r="C3" s="2" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C5" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/uzbekistan_pop_grp.xlsx
+++ b/uzbekistan_pop_grp.xlsx
@@ -14,8 +14,9 @@
   <sheets>
     <sheet name="Population Data" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
-    <sheet name="Лист1" sheetId="4" r:id="rId3"/>
+    <sheet name="Лист2" sheetId="5" r:id="rId3"/>
     <sheet name="Sources" sheetId="2" r:id="rId4"/>
+    <sheet name="Лист1" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="113">
   <si>
     <t>Uzbekistan Population by Region (2024–2025)</t>
   </si>
@@ -370,6 +371,9 @@
   </si>
   <si>
     <t>+</t>
+  </si>
+  <si>
+    <t>Salary Region</t>
   </si>
 </sst>
 </file>
@@ -996,11 +1000,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="263832976"/>
-        <c:axId val="263827880"/>
+        <c:axId val="400473800"/>
+        <c:axId val="400473408"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="263832976"/>
+        <c:axId val="400473800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1029,7 +1033,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="263827880"/>
+        <c:crossAx val="400473408"/>
         <c:crosses val="autoZero"/>
         <c:auto val="0"/>
         <c:lblAlgn val="ctr"/>
@@ -1037,7 +1041,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="263827880"/>
+        <c:axId val="400473408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1067,7 +1071,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="263832976"/>
+        <c:crossAx val="400473800"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1222,11 +1226,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="263829448"/>
-        <c:axId val="263829056"/>
+        <c:axId val="400475368"/>
+        <c:axId val="400475760"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="263829448"/>
+        <c:axId val="400475368"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1255,7 +1259,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="263829056"/>
+        <c:crossAx val="400475760"/>
         <c:crosses val="autoZero"/>
         <c:auto val="0"/>
         <c:lblAlgn val="ctr"/>
@@ -1263,7 +1267,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="263829056"/>
+        <c:axId val="400475760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1293,7 +1297,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="263829448"/>
+        <c:crossAx val="400475368"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1679,11 +1683,11 @@
         </c:dLbls>
         <c:gapWidth val="80"/>
         <c:overlap val="25"/>
-        <c:axId val="263830232"/>
-        <c:axId val="263834936"/>
+        <c:axId val="391766584"/>
+        <c:axId val="391763448"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="263830232"/>
+        <c:axId val="391766584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1726,7 +1730,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="263834936"/>
+        <c:crossAx val="391763448"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1734,7 +1738,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="263834936"/>
+        <c:axId val="391763448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1785,7 +1789,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="263830232"/>
+        <c:crossAx val="391766584"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2228,11 +2232,11 @@
         </c:dLbls>
         <c:gapWidth val="80"/>
         <c:overlap val="25"/>
-        <c:axId val="263832192"/>
-        <c:axId val="263829840"/>
+        <c:axId val="391764624"/>
+        <c:axId val="391765016"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="263832192"/>
+        <c:axId val="391764624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2275,7 +2279,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="263829840"/>
+        <c:crossAx val="391765016"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2283,7 +2287,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="263829840"/>
+        <c:axId val="391765016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2334,7 +2338,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="263832192"/>
+        <c:crossAx val="391764624"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3493,7 +3497,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3524,7 +3528,7 @@
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3560,7 +3564,7 @@
         <xdr:cNvPr id="9" name="Chart 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9E6B9DD3-9AD8-A0F9-6222-3097CBAAF386}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E6B9DD3-9AD8-A0F9-6222-3097CBAAF386}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3596,7 +3600,7 @@
         <xdr:cNvPr id="11" name="Chart 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{90BC8AFB-4008-3DDD-F6BC-DD31737172DD}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90BC8AFB-4008-3DDD-F6BC-DD31737172DD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6303,7 +6307,7 @@
         <v>-1.6085714285714281</v>
       </c>
       <c r="AD5" s="7">
-        <f t="shared" ref="AD5:AD17" si="8">U5/AVERAGE(N5:U5)</f>
+        <f t="shared" ref="AD5:AD16" si="8">U5/AVERAGE(N5:U5)</f>
         <v>0.80702896192645623</v>
       </c>
       <c r="AE5" s="7"/>
@@ -7877,9 +7881,6 @@
       <c r="Z21" s="15"/>
       <c r="AA21" s="15"/>
       <c r="AB21" s="15"/>
-      <c r="AQ21" s="22" t="s">
-        <v>97</v>
-      </c>
     </row>
     <row r="22" spans="1:57">
       <c r="C22" s="15"/>
@@ -7899,30 +7900,6 @@
       <c r="Z22" s="15"/>
       <c r="AA22" s="15"/>
       <c r="AB22" s="15"/>
-      <c r="AS22" s="18">
-        <v>2017</v>
-      </c>
-      <c r="AT22" s="18">
-        <v>2018</v>
-      </c>
-      <c r="AU22" s="18">
-        <v>2019</v>
-      </c>
-      <c r="AV22" s="18">
-        <v>2020</v>
-      </c>
-      <c r="AW22" s="18">
-        <v>2021</v>
-      </c>
-      <c r="AX22" s="18">
-        <v>2022</v>
-      </c>
-      <c r="AY22" s="18">
-        <v>2023</v>
-      </c>
-      <c r="AZ22" s="18">
-        <v>2024</v>
-      </c>
       <c r="BA22" t="s">
         <v>104</v>
       </c>
@@ -8015,6 +7992,33 @@
       <c r="AG23" t="s">
         <v>96</v>
       </c>
+      <c r="AR23" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="AS23" s="18">
+        <v>2017</v>
+      </c>
+      <c r="AT23" s="18">
+        <v>2018</v>
+      </c>
+      <c r="AU23" s="18">
+        <v>2019</v>
+      </c>
+      <c r="AV23" s="18">
+        <v>2020</v>
+      </c>
+      <c r="AW23" s="18">
+        <v>2021</v>
+      </c>
+      <c r="AX23" s="18">
+        <v>2022</v>
+      </c>
+      <c r="AY23" s="18">
+        <v>2023</v>
+      </c>
+      <c r="AZ23" s="18">
+        <v>2024</v>
+      </c>
       <c r="BC23" t="s">
         <v>28</v>
       </c>
@@ -8121,7 +8125,7 @@
         <v>0.80078125</v>
       </c>
       <c r="AG24" s="22" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AH24" s="18">
         <v>2017</v>
@@ -13642,23 +13646,23 @@
         <v>29</v>
       </c>
       <c r="AS62" s="7">
-        <f t="shared" ref="AS62:AS74" si="51">AVERAGE(AS44:AU44)</f>
+        <f t="shared" ref="AS62:AS73" si="51">AVERAGE(AS44:AU44)</f>
         <v>1.1894475364929762</v>
       </c>
       <c r="AT62" s="7">
-        <f t="shared" ref="AT62:AT74" si="52">AVERAGE(AT44:AV44)</f>
+        <f t="shared" ref="AT62:AT73" si="52">AVERAGE(AT44:AV44)</f>
         <v>1.2150371236479625</v>
       </c>
       <c r="AU62" s="7">
-        <f t="shared" ref="AU62:AU74" si="53">AVERAGE(AU44:AW44)</f>
+        <f t="shared" ref="AU62:AU73" si="53">AVERAGE(AU44:AW44)</f>
         <v>1.2215479870315498</v>
       </c>
       <c r="AV62" s="7">
-        <f t="shared" ref="AV62:AV74" si="54">AVERAGE(AV44:AX44)</f>
+        <f t="shared" ref="AV62:AV73" si="54">AVERAGE(AV44:AX44)</f>
         <v>1.2428420832813005</v>
       </c>
       <c r="AW62" s="7">
-        <f t="shared" ref="AW62:AX74" si="55">AVERAGE(AW44:AY44)</f>
+        <f t="shared" ref="AW62:AW73" si="55">AVERAGE(AW44:AY44)</f>
         <v>1.2655774314252204</v>
       </c>
       <c r="AX62" s="7">
@@ -13924,35 +13928,35 @@
         <v>29</v>
       </c>
       <c r="AH64" s="15">
-        <f>AH44/C$19</f>
+        <f t="shared" ref="AH64:AH76" si="65">AH44/C$19</f>
         <v>246.99346763152749</v>
       </c>
       <c r="AI64" s="15">
-        <f>AI44/D$19</f>
+        <f t="shared" ref="AI64:AI76" si="66">AI44/D$19</f>
         <v>204.31109048149523</v>
       </c>
       <c r="AJ64" s="15">
-        <f>AJ44/E$19</f>
+        <f t="shared" ref="AJ64:AJ76" si="67">AJ44/E$19</f>
         <v>228.07527491214148</v>
       </c>
       <c r="AK64" s="15">
-        <f>AK44/F$19</f>
+        <f t="shared" ref="AK64:AK76" si="68">AK44/F$19</f>
         <v>238.00651176705225</v>
       </c>
       <c r="AL64" s="15">
-        <f>AL44/G$19</f>
+        <f t="shared" ref="AL64:AL76" si="69">AL44/G$19</f>
         <v>263.88851408649765</v>
       </c>
       <c r="AM64" s="15">
-        <f>AM44/H$19</f>
+        <f t="shared" ref="AM64:AM76" si="70">AM44/H$19</f>
         <v>317.80706659428159</v>
       </c>
       <c r="AN64" s="15">
-        <f>AN44/I$19</f>
+        <f t="shared" ref="AN64:AN76" si="71">AN44/I$19</f>
         <v>360.53271736353577</v>
       </c>
       <c r="AO64" s="15">
-        <f>AO44/J$19</f>
+        <f t="shared" ref="AO64:AO76" si="72">AO44/J$19</f>
         <v>392.20170723996205</v>
       </c>
       <c r="AQ64">
@@ -14058,11 +14062,11 @@
         <v>34.299999999999997</v>
       </c>
       <c r="W65" s="15">
-        <f t="shared" ref="W65:W77" si="65">AVERAGE(N65:P65)</f>
+        <f t="shared" ref="W65:W77" si="73">AVERAGE(N65:P65)</f>
         <v>32.233333333333341</v>
       </c>
       <c r="X65" s="15">
-        <f t="shared" ref="X65:X77" si="66">AVERAGE(O65:Q65)</f>
+        <f t="shared" ref="X65:X77" si="74">AVERAGE(O65:Q65)</f>
         <v>28.433333333333334</v>
       </c>
       <c r="Y65" s="15">
@@ -14086,7 +14090,7 @@
         <v>0.61047619047619006</v>
       </c>
       <c r="AD65" s="7">
-        <f t="shared" ref="AD65:AD77" si="67">U65/AVERAGE(N65:U65)</f>
+        <f t="shared" ref="AD65:AD77" si="75">U65/AVERAGE(N65:U65)</f>
         <v>1.0660450660450658</v>
       </c>
       <c r="AF65">
@@ -14096,35 +14100,35 @@
         <v>30</v>
       </c>
       <c r="AH65" s="15">
-        <f>AH45/C$19</f>
+        <f t="shared" si="65"/>
         <v>233.91431644826909</v>
       </c>
       <c r="AI65" s="15">
-        <f>AI45/D$19</f>
+        <f t="shared" si="66"/>
         <v>184.99909642282461</v>
       </c>
       <c r="AJ65" s="15">
-        <f>AJ45/E$19</f>
+        <f t="shared" si="67"/>
         <v>210.89244983561954</v>
       </c>
       <c r="AK65" s="15">
-        <f>AK45/F$19</f>
+        <f t="shared" si="68"/>
         <v>213.08409453530115</v>
       </c>
       <c r="AL65" s="15">
-        <f>AL45/G$19</f>
+        <f t="shared" si="69"/>
         <v>240.94557618015639</v>
       </c>
       <c r="AM65" s="15">
-        <f>AM45/H$19</f>
+        <f t="shared" si="70"/>
         <v>283.28887984075283</v>
       </c>
       <c r="AN65" s="15">
-        <f>AN45/I$19</f>
+        <f t="shared" si="71"/>
         <v>320.61110448777998</v>
       </c>
       <c r="AO65" s="15">
-        <f>AO45/J$19</f>
+        <f t="shared" si="72"/>
         <v>341.5252529244388</v>
       </c>
       <c r="AQ65">
@@ -14230,11 +14234,11 @@
         <v>35.200000000000003</v>
       </c>
       <c r="W66" s="15">
-        <f t="shared" si="65"/>
+        <f t="shared" si="73"/>
         <v>33.566666666666663</v>
       </c>
       <c r="X66" s="15">
-        <f t="shared" si="66"/>
+        <f t="shared" si="74"/>
         <v>30.033333333333331</v>
       </c>
       <c r="Y66" s="15">
@@ -14258,7 +14262,7 @@
         <v>0.32190476190476275</v>
       </c>
       <c r="AD66" s="7">
-        <f t="shared" si="67"/>
+        <f t="shared" si="75"/>
         <v>1.0752195494463537</v>
       </c>
       <c r="AF66">
@@ -14268,35 +14272,35 @@
         <v>31</v>
       </c>
       <c r="AH66" s="15">
-        <f>AH46/C$19</f>
+        <f t="shared" si="65"/>
         <v>265.09051437512227</v>
       </c>
       <c r="AI66" s="15">
-        <f>AI46/D$19</f>
+        <f t="shared" si="66"/>
         <v>199.59804431241491</v>
       </c>
       <c r="AJ66" s="15">
-        <f>AJ46/E$19</f>
+        <f t="shared" si="67"/>
         <v>226.82913501870536</v>
       </c>
       <c r="AK66" s="15">
-        <f>AK46/F$19</f>
+        <f t="shared" si="68"/>
         <v>231.31161747108095</v>
       </c>
       <c r="AL66" s="15">
-        <f>AL46/G$19</f>
+        <f t="shared" si="69"/>
         <v>253.2803354376708</v>
       </c>
       <c r="AM66" s="15">
-        <f>AM46/H$19</f>
+        <f t="shared" si="70"/>
         <v>286.96227832066597</v>
       </c>
       <c r="AN66" s="15">
-        <f>AN46/I$19</f>
+        <f t="shared" si="71"/>
         <v>318.07161713361154</v>
       </c>
       <c r="AO66" s="15">
-        <f>AO46/J$19</f>
+        <f t="shared" si="72"/>
         <v>337.92976604489411</v>
       </c>
       <c r="AQ66">
@@ -14402,11 +14406,11 @@
         <v>36</v>
       </c>
       <c r="W67" s="15">
-        <f t="shared" si="65"/>
+        <f t="shared" si="73"/>
         <v>33.766666666666666</v>
       </c>
       <c r="X67" s="15">
-        <f t="shared" si="66"/>
+        <f t="shared" si="74"/>
         <v>29.133333333333336</v>
       </c>
       <c r="Y67" s="15">
@@ -14430,7 +14434,7 @@
         <v>0.28571428571428553</v>
       </c>
       <c r="AD67" s="7">
-        <f t="shared" si="67"/>
+        <f t="shared" si="75"/>
         <v>1.1055662188099808</v>
       </c>
       <c r="AF67">
@@ -14440,35 +14444,35 @@
         <v>32</v>
       </c>
       <c r="AH67" s="15">
-        <f>AH47/C$19</f>
+        <f t="shared" si="65"/>
         <v>268.81470760805792</v>
       </c>
       <c r="AI67" s="15">
-        <f>AI47/D$19</f>
+        <f t="shared" si="66"/>
         <v>204.64880554524075</v>
       </c>
       <c r="AJ67" s="15">
-        <f>AJ47/E$19</f>
+        <f t="shared" si="67"/>
         <v>220.31117787098967</v>
       </c>
       <c r="AK67" s="15">
-        <f>AK47/F$19</f>
+        <f t="shared" si="68"/>
         <v>227.2142899880335</v>
       </c>
       <c r="AL67" s="15">
-        <f>AL47/G$19</f>
+        <f t="shared" si="69"/>
         <v>270.70081974936397</v>
       </c>
       <c r="AM67" s="15">
-        <f>AM47/H$19</f>
+        <f t="shared" si="70"/>
         <v>302.8077452044879</v>
       </c>
       <c r="AN67" s="15">
-        <f>AN47/I$19</f>
+        <f t="shared" si="71"/>
         <v>334.40902665417696</v>
       </c>
       <c r="AO67" s="15">
-        <f>AO47/J$19</f>
+        <f t="shared" si="72"/>
         <v>344.36240120139104</v>
       </c>
       <c r="AQ67">
@@ -14574,11 +14578,11 @@
         <v>41.6</v>
       </c>
       <c r="W68" s="15">
-        <f t="shared" si="65"/>
+        <f t="shared" si="73"/>
         <v>34.133333333333333</v>
       </c>
       <c r="X68" s="15">
-        <f t="shared" si="66"/>
+        <f t="shared" si="74"/>
         <v>34.1</v>
       </c>
       <c r="Y68" s="15">
@@ -14602,7 +14606,7 @@
         <v>1.3542857142857139</v>
       </c>
       <c r="AD68" s="7">
-        <f t="shared" si="67"/>
+        <f t="shared" si="75"/>
         <v>1.1342876618950239</v>
       </c>
       <c r="AF68">
@@ -14612,35 +14616,35 @@
         <v>33</v>
       </c>
       <c r="AH68" s="15">
-        <f>AH48/C$19</f>
+        <f t="shared" si="65"/>
         <v>363.4583414824956</v>
       </c>
       <c r="AI68" s="15">
-        <f>AI48/D$19</f>
+        <f t="shared" si="66"/>
         <v>279.94406485951231</v>
       </c>
       <c r="AJ68" s="15">
-        <f>AJ48/E$19</f>
+        <f t="shared" si="67"/>
         <v>314.42143747874388</v>
       </c>
       <c r="AK68" s="15">
-        <f>AK48/F$19</f>
+        <f t="shared" si="68"/>
         <v>330.10698045472674</v>
       </c>
       <c r="AL68" s="15">
-        <f>AL48/G$19</f>
+        <f t="shared" si="69"/>
         <v>439.76739847357021</v>
       </c>
       <c r="AM68" s="15">
-        <f>AM48/H$19</f>
+        <f t="shared" si="70"/>
         <v>438.95707564241764</v>
       </c>
       <c r="AN68" s="15">
-        <f>AN48/I$19</f>
+        <f t="shared" si="71"/>
         <v>488.00903516988842</v>
       </c>
       <c r="AO68" s="15">
-        <f>AO48/J$19</f>
+        <f t="shared" si="72"/>
         <v>511.37699177995574</v>
       </c>
       <c r="AQ68">
@@ -14746,11 +14750,11 @@
         <v>13</v>
       </c>
       <c r="W69" s="15">
-        <f t="shared" si="65"/>
+        <f t="shared" si="73"/>
         <v>18.3</v>
       </c>
       <c r="X69" s="15">
-        <f t="shared" si="66"/>
+        <f t="shared" si="74"/>
         <v>14.6</v>
       </c>
       <c r="Y69" s="15">
@@ -14774,7 +14778,7 @@
         <v>-0.76380952380952405</v>
       </c>
       <c r="AD69" s="7">
-        <f t="shared" si="67"/>
+        <f t="shared" si="75"/>
         <v>0.86738949124270226</v>
       </c>
       <c r="AF69">
@@ -14784,35 +14788,35 @@
         <v>34</v>
       </c>
       <c r="AH69" s="15">
-        <f>AH49/C$19</f>
+        <f t="shared" si="65"/>
         <v>225.34345785253277</v>
       </c>
       <c r="AI69" s="15">
-        <f>AI49/D$19</f>
+        <f t="shared" si="66"/>
         <v>179.31177125881916</v>
       </c>
       <c r="AJ69" s="15">
-        <f>AJ49/E$19</f>
+        <f t="shared" si="67"/>
         <v>205.24785171749235</v>
       </c>
       <c r="AK69" s="15">
-        <f>AK49/F$19</f>
+        <f t="shared" si="68"/>
         <v>204.04267052253689</v>
       </c>
       <c r="AL69" s="15">
-        <f>AL49/G$19</f>
+        <f t="shared" si="69"/>
         <v>227.47067747102608</v>
       </c>
       <c r="AM69" s="15">
-        <f>AM49/H$19</f>
+        <f t="shared" si="70"/>
         <v>264.01048678972131</v>
       </c>
       <c r="AN69" s="15">
-        <f>AN49/I$19</f>
+        <f t="shared" si="71"/>
         <v>287.15100911181128</v>
       </c>
       <c r="AO69" s="15">
-        <f>AO49/J$19</f>
+        <f t="shared" si="72"/>
         <v>303.18624723363894</v>
       </c>
       <c r="AQ69">
@@ -14918,11 +14922,11 @@
         <v>45.5</v>
       </c>
       <c r="W70" s="15">
-        <f t="shared" si="65"/>
+        <f t="shared" si="73"/>
         <v>40.4</v>
       </c>
       <c r="X70" s="15">
-        <f t="shared" si="66"/>
+        <f t="shared" si="74"/>
         <v>36.733333333333327</v>
       </c>
       <c r="Y70" s="15">
@@ -14946,7 +14950,7 @@
         <v>1.0590476190476199</v>
       </c>
       <c r="AD70" s="7">
-        <f t="shared" si="67"/>
+        <f t="shared" si="75"/>
         <v>1.1104331909701037</v>
       </c>
       <c r="AF70">
@@ -14956,35 +14960,35 @@
         <v>35</v>
       </c>
       <c r="AH70" s="15">
-        <f>AH50/C$19</f>
+        <f t="shared" si="65"/>
         <v>241.52515157441817</v>
       </c>
       <c r="AI70" s="15">
-        <f>AI50/D$19</f>
+        <f t="shared" si="66"/>
         <v>181.66159178116104</v>
       </c>
       <c r="AJ70" s="15">
-        <f>AJ50/E$19</f>
+        <f t="shared" si="67"/>
         <v>207.45117333635642</v>
       </c>
       <c r="AK70" s="15">
-        <f>AK50/F$19</f>
+        <f t="shared" si="68"/>
         <v>212.98173115277223</v>
       </c>
       <c r="AL70" s="15">
-        <f>AL50/G$19</f>
+        <f t="shared" si="69"/>
         <v>241.40685951191935</v>
       </c>
       <c r="AM70" s="15">
-        <f>AM50/H$19</f>
+        <f t="shared" si="70"/>
         <v>281.23172276511036</v>
       </c>
       <c r="AN70" s="15">
-        <f>AN50/I$19</f>
+        <f t="shared" si="71"/>
         <v>311.00147321808737</v>
       </c>
       <c r="AO70" s="15">
-        <f>AO50/J$19</f>
+        <f t="shared" si="72"/>
         <v>337.23688744862471</v>
       </c>
       <c r="AQ70">
@@ -15090,11 +15094,11 @@
         <v>44.9</v>
       </c>
       <c r="W71" s="15">
-        <f t="shared" si="65"/>
+        <f t="shared" si="73"/>
         <v>37.5</v>
       </c>
       <c r="X71" s="15">
-        <f t="shared" si="66"/>
+        <f t="shared" si="74"/>
         <v>34.300000000000004</v>
       </c>
       <c r="Y71" s="15">
@@ -15118,7 +15122,7 @@
         <v>1.4799999999999995</v>
       </c>
       <c r="AD71" s="7">
-        <f t="shared" si="67"/>
+        <f t="shared" si="75"/>
         <v>1.1476038338658148</v>
       </c>
       <c r="AF71">
@@ -15128,35 +15132,35 @@
         <v>36</v>
       </c>
       <c r="AH71" s="15">
-        <f>AH51/C$19</f>
+        <f t="shared" si="65"/>
         <v>252.09458243692549</v>
       </c>
       <c r="AI71" s="15">
-        <f>AI51/D$19</f>
+        <f t="shared" si="66"/>
         <v>200.65727193959648</v>
       </c>
       <c r="AJ71" s="15">
-        <f>AJ51/E$19</f>
+        <f t="shared" si="67"/>
         <v>229.65942636889241</v>
       </c>
       <c r="AK71" s="15">
-        <f>AK51/F$19</f>
+        <f t="shared" si="68"/>
         <v>228.44182289589151</v>
       </c>
       <c r="AL71" s="15">
-        <f>AL51/G$19</f>
+        <f t="shared" si="69"/>
         <v>263.8628757184585</v>
       </c>
       <c r="AM71" s="15">
-        <f>AM51/H$19</f>
+        <f t="shared" si="70"/>
         <v>308.38667209554831</v>
       </c>
       <c r="AN71" s="15">
-        <f>AN51/I$19</f>
+        <f t="shared" si="71"/>
         <v>350.44437537256238</v>
       </c>
       <c r="AO71" s="15">
-        <f>AO51/J$19</f>
+        <f t="shared" si="72"/>
         <v>368.38678469807144</v>
       </c>
       <c r="AQ71">
@@ -15262,11 +15266,11 @@
         <v>41.9</v>
       </c>
       <c r="W72" s="15">
-        <f t="shared" si="65"/>
+        <f t="shared" si="73"/>
         <v>38.366666666666667</v>
       </c>
       <c r="X72" s="15">
-        <f t="shared" si="66"/>
+        <f t="shared" si="74"/>
         <v>35.733333333333341</v>
       </c>
       <c r="Y72" s="15">
@@ -15290,7 +15294,7 @@
         <v>0.7019047619047617</v>
       </c>
       <c r="AD72" s="7">
-        <f t="shared" si="67"/>
+        <f t="shared" si="75"/>
         <v>1.0805931656995487</v>
       </c>
       <c r="AF72">
@@ -15300,35 +15304,35 @@
         <v>37</v>
       </c>
       <c r="AH72" s="15">
-        <f>AH52/C$19</f>
+        <f t="shared" si="65"/>
         <v>238.64707608057893</v>
       </c>
       <c r="AI72" s="15">
-        <f>AI52/D$19</f>
+        <f t="shared" si="66"/>
         <v>180.22617898254734</v>
       </c>
       <c r="AJ72" s="15">
-        <f>AJ52/E$19</f>
+        <f t="shared" si="67"/>
         <v>216.26222650493142</v>
       </c>
       <c r="AK72" s="15">
-        <f>AK52/F$19</f>
+        <f t="shared" si="68"/>
         <v>214.85760869565217</v>
       </c>
       <c r="AL72" s="15">
-        <f>AL52/G$19</f>
+        <f t="shared" si="69"/>
         <v>246.42890794308866</v>
       </c>
       <c r="AM72" s="15">
-        <f>AM52/H$19</f>
+        <f t="shared" si="70"/>
         <v>285.30473217517192</v>
       </c>
       <c r="AN72" s="15">
-        <f>AN52/I$19</f>
+        <f t="shared" si="71"/>
         <v>303.87268159754746</v>
       </c>
       <c r="AO72" s="15">
-        <f>AO52/J$19</f>
+        <f t="shared" si="72"/>
         <v>330.81114448308568</v>
       </c>
       <c r="AQ72">
@@ -15434,11 +15438,11 @@
         <v>32.5</v>
       </c>
       <c r="W73" s="15">
-        <f t="shared" si="65"/>
+        <f t="shared" si="73"/>
         <v>30.166666666666668</v>
       </c>
       <c r="X73" s="15">
-        <f t="shared" si="66"/>
+        <f t="shared" si="74"/>
         <v>28.366666666666664</v>
       </c>
       <c r="Y73" s="15">
@@ -15462,7 +15466,7 @@
         <v>0.44952380952380938</v>
       </c>
       <c r="AD73" s="7">
-        <f t="shared" si="67"/>
+        <f t="shared" si="75"/>
         <v>1.07393638992152</v>
       </c>
       <c r="AF73">
@@ -15472,35 +15476,35 @@
         <v>40</v>
       </c>
       <c r="AH73" s="15">
-        <f>AH53/C$19</f>
+        <f t="shared" si="65"/>
         <v>243.26426755329553</v>
       </c>
       <c r="AI73" s="15">
-        <f>AI53/D$19</f>
+        <f t="shared" si="66"/>
         <v>193.51392499071667</v>
       </c>
       <c r="AJ73" s="15">
-        <f>AJ53/E$19</f>
+        <f t="shared" si="67"/>
         <v>227.25120734610587</v>
       </c>
       <c r="AK73" s="15">
-        <f>AK53/F$19</f>
+        <f t="shared" si="68"/>
         <v>236.38353609892303</v>
       </c>
       <c r="AL73" s="15">
-        <f>AL53/G$19</f>
+        <f t="shared" si="69"/>
         <v>271.68703476867989</v>
       </c>
       <c r="AM73" s="15">
-        <f>AM53/H$19</f>
+        <f t="shared" si="70"/>
         <v>317.36506514657981</v>
       </c>
       <c r="AN73" s="15">
-        <f>AN53/I$19</f>
+        <f t="shared" si="71"/>
         <v>357.39327258792474</v>
       </c>
       <c r="AO73" s="15">
-        <f>AO53/J$19</f>
+        <f t="shared" si="72"/>
         <v>388.78846032247861</v>
       </c>
       <c r="AQ73">
@@ -15606,11 +15610,11 @@
         <v>30.6</v>
       </c>
       <c r="W74" s="15">
-        <f t="shared" si="65"/>
+        <f t="shared" si="73"/>
         <v>28.8</v>
       </c>
       <c r="X74" s="15">
-        <f t="shared" si="66"/>
+        <f t="shared" si="74"/>
         <v>25.3</v>
       </c>
       <c r="Y74" s="15">
@@ -15634,7 +15638,7 @@
         <v>0.12476190476190427</v>
       </c>
       <c r="AD74" s="7">
-        <f t="shared" si="67"/>
+        <f t="shared" si="75"/>
         <v>1.1117166212534062</v>
       </c>
       <c r="AF74">
@@ -15644,35 +15648,35 @@
         <v>41</v>
       </c>
       <c r="AH74" s="15">
-        <f>AH54/C$19</f>
+        <f t="shared" si="65"/>
         <v>336.63672990416586</v>
       </c>
       <c r="AI74" s="15">
-        <f>AI54/D$19</f>
+        <f t="shared" si="66"/>
         <v>261.8566035400421</v>
       </c>
       <c r="AJ74" s="15">
-        <f>AJ54/E$19</f>
+        <f t="shared" si="67"/>
         <v>310.61787779163359</v>
       </c>
       <c r="AK74" s="15">
-        <f>AK54/F$19</f>
+        <f t="shared" si="68"/>
         <v>325.86781013163142</v>
       </c>
       <c r="AL74" s="15">
-        <f>AL54/G$19</f>
+        <f t="shared" si="69"/>
         <v>376.82977480448506</v>
       </c>
       <c r="AM74" s="15">
-        <f>AM54/H$19</f>
+        <f t="shared" si="70"/>
         <v>435.90617987694532</v>
       </c>
       <c r="AN74" s="15">
-        <f>AN54/I$19</f>
+        <f t="shared" si="71"/>
         <v>514.95165630588428</v>
       </c>
       <c r="AO74" s="15">
-        <f>AO54/J$19</f>
+        <f t="shared" si="72"/>
         <v>570.01034619032566</v>
       </c>
       <c r="AS74" s="7"/>
@@ -15690,7 +15694,7 @@
         <v>1</v>
       </c>
       <c r="AZ74" s="7">
-        <f t="shared" ref="AZ62:AZ74" si="68">AX74/$AZ$57</f>
+        <f t="shared" ref="AZ74" si="76">AX74/$AZ$57</f>
         <v>0.95843883164959287</v>
       </c>
     </row>
@@ -15758,11 +15762,11 @@
         <v>44.7</v>
       </c>
       <c r="W75" s="15">
-        <f t="shared" si="65"/>
+        <f t="shared" si="73"/>
         <v>40.133333333333333</v>
       </c>
       <c r="X75" s="15">
-        <f t="shared" si="66"/>
+        <f t="shared" si="74"/>
         <v>37.43333333333333</v>
       </c>
       <c r="Y75" s="15">
@@ -15786,7 +15790,7 @@
         <v>0.86095238095238058</v>
       </c>
       <c r="AD75" s="7">
-        <f t="shared" si="67"/>
+        <f t="shared" si="75"/>
         <v>1.0949173300673609</v>
       </c>
       <c r="AF75">
@@ -15796,35 +15800,35 @@
         <v>39</v>
       </c>
       <c r="AH75" s="15">
-        <f>AH55/C$19</f>
+        <f t="shared" si="65"/>
         <v>244.73352239389791</v>
       </c>
       <c r="AI75" s="15">
-        <f>AI55/D$19</f>
+        <f t="shared" si="66"/>
         <v>224.92770144819903</v>
       </c>
       <c r="AJ75" s="15">
-        <f>AJ55/E$19</f>
+        <f t="shared" si="67"/>
         <v>262.75229565808866</v>
       </c>
       <c r="AK75" s="15">
-        <f>AK55/F$19</f>
+        <f t="shared" si="68"/>
         <v>288.96088950937371</v>
       </c>
       <c r="AL75" s="15">
-        <f>AL55/G$19</f>
+        <f t="shared" si="69"/>
         <v>332.91857156317724</v>
       </c>
       <c r="AM75" s="15">
-        <f>AM55/H$19</f>
+        <f t="shared" si="70"/>
         <v>386.94212812160697</v>
       </c>
       <c r="AN75" s="15">
-        <f>AN55/I$19</f>
+        <f t="shared" si="71"/>
         <v>447.1600698288342</v>
       </c>
       <c r="AO75" s="15">
-        <f>AO55/J$19</f>
+        <f t="shared" si="72"/>
         <v>450.88518811255142</v>
       </c>
     </row>
@@ -15841,7 +15845,7 @@
         <v>6599.9</v>
       </c>
       <c r="L76">
-        <f t="shared" ref="L64:L77" si="69">K76/K57</f>
+        <f t="shared" ref="L76:L77" si="77">K76/K57</f>
         <v>0</v>
       </c>
       <c r="M76" s="14" t="s">
@@ -15872,11 +15876,11 @@
         <v>40.299999999999997</v>
       </c>
       <c r="W76" s="15">
-        <f t="shared" si="65"/>
+        <f t="shared" si="73"/>
         <v>38.033333333333331</v>
       </c>
       <c r="X76" s="15">
-        <f t="shared" si="66"/>
+        <f t="shared" si="74"/>
         <v>34.5</v>
       </c>
       <c r="Y76" s="15">
@@ -15900,7 +15904,7 @@
         <v>0.28476190476190522</v>
       </c>
       <c r="AD76" s="7">
-        <f t="shared" si="67"/>
+        <f t="shared" si="75"/>
         <v>1.0800670016750418</v>
       </c>
       <c r="AF76">
@@ -15910,35 +15914,35 @@
         <v>28</v>
       </c>
       <c r="AH76" s="15">
-        <f>AH56/C$19</f>
+        <f t="shared" si="65"/>
         <v>290.37928808918446</v>
       </c>
       <c r="AI76" s="15">
-        <f>AI56/D$19</f>
+        <f t="shared" si="66"/>
         <v>238.94683747988611</v>
       </c>
       <c r="AJ76" s="15">
-        <f>AJ56/E$19</f>
+        <f t="shared" si="67"/>
         <v>267.72121074708082</v>
       </c>
       <c r="AK76" s="15">
-        <f>AK56/F$19</f>
+        <f t="shared" si="68"/>
         <v>262.23336657359397</v>
       </c>
       <c r="AL76" s="15">
-        <f>AL56/G$19</f>
+        <f t="shared" si="69"/>
         <v>294.38564025252049</v>
       </c>
       <c r="AM76" s="15">
-        <f>AM56/H$19</f>
+        <f t="shared" si="70"/>
         <v>335.76043250090481</v>
       </c>
       <c r="AN76" s="15">
-        <f>AN56/I$19</f>
+        <f t="shared" si="71"/>
         <v>367.43606403815039</v>
       </c>
       <c r="AO76" s="15">
-        <f>AO56/J$19</f>
+        <f t="shared" si="72"/>
         <v>403.78954315523237</v>
       </c>
       <c r="AW76" t="s">
@@ -15950,7 +15954,7 @@
     </row>
     <row r="77" spans="1:52">
       <c r="L77">
-        <f t="shared" si="69"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="M77" s="14" t="s">
@@ -15981,11 +15985,11 @@
         <v>63</v>
       </c>
       <c r="W77" s="15">
-        <f t="shared" si="65"/>
+        <f t="shared" si="73"/>
         <v>57.800000000000004</v>
       </c>
       <c r="X77" s="15">
-        <f t="shared" si="66"/>
+        <f t="shared" si="74"/>
         <v>56.333333333333336</v>
       </c>
       <c r="Y77" s="15">
@@ -16009,7 +16013,7 @@
         <v>0.54190476190476078</v>
       </c>
       <c r="AD77" s="7">
-        <f t="shared" si="67"/>
+        <f t="shared" si="75"/>
         <v>1.0817772054088861</v>
       </c>
       <c r="AF77">
@@ -16023,31 +16027,31 @@
         <v>271.88318012908275</v>
       </c>
       <c r="AI77" s="15">
-        <f t="shared" ref="AI77:AO77" si="70">AI57/D$19</f>
+        <f t="shared" ref="AI77:AO77" si="78">AI57/D$19</f>
         <v>213.6531253868053</v>
       </c>
       <c r="AJ77" s="15">
-        <f t="shared" si="70"/>
+        <f t="shared" si="78"/>
         <v>240.52749121414806</v>
       </c>
       <c r="AK77" s="15">
-        <f t="shared" si="70"/>
+        <f t="shared" si="78"/>
         <v>250.80431790985244</v>
       </c>
       <c r="AL77" s="15">
-        <f t="shared" si="70"/>
+        <f t="shared" si="78"/>
         <v>266.46071798737398</v>
       </c>
       <c r="AM77" s="15">
-        <f t="shared" si="70"/>
+        <f t="shared" si="78"/>
         <v>322.53365001809624</v>
       </c>
       <c r="AN77" s="15">
-        <f t="shared" si="70"/>
+        <f t="shared" si="78"/>
         <v>347.64120752788898</v>
       </c>
       <c r="AO77" s="15">
-        <f t="shared" si="70"/>
+        <f t="shared" si="78"/>
         <v>360.23230319317099</v>
       </c>
     </row>
@@ -16491,15 +16495,15 @@
         <v>2.1199999999999992</v>
       </c>
       <c r="O101">
-        <f t="shared" ref="O101:Q101" si="71">1*14-(SUM(O87:O100))</f>
+        <f t="shared" ref="O101:Q101" si="79">1*14-(SUM(O87:O100))</f>
         <v>-1.0800000000000018</v>
       </c>
       <c r="P101">
-        <f t="shared" si="71"/>
+        <f t="shared" si="79"/>
         <v>-1.0499999999999989</v>
       </c>
       <c r="Q101">
-        <f t="shared" si="71"/>
+        <f t="shared" si="79"/>
         <v>-1.2000000000000011</v>
       </c>
     </row>
@@ -16580,1854 +16584,268 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:Q51"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:14">
-      <c r="C3" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="D3" s="24">
-        <v>2017</v>
-      </c>
-      <c r="E3" s="24">
-        <v>2018</v>
-      </c>
-      <c r="F3" s="24">
-        <v>2019</v>
-      </c>
-      <c r="G3" s="24">
-        <v>2020</v>
-      </c>
-      <c r="H3" s="24">
-        <v>2021</v>
-      </c>
-      <c r="I3" s="24">
-        <v>2022</v>
-      </c>
-      <c r="J3" s="24">
-        <v>2023</v>
-      </c>
-      <c r="K3" s="24">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="4" spans="2:14">
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2">
+        <v>23.5</v>
+      </c>
+      <c r="C2">
+        <v>20.5</v>
+      </c>
+      <c r="D2">
+        <v>8</v>
+      </c>
+      <c r="E2" s="20">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <v>31</v>
+      </c>
+      <c r="C3">
+        <v>28.8</v>
+      </c>
+      <c r="D3">
+        <v>5.9</v>
+      </c>
+      <c r="E3" s="20">
+        <v>34.299999999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="7" t="s">
+        <v>5</v>
+      </c>
       <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="15">
-        <v>1817.5</v>
-      </c>
-      <c r="E4" s="15">
-        <v>1842.3</v>
-      </c>
-      <c r="F4" s="15">
-        <v>1869.8</v>
-      </c>
-      <c r="G4" s="15">
-        <v>1898.3</v>
-      </c>
-      <c r="H4" s="15">
-        <v>1923.7</v>
-      </c>
-      <c r="I4" s="15">
-        <v>1948.5</v>
-      </c>
-      <c r="J4" s="15">
-        <v>1976.2</v>
-      </c>
-      <c r="K4" s="15">
-        <v>2002.7</v>
-      </c>
-      <c r="L4" s="7">
-        <f>K4/AVERAGE(D4:K4)</f>
-        <v>1.048602657241966</v>
-      </c>
-      <c r="M4">
-        <f>L4/$L$18</f>
-        <v>0.97908737497017406</v>
-      </c>
-    </row>
-    <row r="5" spans="2:14">
+        <v>35</v>
+      </c>
+      <c r="C4">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="D4">
+        <v>9.9</v>
+      </c>
+      <c r="E4" s="20">
+        <v>35.200000000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="15">
-        <v>2962.5</v>
-      </c>
-      <c r="E5" s="15">
-        <v>3011.7</v>
-      </c>
-      <c r="F5" s="15">
-        <v>3066.9</v>
-      </c>
-      <c r="G5" s="15">
-        <v>3127.7</v>
-      </c>
-      <c r="H5" s="15">
-        <v>3188.1</v>
-      </c>
-      <c r="I5" s="15">
-        <v>3253.5</v>
-      </c>
-      <c r="J5" s="15">
-        <v>3322.7</v>
-      </c>
-      <c r="K5" s="15">
-        <v>3394.4</v>
-      </c>
-      <c r="L5" s="7">
-        <f t="shared" ref="L5:L18" si="0">K5/AVERAGE(D5:K5)</f>
-        <v>1.0721626690356332</v>
-      </c>
-      <c r="M5">
-        <f t="shared" ref="M5:M17" si="1">L5/$L$18</f>
-        <v>1.0010855169184307</v>
-      </c>
-      <c r="N5" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="6" spans="2:14">
+        <v>40.5</v>
+      </c>
+      <c r="C5">
+        <v>17.3</v>
+      </c>
+      <c r="D5">
+        <v>6.2</v>
+      </c>
+      <c r="E5" s="20">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="7" t="s">
+        <v>7</v>
+      </c>
       <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="15">
-        <v>1843.5</v>
-      </c>
-      <c r="E6" s="15">
-        <v>1870.2</v>
-      </c>
-      <c r="F6" s="15">
-        <v>1894.8</v>
-      </c>
-      <c r="G6" s="15">
-        <v>1923.9</v>
-      </c>
-      <c r="H6" s="15">
-        <v>1947.1</v>
-      </c>
-      <c r="I6" s="15">
-        <v>1976.8</v>
-      </c>
-      <c r="J6" s="15">
-        <v>2009.7</v>
-      </c>
-      <c r="K6" s="15">
-        <v>2044</v>
-      </c>
-      <c r="L6" s="7">
-        <f t="shared" si="0"/>
-        <v>1.0542875564152161</v>
-      </c>
-      <c r="M6">
-        <f t="shared" si="1"/>
-        <v>0.98439540367872924</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="C6">
+        <v>17.7</v>
+      </c>
+      <c r="D6">
+        <v>8</v>
+      </c>
+      <c r="E6" s="20">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="B7">
-        <v>4</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="15">
-        <v>1301</v>
-      </c>
-      <c r="E7" s="15">
-        <v>1325</v>
-      </c>
-      <c r="F7" s="15">
-        <v>1352.4</v>
-      </c>
-      <c r="G7" s="15">
-        <v>1382.1</v>
-      </c>
-      <c r="H7" s="15">
-        <v>1410.5</v>
-      </c>
-      <c r="I7" s="15">
-        <v>1443.4</v>
-      </c>
-      <c r="J7" s="15">
-        <v>1475.5</v>
-      </c>
-      <c r="K7" s="15">
-        <v>1507.4</v>
-      </c>
-      <c r="L7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.0769739133541123</v>
-      </c>
-      <c r="M7">
-        <f t="shared" si="1"/>
-        <v>1.0055778081953857</v>
-      </c>
-      <c r="N7" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="8" spans="2:14">
+        <v>10.7</v>
+      </c>
+      <c r="C7">
+        <v>72.099999999999994</v>
+      </c>
+      <c r="D7">
+        <v>4.2</v>
+      </c>
+      <c r="E7" s="20">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="7" t="s">
+        <v>9</v>
+      </c>
       <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="15">
-        <v>3088.8</v>
-      </c>
-      <c r="E8" s="15">
-        <v>3148.4</v>
-      </c>
-      <c r="F8" s="15">
-        <v>3213.1</v>
-      </c>
-      <c r="G8" s="15">
-        <v>3280.4</v>
-      </c>
-      <c r="H8" s="15">
-        <v>3335.4</v>
-      </c>
-      <c r="I8" s="15">
-        <v>3408.3</v>
-      </c>
-      <c r="J8" s="15">
-        <v>3482.3</v>
-      </c>
-      <c r="K8" s="15">
-        <v>3560.6</v>
-      </c>
-      <c r="L8" s="7">
-        <f t="shared" si="0"/>
-        <v>1.074196845078496</v>
-      </c>
-      <c r="M8">
-        <f t="shared" si="1"/>
-        <v>1.0029848408122612</v>
-      </c>
-      <c r="N8" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14">
+        <v>29.8</v>
+      </c>
+      <c r="C8">
+        <v>16.7</v>
+      </c>
+      <c r="D8">
+        <v>8</v>
+      </c>
+      <c r="E8" s="20">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="B9">
-        <v>6</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="15">
-        <v>942.8</v>
-      </c>
-      <c r="E9" s="15">
-        <v>958</v>
-      </c>
-      <c r="F9" s="15">
-        <v>979.5</v>
-      </c>
-      <c r="G9" s="15">
-        <v>997.1</v>
-      </c>
-      <c r="H9" s="15">
-        <v>1013.6</v>
-      </c>
-      <c r="I9" s="15">
-        <v>1033.9000000000001</v>
-      </c>
-      <c r="J9" s="15">
-        <v>1055.5</v>
-      </c>
-      <c r="K9" s="15">
-        <v>1075.3</v>
-      </c>
-      <c r="L9" s="7">
-        <f t="shared" si="0"/>
-        <v>1.0678649900070758</v>
-      </c>
-      <c r="M9">
-        <f t="shared" si="1"/>
-        <v>0.99707274501720178</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14">
+        <v>32.5</v>
+      </c>
+      <c r="C9">
+        <v>16.7</v>
+      </c>
+      <c r="D9">
+        <v>5.9</v>
+      </c>
+      <c r="E9" s="20">
+        <v>44.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="7" t="s">
+        <v>11</v>
+      </c>
       <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="15">
-        <v>2652.4</v>
-      </c>
-      <c r="E10" s="15">
-        <v>2699.6</v>
-      </c>
-      <c r="F10" s="15">
-        <v>2752.9</v>
-      </c>
-      <c r="G10" s="15">
-        <v>2810.8</v>
-      </c>
-      <c r="H10" s="15">
-        <v>2867.5</v>
-      </c>
-      <c r="I10" s="15">
-        <v>2931.1</v>
-      </c>
-      <c r="J10" s="15">
-        <v>2997.5</v>
-      </c>
-      <c r="K10" s="15">
-        <v>3066.1</v>
-      </c>
-      <c r="L10" s="7">
-        <f t="shared" si="0"/>
-        <v>1.0768683680233913</v>
-      </c>
-      <c r="M10">
-        <f t="shared" si="1"/>
-        <v>1.0054792598080797</v>
-      </c>
-      <c r="N10" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="11" spans="2:14">
+        <v>39.1</v>
+      </c>
+      <c r="C10">
+        <v>9.6</v>
+      </c>
+      <c r="D10">
+        <v>9.4</v>
+      </c>
+      <c r="E10" s="20">
+        <v>41.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="7" t="s">
+        <v>12</v>
+      </c>
       <c r="B11">
-        <v>8</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="15">
-        <v>3651.7</v>
-      </c>
-      <c r="E11" s="15">
-        <v>3720.1</v>
-      </c>
-      <c r="F11" s="15">
-        <v>3798.9</v>
-      </c>
-      <c r="G11" s="15">
-        <v>3877.4</v>
-      </c>
-      <c r="H11" s="15">
-        <v>3947.7</v>
-      </c>
-      <c r="I11" s="15">
-        <v>4031.3</v>
-      </c>
-      <c r="J11" s="15">
-        <v>4118.2</v>
-      </c>
-      <c r="K11" s="15">
-        <v>4208.5</v>
-      </c>
-      <c r="L11" s="7">
-        <f t="shared" si="0"/>
-        <v>1.0738092352442128</v>
-      </c>
-      <c r="M11">
-        <f t="shared" si="1"/>
-        <v>1.0026229268951641</v>
-      </c>
-      <c r="N11" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="12" spans="2:14">
+        <v>32.6</v>
+      </c>
+      <c r="C11">
+        <v>27.3</v>
+      </c>
+      <c r="D11">
+        <v>7.6</v>
+      </c>
+      <c r="E11" s="20">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="7" t="s">
+        <v>13</v>
+      </c>
       <c r="B12">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="15">
-        <v>2462.3000000000002</v>
-      </c>
-      <c r="E12" s="15">
-        <v>2514.1999999999998</v>
-      </c>
-      <c r="F12" s="15">
-        <v>2569.9</v>
-      </c>
-      <c r="G12" s="15">
-        <v>2629.1</v>
-      </c>
-      <c r="H12" s="15">
-        <v>2680.8</v>
-      </c>
-      <c r="I12" s="15">
-        <v>2743.2</v>
-      </c>
-      <c r="J12" s="15">
-        <v>2806.5</v>
-      </c>
-      <c r="K12" s="15">
-        <v>2877.1</v>
-      </c>
-      <c r="L12" s="7">
-        <f t="shared" si="0"/>
-        <v>1.0814589979843163</v>
-      </c>
-      <c r="M12">
-        <f t="shared" si="1"/>
-        <v>1.0097655619711157</v>
-      </c>
-      <c r="N12" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="2:14">
+        <v>17.7</v>
+      </c>
+      <c r="C12">
+        <v>44.5</v>
+      </c>
+      <c r="D12">
+        <v>7.2</v>
+      </c>
+      <c r="E12" s="20">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="B13">
-        <v>10</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="15">
-        <v>803.1</v>
-      </c>
-      <c r="E13" s="15">
-        <v>815.9</v>
-      </c>
-      <c r="F13" s="15">
-        <v>829.9</v>
-      </c>
-      <c r="G13" s="15">
-        <v>846.3</v>
-      </c>
-      <c r="H13" s="15">
-        <v>860.9</v>
-      </c>
-      <c r="I13" s="15">
-        <v>878.6</v>
-      </c>
-      <c r="J13" s="15">
-        <v>896.6</v>
-      </c>
-      <c r="K13" s="15">
-        <v>914</v>
-      </c>
-      <c r="L13" s="7">
-        <f t="shared" si="0"/>
-        <v>1.0681781660409331</v>
-      </c>
-      <c r="M13">
-        <f t="shared" si="1"/>
-        <v>0.99736515959270877</v>
-      </c>
-    </row>
-    <row r="14" spans="2:14">
+        <v>28.2</v>
+      </c>
+      <c r="C13">
+        <v>19.8</v>
+      </c>
+      <c r="D13">
+        <v>7.3</v>
+      </c>
+      <c r="E13" s="20">
+        <v>44.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="B14">
-        <v>11</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="15">
-        <v>2829.3</v>
-      </c>
-      <c r="E14" s="15">
-        <v>2861.2</v>
-      </c>
-      <c r="F14" s="15">
-        <v>2898.5</v>
-      </c>
-      <c r="G14" s="15">
-        <v>2941.9</v>
-      </c>
-      <c r="H14" s="15">
-        <v>2975.9</v>
-      </c>
-      <c r="I14" s="15">
-        <v>2941.5</v>
-      </c>
-      <c r="J14" s="15">
-        <v>2993.4</v>
-      </c>
-      <c r="K14" s="15">
-        <v>3051.8</v>
-      </c>
-      <c r="L14" s="7">
-        <f t="shared" si="0"/>
-        <v>1.0391980760635922</v>
-      </c>
-      <c r="M14">
-        <f t="shared" si="1"/>
-        <v>0.97030625408035431</v>
-      </c>
-    </row>
-    <row r="15" spans="2:14">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="C14">
+        <v>16</v>
+      </c>
+      <c r="D14">
+        <v>8.9</v>
+      </c>
+      <c r="E14" s="20">
+        <v>40.299999999999997</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="7" t="s">
+        <v>16</v>
+      </c>
       <c r="B15">
-        <v>12</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" s="15">
-        <v>3564.8</v>
-      </c>
-      <c r="E15" s="15">
-        <v>3620.2</v>
-      </c>
-      <c r="F15" s="15">
-        <v>3683.3</v>
-      </c>
-      <c r="G15" s="15">
-        <v>3752</v>
-      </c>
-      <c r="H15" s="15">
-        <v>3820</v>
-      </c>
-      <c r="I15" s="15">
-        <v>3896.4</v>
-      </c>
-      <c r="J15" s="15">
-        <v>3976.3</v>
-      </c>
-      <c r="K15" s="15">
-        <v>4061.5</v>
-      </c>
-      <c r="L15" s="7">
-        <f t="shared" si="0"/>
-        <v>1.0697130816968181</v>
-      </c>
-      <c r="M15">
-        <f t="shared" si="1"/>
-        <v>0.99879832069519325</v>
-      </c>
-    </row>
-    <row r="16" spans="2:14">
-      <c r="B16">
-        <v>13</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="15">
-        <v>1776.7</v>
-      </c>
-      <c r="E16" s="15">
-        <v>1805</v>
-      </c>
-      <c r="F16" s="15">
-        <v>1835.7</v>
-      </c>
-      <c r="G16" s="15">
-        <v>1866.5</v>
-      </c>
-      <c r="H16" s="15">
-        <v>1893.3</v>
-      </c>
-      <c r="I16" s="15">
-        <v>1924.2</v>
-      </c>
-      <c r="J16" s="15">
-        <v>1958.1</v>
-      </c>
-      <c r="K16" s="15">
-        <v>1995.6</v>
-      </c>
-      <c r="L16" s="7">
-        <f t="shared" si="0"/>
-        <v>1.0604247065778374</v>
-      </c>
-      <c r="M16">
-        <f t="shared" si="1"/>
-        <v>0.99012570218695828</v>
-      </c>
-    </row>
-    <row r="17" spans="2:15">
-      <c r="B17">
-        <v>14</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="15">
-        <v>2424.1</v>
-      </c>
-      <c r="E17" s="15">
-        <v>2464.9</v>
-      </c>
-      <c r="F17" s="15">
-        <v>2509.9</v>
-      </c>
-      <c r="G17" s="15">
-        <v>2571.6999999999998</v>
-      </c>
-      <c r="H17" s="15">
-        <v>2694.4</v>
-      </c>
-      <c r="I17" s="15">
-        <v>2860.6</v>
-      </c>
-      <c r="J17" s="15">
-        <v>2956.4</v>
-      </c>
-      <c r="K17" s="15">
-        <v>3040.8</v>
-      </c>
-      <c r="L17" s="7">
-        <f t="shared" si="0"/>
-        <v>1.1302618618395377</v>
-      </c>
-      <c r="M17">
-        <f t="shared" si="1"/>
-        <v>1.0553331251782436</v>
-      </c>
-      <c r="N17" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="18" spans="2:15">
-      <c r="C18" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D18" s="15">
-        <f t="shared" ref="D18:K18" si="2">SUM(D4:D17)</f>
-        <v>32120.499999999993</v>
-      </c>
-      <c r="E18" s="15">
-        <f t="shared" si="2"/>
-        <v>32656.700000000004</v>
-      </c>
-      <c r="F18" s="15">
-        <f t="shared" si="2"/>
-        <v>33255.5</v>
-      </c>
-      <c r="G18" s="15">
-        <f t="shared" si="2"/>
-        <v>33905.199999999997</v>
-      </c>
-      <c r="H18" s="15">
-        <f t="shared" si="2"/>
-        <v>34558.9</v>
-      </c>
-      <c r="I18" s="15">
-        <f t="shared" si="2"/>
-        <v>35271.300000000003</v>
-      </c>
-      <c r="J18" s="15">
-        <f t="shared" si="2"/>
-        <v>36024.9</v>
-      </c>
-      <c r="K18" s="15">
-        <f t="shared" si="2"/>
-        <v>36799.800000000003</v>
-      </c>
-      <c r="L18" s="7">
-        <f>AVERAGE(L4:L17)</f>
-        <v>1.0710000803287956</v>
-      </c>
-    </row>
-    <row r="19" spans="2:15">
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="7"/>
-    </row>
-    <row r="20" spans="2:15">
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="7"/>
-    </row>
-    <row r="21" spans="2:15">
-      <c r="C21" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="D21" s="24">
-        <v>2017</v>
-      </c>
-      <c r="E21" s="24">
-        <v>2018</v>
-      </c>
-      <c r="F21" s="24">
-        <v>2019</v>
-      </c>
-      <c r="G21" s="24">
-        <v>2020</v>
-      </c>
-      <c r="H21" s="24">
-        <v>2021</v>
-      </c>
-      <c r="I21" s="24">
-        <v>2022</v>
-      </c>
-      <c r="J21" s="24">
-        <v>2023</v>
-      </c>
-      <c r="K21" s="24">
-        <v>2024</v>
-      </c>
-      <c r="L21" s="7"/>
-    </row>
-    <row r="22" spans="2:15">
-      <c r="L22" s="7"/>
-    </row>
-    <row r="23" spans="2:15">
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" s="25">
-        <v>307.39999999999998</v>
-      </c>
-      <c r="E23" s="25">
-        <v>310.89999999999998</v>
-      </c>
-      <c r="F23" s="25">
-        <v>314.89999999999998</v>
-      </c>
-      <c r="G23" s="25">
-        <v>319.60000000000002</v>
-      </c>
-      <c r="H23" s="25">
-        <v>323.8</v>
-      </c>
-      <c r="I23" s="25">
-        <v>329</v>
-      </c>
-      <c r="J23" s="25">
-        <v>334.6</v>
-      </c>
-      <c r="K23" s="25">
-        <v>339.2</v>
-      </c>
-      <c r="L23" s="7">
-        <f>K23/AVERAGE(D23:K23)</f>
-        <v>1.0520276033186013</v>
-      </c>
-      <c r="M23" s="7">
-        <f>L23/L4</f>
-        <v>1.0032662000739572</v>
-      </c>
-      <c r="N23" s="7">
-        <f>L23/$L$37</f>
-        <v>0.95910326123969891</v>
-      </c>
-    </row>
-    <row r="24" spans="2:15">
-      <c r="B24">
-        <v>2</v>
-      </c>
-      <c r="C24" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24" s="25">
-        <v>421.9</v>
-      </c>
-      <c r="E24" s="25">
-        <v>427.5</v>
-      </c>
-      <c r="F24" s="25">
-        <v>433.9</v>
-      </c>
-      <c r="G24" s="25">
-        <v>441.7</v>
-      </c>
-      <c r="H24" s="25">
-        <v>450</v>
-      </c>
-      <c r="I24" s="25">
-        <v>458.5</v>
-      </c>
-      <c r="J24" s="25">
-        <v>468.1</v>
-      </c>
-      <c r="K24" s="25">
-        <v>480.8</v>
-      </c>
-      <c r="L24" s="7">
-        <f t="shared" ref="L24:L36" si="3">K24/AVERAGE(D24:K24)</f>
-        <v>1.0736936132201875</v>
-      </c>
-      <c r="M24" s="7">
-        <f t="shared" ref="M24:M36" si="4">L24/L5</f>
-        <v>1.0014279029001554</v>
-      </c>
-      <c r="N24" s="7">
-        <f t="shared" ref="N24:N36" si="5">L24/$L$37</f>
-        <v>0.97885553835591999</v>
-      </c>
-    </row>
-    <row r="25" spans="2:15">
-      <c r="B25">
-        <v>3</v>
-      </c>
-      <c r="C25" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25" s="25">
-        <v>276</v>
-      </c>
-      <c r="E25" s="25">
-        <v>276.39999999999998</v>
-      </c>
-      <c r="F25" s="25">
-        <v>277.8</v>
-      </c>
-      <c r="G25" s="25">
-        <v>280.2</v>
-      </c>
-      <c r="H25" s="25">
-        <v>281.2</v>
-      </c>
-      <c r="I25" s="25">
-        <v>283.8</v>
-      </c>
-      <c r="J25" s="25">
-        <v>289.2</v>
-      </c>
-      <c r="K25" s="25">
-        <v>294.5</v>
-      </c>
-      <c r="L25" s="7">
-        <f t="shared" si="3"/>
-        <v>1.0428931875525651</v>
-      </c>
-      <c r="M25" s="7">
-        <f t="shared" si="4"/>
-        <v>0.98919235194106425</v>
-      </c>
-      <c r="N25" s="7">
-        <f t="shared" si="5"/>
-        <v>0.95077567751177317</v>
-      </c>
-    </row>
-    <row r="26" spans="2:15">
-      <c r="B26">
-        <v>4</v>
-      </c>
-      <c r="C26" t="s">
-        <v>31</v>
-      </c>
-      <c r="D26" s="25">
-        <v>169.6</v>
-      </c>
-      <c r="E26" s="25">
-        <v>171.7</v>
-      </c>
-      <c r="F26" s="25">
-        <v>174.4</v>
-      </c>
-      <c r="G26" s="25">
-        <v>177.4</v>
-      </c>
-      <c r="H26" s="25">
-        <v>180.5</v>
-      </c>
-      <c r="I26" s="25">
-        <v>185.1</v>
-      </c>
-      <c r="J26" s="25">
-        <v>191.6</v>
-      </c>
-      <c r="K26" s="25">
-        <v>195.8</v>
-      </c>
-      <c r="L26" s="7">
-        <f t="shared" si="3"/>
-        <v>1.0831892676854993</v>
-      </c>
-      <c r="M26" s="7">
-        <f t="shared" si="4"/>
-        <v>1.00577112802299</v>
-      </c>
-      <c r="N26" s="7">
-        <f t="shared" si="5"/>
-        <v>0.98751245300013368</v>
-      </c>
-    </row>
-    <row r="27" spans="2:15">
-      <c r="B27">
-        <v>5</v>
-      </c>
-      <c r="C27" t="s">
-        <v>32</v>
-      </c>
-      <c r="D27" s="25">
-        <v>264.2</v>
-      </c>
-      <c r="E27" s="25">
-        <v>267.60000000000002</v>
-      </c>
-      <c r="F27" s="25">
-        <v>270.7</v>
-      </c>
-      <c r="G27" s="25">
-        <v>274.89999999999998</v>
-      </c>
-      <c r="H27" s="25">
-        <v>278.3</v>
-      </c>
-      <c r="I27" s="25">
-        <v>283.2</v>
-      </c>
-      <c r="J27" s="25">
-        <v>288.89999999999998</v>
-      </c>
-      <c r="K27" s="25">
-        <v>295.60000000000002</v>
-      </c>
-      <c r="L27" s="7">
-        <f t="shared" si="3"/>
-        <v>1.063596293964199</v>
-      </c>
-      <c r="M27" s="7">
-        <f t="shared" si="4"/>
-        <v>0.99013164936867559</v>
-      </c>
-      <c r="N27" s="7">
-        <f t="shared" si="5"/>
-        <v>0.96965010325360146</v>
-      </c>
-    </row>
-    <row r="28" spans="2:15">
-      <c r="B28">
-        <v>6</v>
-      </c>
-      <c r="C28" t="s">
-        <v>33</v>
-      </c>
-      <c r="D28" s="25">
-        <v>134.1</v>
-      </c>
-      <c r="E28" s="25">
-        <v>135.6</v>
-      </c>
-      <c r="F28" s="25">
-        <v>136.4</v>
-      </c>
-      <c r="G28" s="25">
-        <v>144.19999999999999</v>
-      </c>
-      <c r="H28" s="25">
-        <v>146.9</v>
-      </c>
-      <c r="I28" s="25">
-        <v>150.6</v>
-      </c>
-      <c r="J28" s="25">
-        <v>156</v>
-      </c>
-      <c r="K28" s="25">
-        <v>161.30000000000001</v>
-      </c>
-      <c r="L28" s="7">
-        <f t="shared" si="3"/>
-        <v>1.1075444167882587</v>
-      </c>
-      <c r="M28" s="7">
-        <f t="shared" si="4"/>
-        <v>1.0371577185809977</v>
-      </c>
-      <c r="N28" s="7">
-        <f t="shared" si="5"/>
-        <v>1.0097163408627237</v>
-      </c>
-      <c r="O28" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="29" spans="2:15">
-      <c r="B29">
-        <v>7</v>
-      </c>
-      <c r="C29" t="s">
-        <v>34</v>
-      </c>
-      <c r="D29" s="25">
-        <v>590.20000000000005</v>
-      </c>
-      <c r="E29" s="25">
-        <v>600.20000000000005</v>
-      </c>
-      <c r="F29" s="25">
-        <v>612.20000000000005</v>
-      </c>
-      <c r="G29" s="25">
-        <v>626.1</v>
-      </c>
-      <c r="H29" s="25">
-        <v>644.79999999999995</v>
-      </c>
-      <c r="I29" s="25">
-        <v>661.1</v>
-      </c>
-      <c r="J29" s="25">
-        <v>678.2</v>
-      </c>
-      <c r="K29" s="25">
-        <v>696.5</v>
-      </c>
-      <c r="L29" s="7">
-        <f t="shared" si="3"/>
-        <v>1.0905603507329771</v>
-      </c>
-      <c r="M29" s="7">
-        <f t="shared" si="4"/>
-        <v>1.0127146298620673</v>
-      </c>
-      <c r="N29" s="7">
-        <f t="shared" si="5"/>
-        <v>0.99423245708310981</v>
-      </c>
-    </row>
-    <row r="30" spans="2:15">
-      <c r="B30">
-        <v>8</v>
-      </c>
-      <c r="C30" t="s">
-        <v>35</v>
-      </c>
-      <c r="D30" s="25">
-        <v>523.79999999999995</v>
-      </c>
-      <c r="E30" s="25">
-        <v>529.6</v>
-      </c>
-      <c r="F30" s="25">
-        <v>538.20000000000005</v>
-      </c>
-      <c r="G30" s="25">
-        <v>546.29999999999995</v>
-      </c>
-      <c r="H30" s="25">
-        <v>551.70000000000005</v>
-      </c>
-      <c r="I30" s="25">
-        <v>561.70000000000005</v>
-      </c>
-      <c r="J30" s="25">
-        <v>572.79999999999995</v>
-      </c>
-      <c r="K30" s="25">
-        <v>585.20000000000005</v>
-      </c>
-      <c r="L30" s="7">
-        <f t="shared" si="3"/>
-        <v>1.0617558342594062</v>
-      </c>
-      <c r="M30" s="7">
-        <f t="shared" si="4"/>
-        <v>0.98877510027927329</v>
-      </c>
-      <c r="N30" s="7">
-        <f t="shared" si="5"/>
-        <v>0.96797220915702198</v>
-      </c>
-    </row>
-    <row r="31" spans="2:15">
-      <c r="B31">
-        <v>9</v>
-      </c>
-      <c r="C31" t="s">
-        <v>36</v>
-      </c>
-      <c r="D31" s="25">
-        <v>142.1</v>
-      </c>
-      <c r="E31" s="25">
-        <v>143.80000000000001</v>
-      </c>
-      <c r="F31" s="25">
-        <v>145.1</v>
-      </c>
-      <c r="G31" s="25">
-        <v>179.6</v>
-      </c>
-      <c r="H31" s="25">
-        <v>182.8</v>
-      </c>
-      <c r="I31" s="25">
-        <v>189.5</v>
-      </c>
-      <c r="J31" s="25">
-        <v>195.7</v>
-      </c>
-      <c r="K31" s="25">
-        <v>201.6</v>
-      </c>
-      <c r="L31" s="7">
-        <f t="shared" si="3"/>
-        <v>1.1685263005361541</v>
-      </c>
-      <c r="M31" s="7">
-        <f t="shared" si="4"/>
-        <v>1.0805091110380687</v>
-      </c>
-      <c r="N31" s="7">
-        <f t="shared" si="5"/>
-        <v>1.0653117676316106</v>
-      </c>
-      <c r="O31" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="32" spans="2:15">
-      <c r="B32">
-        <v>10</v>
-      </c>
-      <c r="C32" t="s">
-        <v>37</v>
-      </c>
-      <c r="D32" s="25">
-        <v>87.5</v>
-      </c>
-      <c r="E32" s="25">
-        <v>88.2</v>
-      </c>
-      <c r="F32" s="25">
-        <v>89</v>
-      </c>
-      <c r="G32" s="25">
-        <v>90.4</v>
-      </c>
-      <c r="H32" s="25">
-        <v>91.3</v>
-      </c>
-      <c r="I32" s="25">
-        <v>93.4</v>
-      </c>
-      <c r="J32" s="25">
-        <v>96.2</v>
-      </c>
-      <c r="K32" s="25">
-        <v>99.3</v>
-      </c>
-      <c r="L32" s="7">
-        <f t="shared" si="3"/>
-        <v>1.0803753569971439</v>
-      </c>
-      <c r="M32" s="7">
-        <f t="shared" si="4"/>
-        <v>1.0114186858934013</v>
-      </c>
-      <c r="N32" s="7">
-        <f t="shared" si="5"/>
-        <v>0.98494709168306793</v>
-      </c>
-    </row>
-    <row r="33" spans="2:17">
-      <c r="B33">
-        <v>11</v>
-      </c>
-      <c r="C33" t="s">
-        <v>39</v>
-      </c>
-      <c r="D33" s="25">
         <v>0</v>
       </c>
-      <c r="E33" s="25">
-        <v>47.7</v>
-      </c>
-      <c r="F33" s="25">
-        <v>48.2</v>
-      </c>
-      <c r="G33" s="25">
-        <v>48.7</v>
-      </c>
-      <c r="H33" s="25">
-        <v>51.4</v>
-      </c>
-      <c r="I33" s="25">
-        <v>52.7</v>
-      </c>
-      <c r="J33" s="25">
-        <v>54.1</v>
-      </c>
-      <c r="K33" s="25">
-        <v>56.2</v>
-      </c>
-      <c r="L33" s="7">
-        <f t="shared" si="3"/>
-        <v>1.252367688022284</v>
-      </c>
-      <c r="M33" s="7">
-        <f t="shared" si="4"/>
-        <v>1.2051289517068422</v>
-      </c>
-      <c r="N33" s="7">
-        <f t="shared" si="5"/>
-        <v>1.1417475454678085</v>
-      </c>
-      <c r="O33" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="34" spans="2:17">
-      <c r="B34">
-        <v>12</v>
-      </c>
-      <c r="C34" t="s">
-        <v>100</v>
-      </c>
-      <c r="D34" s="15">
-        <v>274.5</v>
-      </c>
-      <c r="E34" s="15">
-        <v>278.5</v>
-      </c>
-      <c r="F34" s="15">
-        <v>283.8</v>
-      </c>
-      <c r="G34" s="15">
-        <v>288.8</v>
-      </c>
-      <c r="H34" s="15">
-        <v>293.5</v>
-      </c>
-      <c r="I34" s="15">
-        <v>299.10000000000002</v>
-      </c>
-      <c r="J34" s="15">
-        <v>314.5</v>
-      </c>
-      <c r="K34" s="15">
-        <v>321.8</v>
-      </c>
-      <c r="L34" s="7">
-        <f>K34/AVERAGE(D34:K34)</f>
-        <v>1.0933956253981738</v>
-      </c>
-      <c r="M34" s="7">
-        <f t="shared" si="4"/>
-        <v>1.0221391549814363</v>
-      </c>
-      <c r="N34" s="7">
-        <f t="shared" si="5"/>
-        <v>0.99681729532245111</v>
-      </c>
-      <c r="O34" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="35" spans="2:17">
-      <c r="B35">
-        <v>13</v>
-      </c>
-      <c r="C35" t="s">
-        <v>40</v>
-      </c>
-      <c r="D35" s="25">
-        <v>139.30000000000001</v>
-      </c>
-      <c r="E35" s="25">
-        <v>140.19999999999999</v>
-      </c>
-      <c r="F35" s="25">
-        <v>141.69999999999999</v>
-      </c>
-      <c r="G35" s="25">
-        <v>143.69999999999999</v>
-      </c>
-      <c r="H35" s="25">
-        <v>145</v>
-      </c>
-      <c r="I35" s="25">
-        <v>146.69999999999999</v>
-      </c>
-      <c r="J35" s="25">
-        <v>149.9</v>
-      </c>
-      <c r="K35" s="25">
-        <v>153.1</v>
-      </c>
-      <c r="L35" s="7">
-        <f t="shared" si="3"/>
-        <v>1.0562262849258366</v>
-      </c>
-      <c r="M35" s="7">
-        <f t="shared" si="4"/>
-        <v>0.99604081117126197</v>
-      </c>
-      <c r="N35" s="7">
-        <f t="shared" si="5"/>
-        <v>0.96293107831379798</v>
-      </c>
-    </row>
-    <row r="36" spans="2:17">
-      <c r="B36">
-        <v>14</v>
-      </c>
-      <c r="C36" t="s">
-        <v>41</v>
-      </c>
-      <c r="D36" s="15">
-        <v>2424.1</v>
-      </c>
-      <c r="E36" s="15">
-        <v>2464.9</v>
-      </c>
-      <c r="F36" s="15">
-        <v>2509.9</v>
-      </c>
-      <c r="G36" s="15">
-        <v>2571.6999999999998</v>
-      </c>
-      <c r="H36" s="15">
-        <v>2694.4</v>
-      </c>
-      <c r="I36" s="15">
-        <v>2860.6</v>
-      </c>
-      <c r="J36" s="15">
-        <v>2956.4</v>
-      </c>
-      <c r="K36" s="15">
-        <v>3040.8</v>
-      </c>
-      <c r="L36" s="7">
-        <f t="shared" si="3"/>
-        <v>1.1302618618395377</v>
-      </c>
-      <c r="M36" s="7">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="N36" s="7">
-        <f t="shared" si="5"/>
-        <v>1.0304271811172803</v>
-      </c>
-      <c r="O36" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="37" spans="2:17">
-      <c r="L37" s="7">
-        <f>AVERAGE(L23:L36)</f>
-        <v>1.0968866918029161</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="38" spans="2:17">
-      <c r="C38" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D38" s="7">
-        <f>D23/D4</f>
-        <v>0.16913342503438789</v>
-      </c>
-      <c r="E38" s="7">
-        <f t="shared" ref="E38:L38" si="6">E23/E4</f>
-        <v>0.16875644574716386</v>
-      </c>
-      <c r="F38" s="7">
-        <f t="shared" si="6"/>
-        <v>0.1684137340892074</v>
-      </c>
-      <c r="G38" s="7">
-        <f t="shared" si="6"/>
-        <v>0.16836116525312123</v>
-      </c>
-      <c r="H38" s="7">
-        <f t="shared" si="6"/>
-        <v>0.168321463845714</v>
-      </c>
-      <c r="I38" s="7">
-        <f t="shared" si="6"/>
-        <v>0.16884783166538364</v>
-      </c>
-      <c r="J38" s="7">
-        <f t="shared" si="6"/>
-        <v>0.16931484667543772</v>
-      </c>
-      <c r="K38" s="7">
-        <f t="shared" si="6"/>
-        <v>0.16937134867928297</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="39" spans="2:17">
-      <c r="C39" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D39" s="7">
-        <f t="shared" ref="D39:K39" si="7">D24/D5</f>
-        <v>0.14241350210970463</v>
-      </c>
-      <c r="E39" s="7">
-        <f t="shared" si="7"/>
-        <v>0.14194640900488098</v>
-      </c>
-      <c r="F39" s="7">
-        <f t="shared" si="7"/>
-        <v>0.14147836577651698</v>
-      </c>
-      <c r="G39" s="7">
-        <f t="shared" si="7"/>
-        <v>0.14122198420564633</v>
-      </c>
-      <c r="H39" s="7">
-        <f t="shared" si="7"/>
-        <v>0.14114990119506918</v>
-      </c>
-      <c r="I39" s="7">
-        <f t="shared" si="7"/>
-        <v>0.1409251575226679</v>
-      </c>
-      <c r="J39" s="7">
-        <f t="shared" si="7"/>
-        <v>0.14087940530291632</v>
-      </c>
-      <c r="K39" s="7">
-        <f t="shared" si="7"/>
-        <v>0.14164506245580957</v>
-      </c>
-    </row>
-    <row r="40" spans="2:17">
-      <c r="C40" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D40" s="7">
-        <f t="shared" ref="D40:K40" si="8">D25/D6</f>
-        <v>0.14971521562245729</v>
-      </c>
-      <c r="E40" s="7">
-        <f t="shared" si="8"/>
-        <v>0.14779168003422091</v>
-      </c>
-      <c r="F40" s="7">
-        <f t="shared" si="8"/>
-        <v>0.14661177960734642</v>
-      </c>
-      <c r="G40" s="7">
-        <f t="shared" si="8"/>
-        <v>0.14564166536722281</v>
-      </c>
-      <c r="H40" s="7">
-        <f t="shared" si="8"/>
-        <v>0.14441990652765652</v>
-      </c>
-      <c r="I40" s="7">
-        <f t="shared" si="8"/>
-        <v>0.14356535815459329</v>
-      </c>
-      <c r="J40" s="7">
-        <f t="shared" si="8"/>
-        <v>0.14390207493655768</v>
-      </c>
-      <c r="K40" s="7">
-        <f t="shared" si="8"/>
-        <v>0.1440802348336595</v>
-      </c>
-    </row>
-    <row r="41" spans="2:17">
-      <c r="C41" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D41" s="7">
-        <f t="shared" ref="D41:K41" si="9">D26/D7</f>
-        <v>0.13036126056879324</v>
-      </c>
-      <c r="E41" s="7">
-        <f t="shared" si="9"/>
-        <v>0.12958490566037734</v>
-      </c>
-      <c r="F41" s="7">
-        <f t="shared" si="9"/>
-        <v>0.12895593019816623</v>
-      </c>
-      <c r="G41" s="7">
-        <f t="shared" si="9"/>
-        <v>0.12835540120107083</v>
-      </c>
-      <c r="H41" s="7">
-        <f t="shared" si="9"/>
-        <v>0.12796880538816022</v>
-      </c>
-      <c r="I41" s="7">
-        <f t="shared" si="9"/>
-        <v>0.12823888042122764</v>
-      </c>
-      <c r="J41" s="7">
-        <f t="shared" si="9"/>
-        <v>0.1298542866824805</v>
-      </c>
-      <c r="K41" s="7">
-        <f t="shared" si="9"/>
-        <v>0.12989253018442351</v>
-      </c>
-    </row>
-    <row r="42" spans="2:17">
-      <c r="C42" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D42" s="7">
-        <f t="shared" ref="D42:K42" si="10">D27/D8</f>
-        <v>8.5534835534835527E-2</v>
-      </c>
-      <c r="E42" s="7">
-        <f t="shared" si="10"/>
-        <v>8.4995553296912718E-2</v>
-      </c>
-      <c r="F42" s="7">
-        <f t="shared" si="10"/>
-        <v>8.4248856244748066E-2</v>
-      </c>
-      <c r="G42" s="7">
-        <f t="shared" si="10"/>
-        <v>8.3800756005365185E-2</v>
-      </c>
-      <c r="H42" s="7">
-        <f t="shared" si="10"/>
-        <v>8.3438268273670332E-2</v>
-      </c>
-      <c r="I42" s="7">
-        <f t="shared" si="10"/>
-        <v>8.3091277176304892E-2</v>
-      </c>
-      <c r="J42" s="7">
-        <f t="shared" si="10"/>
-        <v>8.2962409901501874E-2</v>
-      </c>
-      <c r="K42" s="7">
-        <f t="shared" si="10"/>
-        <v>8.3019715778239633E-2</v>
-      </c>
-    </row>
-    <row r="43" spans="2:17">
-      <c r="C43" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D43" s="7">
-        <f t="shared" ref="D43:K43" si="11">D28/D9</f>
-        <v>0.14223589308442935</v>
-      </c>
-      <c r="E43" s="7">
-        <f t="shared" si="11"/>
-        <v>0.14154488517745303</v>
-      </c>
-      <c r="F43" s="7">
-        <f t="shared" si="11"/>
-        <v>0.13925472179683512</v>
-      </c>
-      <c r="G43" s="7">
-        <f t="shared" si="11"/>
-        <v>0.14461939624912243</v>
-      </c>
-      <c r="H43" s="7">
-        <f t="shared" si="11"/>
-        <v>0.14492896606156275</v>
-      </c>
-      <c r="I43" s="7">
-        <f t="shared" si="11"/>
-        <v>0.14566205629171097</v>
-      </c>
-      <c r="J43" s="7">
-        <f t="shared" si="11"/>
-        <v>0.14779725248697301</v>
-      </c>
-      <c r="K43" s="7">
-        <f t="shared" si="11"/>
-        <v>0.15000464986515394</v>
-      </c>
-    </row>
-    <row r="44" spans="2:17">
-      <c r="C44" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D44" s="7">
-        <f t="shared" ref="D44:K44" si="12">D29/D10</f>
-        <v>0.222515457698688</v>
-      </c>
-      <c r="E44" s="7">
-        <f t="shared" si="12"/>
-        <v>0.22232923396058679</v>
-      </c>
-      <c r="F44" s="7">
-        <f t="shared" si="12"/>
-        <v>0.22238366813178831</v>
-      </c>
-      <c r="G44" s="7">
-        <f t="shared" si="12"/>
-        <v>0.22274797210758501</v>
-      </c>
-      <c r="H44" s="7">
-        <f t="shared" si="12"/>
-        <v>0.22486486486486484</v>
-      </c>
-      <c r="I44" s="7">
-        <f t="shared" si="12"/>
-        <v>0.22554672307324897</v>
-      </c>
-      <c r="J44" s="7">
-        <f t="shared" si="12"/>
-        <v>0.22625521267723103</v>
-      </c>
-      <c r="K44" s="7">
-        <f t="shared" si="12"/>
-        <v>0.22716154071948078</v>
-      </c>
-    </row>
-    <row r="45" spans="2:17">
-      <c r="C45" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D45" s="7">
-        <f t="shared" ref="D45:K45" si="13">D30/D11</f>
-        <v>0.14344004162444887</v>
-      </c>
-      <c r="E45" s="7">
-        <f t="shared" si="13"/>
-        <v>0.14236176446869708</v>
-      </c>
-      <c r="F45" s="7">
-        <f t="shared" si="13"/>
-        <v>0.14167258943378347</v>
-      </c>
-      <c r="G45" s="7">
-        <f t="shared" si="13"/>
-        <v>0.1408933821633053</v>
-      </c>
-      <c r="H45" s="7">
-        <f t="shared" si="13"/>
-        <v>0.13975226081009198</v>
-      </c>
-      <c r="I45" s="7">
-        <f t="shared" si="13"/>
-        <v>0.13933470592612807</v>
-      </c>
-      <c r="J45" s="7">
-        <f t="shared" si="13"/>
-        <v>0.13908989364285368</v>
-      </c>
-      <c r="K45" s="7">
-        <f t="shared" si="13"/>
-        <v>0.13905191873589165</v>
-      </c>
-    </row>
-    <row r="46" spans="2:17">
-      <c r="C46" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D46" s="7">
-        <f t="shared" ref="D46:K46" si="14">D31/D12</f>
-        <v>5.7710270884944966E-2</v>
-      </c>
-      <c r="E46" s="7">
-        <f t="shared" si="14"/>
-        <v>5.7195131652215424E-2</v>
-      </c>
-      <c r="F46" s="7">
-        <f t="shared" si="14"/>
-        <v>5.6461340908206543E-2</v>
-      </c>
-      <c r="G46" s="7">
-        <f t="shared" si="14"/>
-        <v>6.8312350233920349E-2</v>
-      </c>
-      <c r="H46" s="7">
-        <f t="shared" si="14"/>
-        <v>6.8188600417785739E-2</v>
-      </c>
-      <c r="I46" s="7">
-        <f t="shared" si="14"/>
-        <v>6.9079906678331873E-2</v>
-      </c>
-      <c r="J46" s="7">
-        <f t="shared" si="14"/>
-        <v>6.9730981649741661E-2</v>
-      </c>
-      <c r="K46" s="7">
-        <f t="shared" si="14"/>
-        <v>7.0070557158249627E-2</v>
-      </c>
-    </row>
-    <row r="47" spans="2:17">
-      <c r="C47" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D47" s="7">
-        <f t="shared" ref="D47:K47" si="15">D32/D13</f>
-        <v>0.10895280786950566</v>
-      </c>
-      <c r="E47" s="7">
-        <f t="shared" si="15"/>
-        <v>0.10810148302488051</v>
-      </c>
-      <c r="F47" s="7">
-        <f t="shared" si="15"/>
-        <v>0.10724183636582721</v>
-      </c>
-      <c r="G47" s="7">
-        <f t="shared" si="15"/>
-        <v>0.10681791326952618</v>
-      </c>
-      <c r="H47" s="7">
-        <f t="shared" si="15"/>
-        <v>0.10605180624927402</v>
-      </c>
-      <c r="I47" s="7">
-        <f t="shared" si="15"/>
-        <v>0.10630548600045528</v>
-      </c>
-      <c r="J47" s="7">
-        <f t="shared" si="15"/>
-        <v>0.10729422261878206</v>
-      </c>
-      <c r="K47" s="7">
-        <f t="shared" si="15"/>
-        <v>0.10864332603938731</v>
-      </c>
-    </row>
-    <row r="48" spans="2:17">
-      <c r="C48" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D48" s="7">
-        <f>D33/D14</f>
-        <v>0</v>
-      </c>
-      <c r="E48" s="7">
-        <f t="shared" ref="E48:K48" si="16">E33/E14</f>
-        <v>1.6671326716063192E-2</v>
-      </c>
-      <c r="F48" s="7">
-        <f t="shared" si="16"/>
-        <v>1.6629291012592723E-2</v>
-      </c>
-      <c r="G48" s="7">
-        <f t="shared" si="16"/>
-        <v>1.655392773377749E-2</v>
-      </c>
-      <c r="H48" s="7">
-        <f t="shared" si="16"/>
-        <v>1.7272085755569742E-2</v>
-      </c>
-      <c r="I48" s="7">
-        <f t="shared" si="16"/>
-        <v>1.7916029236783954E-2</v>
-      </c>
-      <c r="J48" s="7">
-        <f t="shared" si="16"/>
-        <v>1.8073094140442305E-2</v>
-      </c>
-      <c r="K48" s="7">
-        <f t="shared" si="16"/>
-        <v>1.8415361426043646E-2</v>
-      </c>
-    </row>
-    <row r="49" spans="3:11">
-      <c r="C49" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="D49" s="7">
-        <f t="shared" ref="D49:K49" si="17">D34/D15</f>
-        <v>7.7002917414721719E-2</v>
-      </c>
-      <c r="E49" s="7">
-        <f t="shared" si="17"/>
-        <v>7.6929451411524227E-2</v>
-      </c>
-      <c r="F49" s="7">
-        <f t="shared" si="17"/>
-        <v>7.7050471044986829E-2</v>
-      </c>
-      <c r="G49" s="7">
-        <f t="shared" si="17"/>
-        <v>7.697228144989339E-2</v>
-      </c>
-      <c r="H49" s="7">
-        <f t="shared" si="17"/>
-        <v>7.683246073298429E-2</v>
-      </c>
-      <c r="I49" s="7">
-        <f t="shared" si="17"/>
-        <v>7.6763165999384056E-2</v>
-      </c>
-      <c r="J49" s="7">
-        <f t="shared" si="17"/>
-        <v>7.9093629756306114E-2</v>
-      </c>
-      <c r="K49" s="7">
-        <f t="shared" si="17"/>
-        <v>7.9231810907300262E-2</v>
-      </c>
-    </row>
-    <row r="50" spans="3:11">
-      <c r="C50" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D50" s="7">
-        <f t="shared" ref="D50:K51" si="18">D35/D16</f>
-        <v>7.8403782293015145E-2</v>
-      </c>
-      <c r="E50" s="7">
-        <f t="shared" si="18"/>
-        <v>7.7673130193905815E-2</v>
-      </c>
-      <c r="F50" s="7">
-        <f t="shared" si="18"/>
-        <v>7.7191262188810797E-2</v>
-      </c>
-      <c r="G50" s="7">
-        <f t="shared" si="18"/>
-        <v>7.6989016876506819E-2</v>
-      </c>
-      <c r="H50" s="7">
-        <f t="shared" si="18"/>
-        <v>7.6585855384777898E-2</v>
-      </c>
-      <c r="I50" s="7">
-        <f t="shared" si="18"/>
-        <v>7.6239476145930768E-2</v>
-      </c>
-      <c r="J50" s="7">
-        <f t="shared" si="18"/>
-        <v>7.6553802155150411E-2</v>
-      </c>
-      <c r="K50" s="7">
-        <f t="shared" si="18"/>
-        <v>7.6718781318901585E-2</v>
-      </c>
-    </row>
-    <row r="51" spans="3:11">
-      <c r="C51" t="s">
-        <v>41</v>
+      <c r="C15" s="21">
+        <v>27.8</v>
+      </c>
+      <c r="D15" s="21">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E15" s="21">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="B23:M36">
-    <sortCondition ref="B23"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -18475,4 +16893,1858 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B3:Q51"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="16.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:14">
+      <c r="C3" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" s="24">
+        <v>2017</v>
+      </c>
+      <c r="E3" s="24">
+        <v>2018</v>
+      </c>
+      <c r="F3" s="24">
+        <v>2019</v>
+      </c>
+      <c r="G3" s="24">
+        <v>2020</v>
+      </c>
+      <c r="H3" s="24">
+        <v>2021</v>
+      </c>
+      <c r="I3" s="24">
+        <v>2022</v>
+      </c>
+      <c r="J3" s="24">
+        <v>2023</v>
+      </c>
+      <c r="K3" s="24">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="15">
+        <v>1817.5</v>
+      </c>
+      <c r="E4" s="15">
+        <v>1842.3</v>
+      </c>
+      <c r="F4" s="15">
+        <v>1869.8</v>
+      </c>
+      <c r="G4" s="15">
+        <v>1898.3</v>
+      </c>
+      <c r="H4" s="15">
+        <v>1923.7</v>
+      </c>
+      <c r="I4" s="15">
+        <v>1948.5</v>
+      </c>
+      <c r="J4" s="15">
+        <v>1976.2</v>
+      </c>
+      <c r="K4" s="15">
+        <v>2002.7</v>
+      </c>
+      <c r="L4" s="7">
+        <f>K4/AVERAGE(D4:K4)</f>
+        <v>1.048602657241966</v>
+      </c>
+      <c r="M4">
+        <f>L4/$L$18</f>
+        <v>0.97908737497017406</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14">
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="15">
+        <v>2962.5</v>
+      </c>
+      <c r="E5" s="15">
+        <v>3011.7</v>
+      </c>
+      <c r="F5" s="15">
+        <v>3066.9</v>
+      </c>
+      <c r="G5" s="15">
+        <v>3127.7</v>
+      </c>
+      <c r="H5" s="15">
+        <v>3188.1</v>
+      </c>
+      <c r="I5" s="15">
+        <v>3253.5</v>
+      </c>
+      <c r="J5" s="15">
+        <v>3322.7</v>
+      </c>
+      <c r="K5" s="15">
+        <v>3394.4</v>
+      </c>
+      <c r="L5" s="7">
+        <f t="shared" ref="L5:L17" si="0">K5/AVERAGE(D5:K5)</f>
+        <v>1.0721626690356332</v>
+      </c>
+      <c r="M5">
+        <f t="shared" ref="M5:M17" si="1">L5/$L$18</f>
+        <v>1.0010855169184307</v>
+      </c>
+      <c r="N5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14">
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="15">
+        <v>1843.5</v>
+      </c>
+      <c r="E6" s="15">
+        <v>1870.2</v>
+      </c>
+      <c r="F6" s="15">
+        <v>1894.8</v>
+      </c>
+      <c r="G6" s="15">
+        <v>1923.9</v>
+      </c>
+      <c r="H6" s="15">
+        <v>1947.1</v>
+      </c>
+      <c r="I6" s="15">
+        <v>1976.8</v>
+      </c>
+      <c r="J6" s="15">
+        <v>2009.7</v>
+      </c>
+      <c r="K6" s="15">
+        <v>2044</v>
+      </c>
+      <c r="L6" s="7">
+        <f t="shared" si="0"/>
+        <v>1.0542875564152161</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="1"/>
+        <v>0.98439540367872924</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14">
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="15">
+        <v>1301</v>
+      </c>
+      <c r="E7" s="15">
+        <v>1325</v>
+      </c>
+      <c r="F7" s="15">
+        <v>1352.4</v>
+      </c>
+      <c r="G7" s="15">
+        <v>1382.1</v>
+      </c>
+      <c r="H7" s="15">
+        <v>1410.5</v>
+      </c>
+      <c r="I7" s="15">
+        <v>1443.4</v>
+      </c>
+      <c r="J7" s="15">
+        <v>1475.5</v>
+      </c>
+      <c r="K7" s="15">
+        <v>1507.4</v>
+      </c>
+      <c r="L7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.0769739133541123</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="1"/>
+        <v>1.0055778081953857</v>
+      </c>
+      <c r="N7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14">
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="15">
+        <v>3088.8</v>
+      </c>
+      <c r="E8" s="15">
+        <v>3148.4</v>
+      </c>
+      <c r="F8" s="15">
+        <v>3213.1</v>
+      </c>
+      <c r="G8" s="15">
+        <v>3280.4</v>
+      </c>
+      <c r="H8" s="15">
+        <v>3335.4</v>
+      </c>
+      <c r="I8" s="15">
+        <v>3408.3</v>
+      </c>
+      <c r="J8" s="15">
+        <v>3482.3</v>
+      </c>
+      <c r="K8" s="15">
+        <v>3560.6</v>
+      </c>
+      <c r="L8" s="7">
+        <f t="shared" si="0"/>
+        <v>1.074196845078496</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="1"/>
+        <v>1.0029848408122612</v>
+      </c>
+      <c r="N8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14">
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="15">
+        <v>942.8</v>
+      </c>
+      <c r="E9" s="15">
+        <v>958</v>
+      </c>
+      <c r="F9" s="15">
+        <v>979.5</v>
+      </c>
+      <c r="G9" s="15">
+        <v>997.1</v>
+      </c>
+      <c r="H9" s="15">
+        <v>1013.6</v>
+      </c>
+      <c r="I9" s="15">
+        <v>1033.9000000000001</v>
+      </c>
+      <c r="J9" s="15">
+        <v>1055.5</v>
+      </c>
+      <c r="K9" s="15">
+        <v>1075.3</v>
+      </c>
+      <c r="L9" s="7">
+        <f t="shared" si="0"/>
+        <v>1.0678649900070758</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="1"/>
+        <v>0.99707274501720178</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14">
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="15">
+        <v>2652.4</v>
+      </c>
+      <c r="E10" s="15">
+        <v>2699.6</v>
+      </c>
+      <c r="F10" s="15">
+        <v>2752.9</v>
+      </c>
+      <c r="G10" s="15">
+        <v>2810.8</v>
+      </c>
+      <c r="H10" s="15">
+        <v>2867.5</v>
+      </c>
+      <c r="I10" s="15">
+        <v>2931.1</v>
+      </c>
+      <c r="J10" s="15">
+        <v>2997.5</v>
+      </c>
+      <c r="K10" s="15">
+        <v>3066.1</v>
+      </c>
+      <c r="L10" s="7">
+        <f t="shared" si="0"/>
+        <v>1.0768683680233913</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="1"/>
+        <v>1.0054792598080797</v>
+      </c>
+      <c r="N10" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14">
+      <c r="B11">
+        <v>8</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="15">
+        <v>3651.7</v>
+      </c>
+      <c r="E11" s="15">
+        <v>3720.1</v>
+      </c>
+      <c r="F11" s="15">
+        <v>3798.9</v>
+      </c>
+      <c r="G11" s="15">
+        <v>3877.4</v>
+      </c>
+      <c r="H11" s="15">
+        <v>3947.7</v>
+      </c>
+      <c r="I11" s="15">
+        <v>4031.3</v>
+      </c>
+      <c r="J11" s="15">
+        <v>4118.2</v>
+      </c>
+      <c r="K11" s="15">
+        <v>4208.5</v>
+      </c>
+      <c r="L11" s="7">
+        <f t="shared" si="0"/>
+        <v>1.0738092352442128</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="1"/>
+        <v>1.0026229268951641</v>
+      </c>
+      <c r="N11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14">
+      <c r="B12">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="15">
+        <v>2462.3000000000002</v>
+      </c>
+      <c r="E12" s="15">
+        <v>2514.1999999999998</v>
+      </c>
+      <c r="F12" s="15">
+        <v>2569.9</v>
+      </c>
+      <c r="G12" s="15">
+        <v>2629.1</v>
+      </c>
+      <c r="H12" s="15">
+        <v>2680.8</v>
+      </c>
+      <c r="I12" s="15">
+        <v>2743.2</v>
+      </c>
+      <c r="J12" s="15">
+        <v>2806.5</v>
+      </c>
+      <c r="K12" s="15">
+        <v>2877.1</v>
+      </c>
+      <c r="L12" s="7">
+        <f t="shared" si="0"/>
+        <v>1.0814589979843163</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="1"/>
+        <v>1.0097655619711157</v>
+      </c>
+      <c r="N12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14">
+      <c r="B13">
+        <v>10</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="15">
+        <v>803.1</v>
+      </c>
+      <c r="E13" s="15">
+        <v>815.9</v>
+      </c>
+      <c r="F13" s="15">
+        <v>829.9</v>
+      </c>
+      <c r="G13" s="15">
+        <v>846.3</v>
+      </c>
+      <c r="H13" s="15">
+        <v>860.9</v>
+      </c>
+      <c r="I13" s="15">
+        <v>878.6</v>
+      </c>
+      <c r="J13" s="15">
+        <v>896.6</v>
+      </c>
+      <c r="K13" s="15">
+        <v>914</v>
+      </c>
+      <c r="L13" s="7">
+        <f t="shared" si="0"/>
+        <v>1.0681781660409331</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="1"/>
+        <v>0.99736515959270877</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14">
+      <c r="B14">
+        <v>11</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="15">
+        <v>2829.3</v>
+      </c>
+      <c r="E14" s="15">
+        <v>2861.2</v>
+      </c>
+      <c r="F14" s="15">
+        <v>2898.5</v>
+      </c>
+      <c r="G14" s="15">
+        <v>2941.9</v>
+      </c>
+      <c r="H14" s="15">
+        <v>2975.9</v>
+      </c>
+      <c r="I14" s="15">
+        <v>2941.5</v>
+      </c>
+      <c r="J14" s="15">
+        <v>2993.4</v>
+      </c>
+      <c r="K14" s="15">
+        <v>3051.8</v>
+      </c>
+      <c r="L14" s="7">
+        <f t="shared" si="0"/>
+        <v>1.0391980760635922</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="1"/>
+        <v>0.97030625408035431</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14">
+      <c r="B15">
+        <v>12</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="15">
+        <v>3564.8</v>
+      </c>
+      <c r="E15" s="15">
+        <v>3620.2</v>
+      </c>
+      <c r="F15" s="15">
+        <v>3683.3</v>
+      </c>
+      <c r="G15" s="15">
+        <v>3752</v>
+      </c>
+      <c r="H15" s="15">
+        <v>3820</v>
+      </c>
+      <c r="I15" s="15">
+        <v>3896.4</v>
+      </c>
+      <c r="J15" s="15">
+        <v>3976.3</v>
+      </c>
+      <c r="K15" s="15">
+        <v>4061.5</v>
+      </c>
+      <c r="L15" s="7">
+        <f t="shared" si="0"/>
+        <v>1.0697130816968181</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="1"/>
+        <v>0.99879832069519325</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14">
+      <c r="B16">
+        <v>13</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="15">
+        <v>1776.7</v>
+      </c>
+      <c r="E16" s="15">
+        <v>1805</v>
+      </c>
+      <c r="F16" s="15">
+        <v>1835.7</v>
+      </c>
+      <c r="G16" s="15">
+        <v>1866.5</v>
+      </c>
+      <c r="H16" s="15">
+        <v>1893.3</v>
+      </c>
+      <c r="I16" s="15">
+        <v>1924.2</v>
+      </c>
+      <c r="J16" s="15">
+        <v>1958.1</v>
+      </c>
+      <c r="K16" s="15">
+        <v>1995.6</v>
+      </c>
+      <c r="L16" s="7">
+        <f t="shared" si="0"/>
+        <v>1.0604247065778374</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="1"/>
+        <v>0.99012570218695828</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15">
+      <c r="B17">
+        <v>14</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="15">
+        <v>2424.1</v>
+      </c>
+      <c r="E17" s="15">
+        <v>2464.9</v>
+      </c>
+      <c r="F17" s="15">
+        <v>2509.9</v>
+      </c>
+      <c r="G17" s="15">
+        <v>2571.6999999999998</v>
+      </c>
+      <c r="H17" s="15">
+        <v>2694.4</v>
+      </c>
+      <c r="I17" s="15">
+        <v>2860.6</v>
+      </c>
+      <c r="J17" s="15">
+        <v>2956.4</v>
+      </c>
+      <c r="K17" s="15">
+        <v>3040.8</v>
+      </c>
+      <c r="L17" s="7">
+        <f t="shared" si="0"/>
+        <v>1.1302618618395377</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="1"/>
+        <v>1.0553331251782436</v>
+      </c>
+      <c r="N17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15">
+      <c r="C18" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="15">
+        <f t="shared" ref="D18:K18" si="2">SUM(D4:D17)</f>
+        <v>32120.499999999993</v>
+      </c>
+      <c r="E18" s="15">
+        <f t="shared" si="2"/>
+        <v>32656.700000000004</v>
+      </c>
+      <c r="F18" s="15">
+        <f t="shared" si="2"/>
+        <v>33255.5</v>
+      </c>
+      <c r="G18" s="15">
+        <f t="shared" si="2"/>
+        <v>33905.199999999997</v>
+      </c>
+      <c r="H18" s="15">
+        <f t="shared" si="2"/>
+        <v>34558.9</v>
+      </c>
+      <c r="I18" s="15">
+        <f t="shared" si="2"/>
+        <v>35271.300000000003</v>
+      </c>
+      <c r="J18" s="15">
+        <f t="shared" si="2"/>
+        <v>36024.9</v>
+      </c>
+      <c r="K18" s="15">
+        <f t="shared" si="2"/>
+        <v>36799.800000000003</v>
+      </c>
+      <c r="L18" s="7">
+        <f>AVERAGE(L4:L17)</f>
+        <v>1.0710000803287956</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15">
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="7"/>
+    </row>
+    <row r="20" spans="2:15">
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="7"/>
+    </row>
+    <row r="21" spans="2:15">
+      <c r="L21" s="7"/>
+    </row>
+    <row r="22" spans="2:15">
+      <c r="C22" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" s="24">
+        <v>2017</v>
+      </c>
+      <c r="E22" s="24">
+        <v>2018</v>
+      </c>
+      <c r="F22" s="24">
+        <v>2019</v>
+      </c>
+      <c r="G22" s="24">
+        <v>2020</v>
+      </c>
+      <c r="H22" s="24">
+        <v>2021</v>
+      </c>
+      <c r="I22" s="24">
+        <v>2022</v>
+      </c>
+      <c r="J22" s="24">
+        <v>2023</v>
+      </c>
+      <c r="K22" s="24">
+        <v>2024</v>
+      </c>
+      <c r="L22" s="7"/>
+    </row>
+    <row r="23" spans="2:15">
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="25">
+        <v>307.39999999999998</v>
+      </c>
+      <c r="E23" s="25">
+        <v>310.89999999999998</v>
+      </c>
+      <c r="F23" s="25">
+        <v>314.89999999999998</v>
+      </c>
+      <c r="G23" s="25">
+        <v>319.60000000000002</v>
+      </c>
+      <c r="H23" s="25">
+        <v>323.8</v>
+      </c>
+      <c r="I23" s="25">
+        <v>329</v>
+      </c>
+      <c r="J23" s="25">
+        <v>334.6</v>
+      </c>
+      <c r="K23" s="25">
+        <v>339.2</v>
+      </c>
+      <c r="L23" s="7">
+        <f>K23/AVERAGE(D23:K23)</f>
+        <v>1.0520276033186013</v>
+      </c>
+      <c r="M23" s="7">
+        <f>L23/L4</f>
+        <v>1.0032662000739572</v>
+      </c>
+      <c r="N23" s="7">
+        <f>L23/$L$37</f>
+        <v>0.95910326123969891</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15">
+      <c r="B24">
+        <v>2</v>
+      </c>
+      <c r="C24" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="25">
+        <v>421.9</v>
+      </c>
+      <c r="E24" s="25">
+        <v>427.5</v>
+      </c>
+      <c r="F24" s="25">
+        <v>433.9</v>
+      </c>
+      <c r="G24" s="25">
+        <v>441.7</v>
+      </c>
+      <c r="H24" s="25">
+        <v>450</v>
+      </c>
+      <c r="I24" s="25">
+        <v>458.5</v>
+      </c>
+      <c r="J24" s="25">
+        <v>468.1</v>
+      </c>
+      <c r="K24" s="25">
+        <v>480.8</v>
+      </c>
+      <c r="L24" s="7">
+        <f t="shared" ref="L24:L36" si="3">K24/AVERAGE(D24:K24)</f>
+        <v>1.0736936132201875</v>
+      </c>
+      <c r="M24" s="7">
+        <f t="shared" ref="M24:M36" si="4">L24/L5</f>
+        <v>1.0014279029001554</v>
+      </c>
+      <c r="N24" s="7">
+        <f t="shared" ref="N24:N36" si="5">L24/$L$37</f>
+        <v>0.97885553835591999</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15">
+      <c r="B25">
+        <v>3</v>
+      </c>
+      <c r="C25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" s="25">
+        <v>276</v>
+      </c>
+      <c r="E25" s="25">
+        <v>276.39999999999998</v>
+      </c>
+      <c r="F25" s="25">
+        <v>277.8</v>
+      </c>
+      <c r="G25" s="25">
+        <v>280.2</v>
+      </c>
+      <c r="H25" s="25">
+        <v>281.2</v>
+      </c>
+      <c r="I25" s="25">
+        <v>283.8</v>
+      </c>
+      <c r="J25" s="25">
+        <v>289.2</v>
+      </c>
+      <c r="K25" s="25">
+        <v>294.5</v>
+      </c>
+      <c r="L25" s="7">
+        <f t="shared" si="3"/>
+        <v>1.0428931875525651</v>
+      </c>
+      <c r="M25" s="7">
+        <f t="shared" si="4"/>
+        <v>0.98919235194106425</v>
+      </c>
+      <c r="N25" s="7">
+        <f t="shared" si="5"/>
+        <v>0.95077567751177317</v>
+      </c>
+    </row>
+    <row r="26" spans="2:15">
+      <c r="B26">
+        <v>4</v>
+      </c>
+      <c r="C26" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26" s="25">
+        <v>169.6</v>
+      </c>
+      <c r="E26" s="25">
+        <v>171.7</v>
+      </c>
+      <c r="F26" s="25">
+        <v>174.4</v>
+      </c>
+      <c r="G26" s="25">
+        <v>177.4</v>
+      </c>
+      <c r="H26" s="25">
+        <v>180.5</v>
+      </c>
+      <c r="I26" s="25">
+        <v>185.1</v>
+      </c>
+      <c r="J26" s="25">
+        <v>191.6</v>
+      </c>
+      <c r="K26" s="25">
+        <v>195.8</v>
+      </c>
+      <c r="L26" s="7">
+        <f t="shared" si="3"/>
+        <v>1.0831892676854993</v>
+      </c>
+      <c r="M26" s="7">
+        <f t="shared" si="4"/>
+        <v>1.00577112802299</v>
+      </c>
+      <c r="N26" s="7">
+        <f t="shared" si="5"/>
+        <v>0.98751245300013368</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15">
+      <c r="B27">
+        <v>5</v>
+      </c>
+      <c r="C27" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" s="25">
+        <v>264.2</v>
+      </c>
+      <c r="E27" s="25">
+        <v>267.60000000000002</v>
+      </c>
+      <c r="F27" s="25">
+        <v>270.7</v>
+      </c>
+      <c r="G27" s="25">
+        <v>274.89999999999998</v>
+      </c>
+      <c r="H27" s="25">
+        <v>278.3</v>
+      </c>
+      <c r="I27" s="25">
+        <v>283.2</v>
+      </c>
+      <c r="J27" s="25">
+        <v>288.89999999999998</v>
+      </c>
+      <c r="K27" s="25">
+        <v>295.60000000000002</v>
+      </c>
+      <c r="L27" s="7">
+        <f t="shared" si="3"/>
+        <v>1.063596293964199</v>
+      </c>
+      <c r="M27" s="7">
+        <f t="shared" si="4"/>
+        <v>0.99013164936867559</v>
+      </c>
+      <c r="N27" s="7">
+        <f t="shared" si="5"/>
+        <v>0.96965010325360146</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15">
+      <c r="B28">
+        <v>6</v>
+      </c>
+      <c r="C28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" s="25">
+        <v>134.1</v>
+      </c>
+      <c r="E28" s="25">
+        <v>135.6</v>
+      </c>
+      <c r="F28" s="25">
+        <v>136.4</v>
+      </c>
+      <c r="G28" s="25">
+        <v>144.19999999999999</v>
+      </c>
+      <c r="H28" s="25">
+        <v>146.9</v>
+      </c>
+      <c r="I28" s="25">
+        <v>150.6</v>
+      </c>
+      <c r="J28" s="25">
+        <v>156</v>
+      </c>
+      <c r="K28" s="25">
+        <v>161.30000000000001</v>
+      </c>
+      <c r="L28" s="7">
+        <f t="shared" si="3"/>
+        <v>1.1075444167882587</v>
+      </c>
+      <c r="M28" s="7">
+        <f t="shared" si="4"/>
+        <v>1.0371577185809977</v>
+      </c>
+      <c r="N28" s="7">
+        <f t="shared" si="5"/>
+        <v>1.0097163408627237</v>
+      </c>
+      <c r="O28" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15">
+      <c r="B29">
+        <v>7</v>
+      </c>
+      <c r="C29" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29" s="25">
+        <v>590.20000000000005</v>
+      </c>
+      <c r="E29" s="25">
+        <v>600.20000000000005</v>
+      </c>
+      <c r="F29" s="25">
+        <v>612.20000000000005</v>
+      </c>
+      <c r="G29" s="25">
+        <v>626.1</v>
+      </c>
+      <c r="H29" s="25">
+        <v>644.79999999999995</v>
+      </c>
+      <c r="I29" s="25">
+        <v>661.1</v>
+      </c>
+      <c r="J29" s="25">
+        <v>678.2</v>
+      </c>
+      <c r="K29" s="25">
+        <v>696.5</v>
+      </c>
+      <c r="L29" s="7">
+        <f t="shared" si="3"/>
+        <v>1.0905603507329771</v>
+      </c>
+      <c r="M29" s="7">
+        <f t="shared" si="4"/>
+        <v>1.0127146298620673</v>
+      </c>
+      <c r="N29" s="7">
+        <f t="shared" si="5"/>
+        <v>0.99423245708310981</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15">
+      <c r="B30">
+        <v>8</v>
+      </c>
+      <c r="C30" t="s">
+        <v>35</v>
+      </c>
+      <c r="D30" s="25">
+        <v>523.79999999999995</v>
+      </c>
+      <c r="E30" s="25">
+        <v>529.6</v>
+      </c>
+      <c r="F30" s="25">
+        <v>538.20000000000005</v>
+      </c>
+      <c r="G30" s="25">
+        <v>546.29999999999995</v>
+      </c>
+      <c r="H30" s="25">
+        <v>551.70000000000005</v>
+      </c>
+      <c r="I30" s="25">
+        <v>561.70000000000005</v>
+      </c>
+      <c r="J30" s="25">
+        <v>572.79999999999995</v>
+      </c>
+      <c r="K30" s="25">
+        <v>585.20000000000005</v>
+      </c>
+      <c r="L30" s="7">
+        <f t="shared" si="3"/>
+        <v>1.0617558342594062</v>
+      </c>
+      <c r="M30" s="7">
+        <f t="shared" si="4"/>
+        <v>0.98877510027927329</v>
+      </c>
+      <c r="N30" s="7">
+        <f t="shared" si="5"/>
+        <v>0.96797220915702198</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15">
+      <c r="B31">
+        <v>9</v>
+      </c>
+      <c r="C31" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" s="25">
+        <v>142.1</v>
+      </c>
+      <c r="E31" s="25">
+        <v>143.80000000000001</v>
+      </c>
+      <c r="F31" s="25">
+        <v>145.1</v>
+      </c>
+      <c r="G31" s="25">
+        <v>179.6</v>
+      </c>
+      <c r="H31" s="25">
+        <v>182.8</v>
+      </c>
+      <c r="I31" s="25">
+        <v>189.5</v>
+      </c>
+      <c r="J31" s="25">
+        <v>195.7</v>
+      </c>
+      <c r="K31" s="25">
+        <v>201.6</v>
+      </c>
+      <c r="L31" s="7">
+        <f t="shared" si="3"/>
+        <v>1.1685263005361541</v>
+      </c>
+      <c r="M31" s="7">
+        <f t="shared" si="4"/>
+        <v>1.0805091110380687</v>
+      </c>
+      <c r="N31" s="7">
+        <f t="shared" si="5"/>
+        <v>1.0653117676316106</v>
+      </c>
+      <c r="O31" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="32" spans="2:15">
+      <c r="B32">
+        <v>10</v>
+      </c>
+      <c r="C32" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" s="25">
+        <v>87.5</v>
+      </c>
+      <c r="E32" s="25">
+        <v>88.2</v>
+      </c>
+      <c r="F32" s="25">
+        <v>89</v>
+      </c>
+      <c r="G32" s="25">
+        <v>90.4</v>
+      </c>
+      <c r="H32" s="25">
+        <v>91.3</v>
+      </c>
+      <c r="I32" s="25">
+        <v>93.4</v>
+      </c>
+      <c r="J32" s="25">
+        <v>96.2</v>
+      </c>
+      <c r="K32" s="25">
+        <v>99.3</v>
+      </c>
+      <c r="L32" s="7">
+        <f t="shared" si="3"/>
+        <v>1.0803753569971439</v>
+      </c>
+      <c r="M32" s="7">
+        <f t="shared" si="4"/>
+        <v>1.0114186858934013</v>
+      </c>
+      <c r="N32" s="7">
+        <f t="shared" si="5"/>
+        <v>0.98494709168306793</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17">
+      <c r="B33">
+        <v>11</v>
+      </c>
+      <c r="C33" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" s="25">
+        <v>0</v>
+      </c>
+      <c r="E33" s="25">
+        <v>47.7</v>
+      </c>
+      <c r="F33" s="25">
+        <v>48.2</v>
+      </c>
+      <c r="G33" s="25">
+        <v>48.7</v>
+      </c>
+      <c r="H33" s="25">
+        <v>51.4</v>
+      </c>
+      <c r="I33" s="25">
+        <v>52.7</v>
+      </c>
+      <c r="J33" s="25">
+        <v>54.1</v>
+      </c>
+      <c r="K33" s="25">
+        <v>56.2</v>
+      </c>
+      <c r="L33" s="7">
+        <f t="shared" si="3"/>
+        <v>1.252367688022284</v>
+      </c>
+      <c r="M33" s="7">
+        <f t="shared" si="4"/>
+        <v>1.2051289517068422</v>
+      </c>
+      <c r="N33" s="7">
+        <f t="shared" si="5"/>
+        <v>1.1417475454678085</v>
+      </c>
+      <c r="O33" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17">
+      <c r="B34">
+        <v>12</v>
+      </c>
+      <c r="C34" t="s">
+        <v>100</v>
+      </c>
+      <c r="D34" s="15">
+        <v>274.5</v>
+      </c>
+      <c r="E34" s="15">
+        <v>278.5</v>
+      </c>
+      <c r="F34" s="15">
+        <v>283.8</v>
+      </c>
+      <c r="G34" s="15">
+        <v>288.8</v>
+      </c>
+      <c r="H34" s="15">
+        <v>293.5</v>
+      </c>
+      <c r="I34" s="15">
+        <v>299.10000000000002</v>
+      </c>
+      <c r="J34" s="15">
+        <v>314.5</v>
+      </c>
+      <c r="K34" s="15">
+        <v>321.8</v>
+      </c>
+      <c r="L34" s="7">
+        <f>K34/AVERAGE(D34:K34)</f>
+        <v>1.0933956253981738</v>
+      </c>
+      <c r="M34" s="7">
+        <f t="shared" si="4"/>
+        <v>1.0221391549814363</v>
+      </c>
+      <c r="N34" s="7">
+        <f t="shared" si="5"/>
+        <v>0.99681729532245111</v>
+      </c>
+      <c r="O34" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17">
+      <c r="B35">
+        <v>13</v>
+      </c>
+      <c r="C35" t="s">
+        <v>40</v>
+      </c>
+      <c r="D35" s="25">
+        <v>139.30000000000001</v>
+      </c>
+      <c r="E35" s="25">
+        <v>140.19999999999999</v>
+      </c>
+      <c r="F35" s="25">
+        <v>141.69999999999999</v>
+      </c>
+      <c r="G35" s="25">
+        <v>143.69999999999999</v>
+      </c>
+      <c r="H35" s="25">
+        <v>145</v>
+      </c>
+      <c r="I35" s="25">
+        <v>146.69999999999999</v>
+      </c>
+      <c r="J35" s="25">
+        <v>149.9</v>
+      </c>
+      <c r="K35" s="25">
+        <v>153.1</v>
+      </c>
+      <c r="L35" s="7">
+        <f t="shared" si="3"/>
+        <v>1.0562262849258366</v>
+      </c>
+      <c r="M35" s="7">
+        <f t="shared" si="4"/>
+        <v>0.99604081117126197</v>
+      </c>
+      <c r="N35" s="7">
+        <f t="shared" si="5"/>
+        <v>0.96293107831379798</v>
+      </c>
+    </row>
+    <row r="36" spans="2:17">
+      <c r="B36">
+        <v>14</v>
+      </c>
+      <c r="C36" t="s">
+        <v>41</v>
+      </c>
+      <c r="D36" s="15">
+        <v>2424.1</v>
+      </c>
+      <c r="E36" s="15">
+        <v>2464.9</v>
+      </c>
+      <c r="F36" s="15">
+        <v>2509.9</v>
+      </c>
+      <c r="G36" s="15">
+        <v>2571.6999999999998</v>
+      </c>
+      <c r="H36" s="15">
+        <v>2694.4</v>
+      </c>
+      <c r="I36" s="15">
+        <v>2860.6</v>
+      </c>
+      <c r="J36" s="15">
+        <v>2956.4</v>
+      </c>
+      <c r="K36" s="15">
+        <v>3040.8</v>
+      </c>
+      <c r="L36" s="7">
+        <f t="shared" si="3"/>
+        <v>1.1302618618395377</v>
+      </c>
+      <c r="M36" s="7">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="N36" s="7">
+        <f t="shared" si="5"/>
+        <v>1.0304271811172803</v>
+      </c>
+      <c r="O36" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17">
+      <c r="L37" s="7">
+        <f>AVERAGE(L23:L36)</f>
+        <v>1.0968866918029161</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="38" spans="2:17">
+      <c r="C38" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D38" s="7">
+        <f>D23/D4</f>
+        <v>0.16913342503438789</v>
+      </c>
+      <c r="E38" s="7">
+        <f t="shared" ref="E38:K38" si="6">E23/E4</f>
+        <v>0.16875644574716386</v>
+      </c>
+      <c r="F38" s="7">
+        <f t="shared" si="6"/>
+        <v>0.1684137340892074</v>
+      </c>
+      <c r="G38" s="7">
+        <f t="shared" si="6"/>
+        <v>0.16836116525312123</v>
+      </c>
+      <c r="H38" s="7">
+        <f t="shared" si="6"/>
+        <v>0.168321463845714</v>
+      </c>
+      <c r="I38" s="7">
+        <f t="shared" si="6"/>
+        <v>0.16884783166538364</v>
+      </c>
+      <c r="J38" s="7">
+        <f t="shared" si="6"/>
+        <v>0.16931484667543772</v>
+      </c>
+      <c r="K38" s="7">
+        <f t="shared" si="6"/>
+        <v>0.16937134867928297</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17">
+      <c r="C39" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D39" s="7">
+        <f t="shared" ref="D39:K39" si="7">D24/D5</f>
+        <v>0.14241350210970463</v>
+      </c>
+      <c r="E39" s="7">
+        <f t="shared" si="7"/>
+        <v>0.14194640900488098</v>
+      </c>
+      <c r="F39" s="7">
+        <f t="shared" si="7"/>
+        <v>0.14147836577651698</v>
+      </c>
+      <c r="G39" s="7">
+        <f t="shared" si="7"/>
+        <v>0.14122198420564633</v>
+      </c>
+      <c r="H39" s="7">
+        <f t="shared" si="7"/>
+        <v>0.14114990119506918</v>
+      </c>
+      <c r="I39" s="7">
+        <f t="shared" si="7"/>
+        <v>0.1409251575226679</v>
+      </c>
+      <c r="J39" s="7">
+        <f t="shared" si="7"/>
+        <v>0.14087940530291632</v>
+      </c>
+      <c r="K39" s="7">
+        <f t="shared" si="7"/>
+        <v>0.14164506245580957</v>
+      </c>
+    </row>
+    <row r="40" spans="2:17">
+      <c r="C40" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D40" s="7">
+        <f t="shared" ref="D40:K40" si="8">D25/D6</f>
+        <v>0.14971521562245729</v>
+      </c>
+      <c r="E40" s="7">
+        <f t="shared" si="8"/>
+        <v>0.14779168003422091</v>
+      </c>
+      <c r="F40" s="7">
+        <f t="shared" si="8"/>
+        <v>0.14661177960734642</v>
+      </c>
+      <c r="G40" s="7">
+        <f t="shared" si="8"/>
+        <v>0.14564166536722281</v>
+      </c>
+      <c r="H40" s="7">
+        <f t="shared" si="8"/>
+        <v>0.14441990652765652</v>
+      </c>
+      <c r="I40" s="7">
+        <f t="shared" si="8"/>
+        <v>0.14356535815459329</v>
+      </c>
+      <c r="J40" s="7">
+        <f t="shared" si="8"/>
+        <v>0.14390207493655768</v>
+      </c>
+      <c r="K40" s="7">
+        <f t="shared" si="8"/>
+        <v>0.1440802348336595</v>
+      </c>
+    </row>
+    <row r="41" spans="2:17">
+      <c r="C41" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D41" s="7">
+        <f t="shared" ref="D41:K41" si="9">D26/D7</f>
+        <v>0.13036126056879324</v>
+      </c>
+      <c r="E41" s="7">
+        <f t="shared" si="9"/>
+        <v>0.12958490566037734</v>
+      </c>
+      <c r="F41" s="7">
+        <f t="shared" si="9"/>
+        <v>0.12895593019816623</v>
+      </c>
+      <c r="G41" s="7">
+        <f t="shared" si="9"/>
+        <v>0.12835540120107083</v>
+      </c>
+      <c r="H41" s="7">
+        <f t="shared" si="9"/>
+        <v>0.12796880538816022</v>
+      </c>
+      <c r="I41" s="7">
+        <f t="shared" si="9"/>
+        <v>0.12823888042122764</v>
+      </c>
+      <c r="J41" s="7">
+        <f t="shared" si="9"/>
+        <v>0.1298542866824805</v>
+      </c>
+      <c r="K41" s="7">
+        <f t="shared" si="9"/>
+        <v>0.12989253018442351</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17">
+      <c r="C42" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D42" s="7">
+        <f t="shared" ref="D42:K42" si="10">D27/D8</f>
+        <v>8.5534835534835527E-2</v>
+      </c>
+      <c r="E42" s="7">
+        <f t="shared" si="10"/>
+        <v>8.4995553296912718E-2</v>
+      </c>
+      <c r="F42" s="7">
+        <f t="shared" si="10"/>
+        <v>8.4248856244748066E-2</v>
+      </c>
+      <c r="G42" s="7">
+        <f t="shared" si="10"/>
+        <v>8.3800756005365185E-2</v>
+      </c>
+      <c r="H42" s="7">
+        <f t="shared" si="10"/>
+        <v>8.3438268273670332E-2</v>
+      </c>
+      <c r="I42" s="7">
+        <f t="shared" si="10"/>
+        <v>8.3091277176304892E-2</v>
+      </c>
+      <c r="J42" s="7">
+        <f t="shared" si="10"/>
+        <v>8.2962409901501874E-2</v>
+      </c>
+      <c r="K42" s="7">
+        <f t="shared" si="10"/>
+        <v>8.3019715778239633E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17">
+      <c r="C43" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D43" s="7">
+        <f t="shared" ref="D43:K43" si="11">D28/D9</f>
+        <v>0.14223589308442935</v>
+      </c>
+      <c r="E43" s="7">
+        <f t="shared" si="11"/>
+        <v>0.14154488517745303</v>
+      </c>
+      <c r="F43" s="7">
+        <f t="shared" si="11"/>
+        <v>0.13925472179683512</v>
+      </c>
+      <c r="G43" s="7">
+        <f t="shared" si="11"/>
+        <v>0.14461939624912243</v>
+      </c>
+      <c r="H43" s="7">
+        <f t="shared" si="11"/>
+        <v>0.14492896606156275</v>
+      </c>
+      <c r="I43" s="7">
+        <f t="shared" si="11"/>
+        <v>0.14566205629171097</v>
+      </c>
+      <c r="J43" s="7">
+        <f t="shared" si="11"/>
+        <v>0.14779725248697301</v>
+      </c>
+      <c r="K43" s="7">
+        <f t="shared" si="11"/>
+        <v>0.15000464986515394</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17">
+      <c r="C44" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D44" s="7">
+        <f t="shared" ref="D44:K44" si="12">D29/D10</f>
+        <v>0.222515457698688</v>
+      </c>
+      <c r="E44" s="7">
+        <f t="shared" si="12"/>
+        <v>0.22232923396058679</v>
+      </c>
+      <c r="F44" s="7">
+        <f t="shared" si="12"/>
+        <v>0.22238366813178831</v>
+      </c>
+      <c r="G44" s="7">
+        <f t="shared" si="12"/>
+        <v>0.22274797210758501</v>
+      </c>
+      <c r="H44" s="7">
+        <f t="shared" si="12"/>
+        <v>0.22486486486486484</v>
+      </c>
+      <c r="I44" s="7">
+        <f t="shared" si="12"/>
+        <v>0.22554672307324897</v>
+      </c>
+      <c r="J44" s="7">
+        <f t="shared" si="12"/>
+        <v>0.22625521267723103</v>
+      </c>
+      <c r="K44" s="7">
+        <f t="shared" si="12"/>
+        <v>0.22716154071948078</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17">
+      <c r="C45" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D45" s="7">
+        <f t="shared" ref="D45:K45" si="13">D30/D11</f>
+        <v>0.14344004162444887</v>
+      </c>
+      <c r="E45" s="7">
+        <f t="shared" si="13"/>
+        <v>0.14236176446869708</v>
+      </c>
+      <c r="F45" s="7">
+        <f t="shared" si="13"/>
+        <v>0.14167258943378347</v>
+      </c>
+      <c r="G45" s="7">
+        <f t="shared" si="13"/>
+        <v>0.1408933821633053</v>
+      </c>
+      <c r="H45" s="7">
+        <f t="shared" si="13"/>
+        <v>0.13975226081009198</v>
+      </c>
+      <c r="I45" s="7">
+        <f t="shared" si="13"/>
+        <v>0.13933470592612807</v>
+      </c>
+      <c r="J45" s="7">
+        <f t="shared" si="13"/>
+        <v>0.13908989364285368</v>
+      </c>
+      <c r="K45" s="7">
+        <f t="shared" si="13"/>
+        <v>0.13905191873589165</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17">
+      <c r="C46" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D46" s="7">
+        <f t="shared" ref="D46:K46" si="14">D31/D12</f>
+        <v>5.7710270884944966E-2</v>
+      </c>
+      <c r="E46" s="7">
+        <f t="shared" si="14"/>
+        <v>5.7195131652215424E-2</v>
+      </c>
+      <c r="F46" s="7">
+        <f t="shared" si="14"/>
+        <v>5.6461340908206543E-2</v>
+      </c>
+      <c r="G46" s="7">
+        <f t="shared" si="14"/>
+        <v>6.8312350233920349E-2</v>
+      </c>
+      <c r="H46" s="7">
+        <f t="shared" si="14"/>
+        <v>6.8188600417785739E-2</v>
+      </c>
+      <c r="I46" s="7">
+        <f t="shared" si="14"/>
+        <v>6.9079906678331873E-2</v>
+      </c>
+      <c r="J46" s="7">
+        <f t="shared" si="14"/>
+        <v>6.9730981649741661E-2</v>
+      </c>
+      <c r="K46" s="7">
+        <f t="shared" si="14"/>
+        <v>7.0070557158249627E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17">
+      <c r="C47" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D47" s="7">
+        <f t="shared" ref="D47:K47" si="15">D32/D13</f>
+        <v>0.10895280786950566</v>
+      </c>
+      <c r="E47" s="7">
+        <f t="shared" si="15"/>
+        <v>0.10810148302488051</v>
+      </c>
+      <c r="F47" s="7">
+        <f t="shared" si="15"/>
+        <v>0.10724183636582721</v>
+      </c>
+      <c r="G47" s="7">
+        <f t="shared" si="15"/>
+        <v>0.10681791326952618</v>
+      </c>
+      <c r="H47" s="7">
+        <f t="shared" si="15"/>
+        <v>0.10605180624927402</v>
+      </c>
+      <c r="I47" s="7">
+        <f t="shared" si="15"/>
+        <v>0.10630548600045528</v>
+      </c>
+      <c r="J47" s="7">
+        <f t="shared" si="15"/>
+        <v>0.10729422261878206</v>
+      </c>
+      <c r="K47" s="7">
+        <f t="shared" si="15"/>
+        <v>0.10864332603938731</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17">
+      <c r="C48" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D48" s="7">
+        <f>D33/D14</f>
+        <v>0</v>
+      </c>
+      <c r="E48" s="7">
+        <f t="shared" ref="E48:K48" si="16">E33/E14</f>
+        <v>1.6671326716063192E-2</v>
+      </c>
+      <c r="F48" s="7">
+        <f t="shared" si="16"/>
+        <v>1.6629291012592723E-2</v>
+      </c>
+      <c r="G48" s="7">
+        <f t="shared" si="16"/>
+        <v>1.655392773377749E-2</v>
+      </c>
+      <c r="H48" s="7">
+        <f t="shared" si="16"/>
+        <v>1.7272085755569742E-2</v>
+      </c>
+      <c r="I48" s="7">
+        <f t="shared" si="16"/>
+        <v>1.7916029236783954E-2</v>
+      </c>
+      <c r="J48" s="7">
+        <f t="shared" si="16"/>
+        <v>1.8073094140442305E-2</v>
+      </c>
+      <c r="K48" s="7">
+        <f t="shared" si="16"/>
+        <v>1.8415361426043646E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="3:11">
+      <c r="C49" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D49" s="7">
+        <f t="shared" ref="D49:K49" si="17">D34/D15</f>
+        <v>7.7002917414721719E-2</v>
+      </c>
+      <c r="E49" s="7">
+        <f t="shared" si="17"/>
+        <v>7.6929451411524227E-2</v>
+      </c>
+      <c r="F49" s="7">
+        <f t="shared" si="17"/>
+        <v>7.7050471044986829E-2</v>
+      </c>
+      <c r="G49" s="7">
+        <f t="shared" si="17"/>
+        <v>7.697228144989339E-2</v>
+      </c>
+      <c r="H49" s="7">
+        <f t="shared" si="17"/>
+        <v>7.683246073298429E-2</v>
+      </c>
+      <c r="I49" s="7">
+        <f t="shared" si="17"/>
+        <v>7.6763165999384056E-2</v>
+      </c>
+      <c r="J49" s="7">
+        <f t="shared" si="17"/>
+        <v>7.9093629756306114E-2</v>
+      </c>
+      <c r="K49" s="7">
+        <f t="shared" si="17"/>
+        <v>7.9231810907300262E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="3:11">
+      <c r="C50" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D50" s="7">
+        <f t="shared" ref="D50:K50" si="18">D35/D16</f>
+        <v>7.8403782293015145E-2</v>
+      </c>
+      <c r="E50" s="7">
+        <f t="shared" si="18"/>
+        <v>7.7673130193905815E-2</v>
+      </c>
+      <c r="F50" s="7">
+        <f t="shared" si="18"/>
+        <v>7.7191262188810797E-2</v>
+      </c>
+      <c r="G50" s="7">
+        <f t="shared" si="18"/>
+        <v>7.6989016876506819E-2</v>
+      </c>
+      <c r="H50" s="7">
+        <f t="shared" si="18"/>
+        <v>7.6585855384777898E-2</v>
+      </c>
+      <c r="I50" s="7">
+        <f t="shared" si="18"/>
+        <v>7.6239476145930768E-2</v>
+      </c>
+      <c r="J50" s="7">
+        <f t="shared" si="18"/>
+        <v>7.6553802155150411E-2</v>
+      </c>
+      <c r="K50" s="7">
+        <f t="shared" si="18"/>
+        <v>7.6718781318901585E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="3:11">
+      <c r="C51" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState ref="B23:M36">
+    <sortCondition ref="B23"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/uzbekistan_pop_grp.xlsx
+++ b/uzbekistan_pop_grp.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="765" windowWidth="29400" windowHeight="16485" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="765" windowWidth="29400" windowHeight="16485" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Population Data" sheetId="1" r:id="rId1"/>
@@ -693,7 +693,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -1000,11 +999,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="400473800"/>
-        <c:axId val="400473408"/>
+        <c:axId val="268866040"/>
+        <c:axId val="268867608"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="400473800"/>
+        <c:axId val="268866040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1026,14 +1025,13 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="400473408"/>
+        <c:crossAx val="268867608"/>
         <c:crosses val="autoZero"/>
         <c:auto val="0"/>
         <c:lblAlgn val="ctr"/>
@@ -1041,7 +1039,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="400473408"/>
+        <c:axId val="268867608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1064,21 +1062,19 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="400473800"/>
+        <c:crossAx val="268866040"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
@@ -1123,7 +1119,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -1226,11 +1221,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="400475368"/>
-        <c:axId val="400475760"/>
+        <c:axId val="268864864"/>
+        <c:axId val="268865256"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="400475368"/>
+        <c:axId val="268864864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1252,14 +1247,13 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="400475760"/>
+        <c:crossAx val="268865256"/>
         <c:crosses val="autoZero"/>
         <c:auto val="0"/>
         <c:lblAlgn val="ctr"/>
@@ -1267,7 +1261,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="400475760"/>
+        <c:axId val="268865256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1290,21 +1284,19 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="400475368"/>
+        <c:crossAx val="268864864"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
@@ -1683,11 +1675,11 @@
         </c:dLbls>
         <c:gapWidth val="80"/>
         <c:overlap val="25"/>
-        <c:axId val="391766584"/>
-        <c:axId val="391763448"/>
+        <c:axId val="268870352"/>
+        <c:axId val="268872312"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="391766584"/>
+        <c:axId val="268870352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1730,7 +1722,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="391763448"/>
+        <c:crossAx val="268872312"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1738,7 +1730,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="391763448"/>
+        <c:axId val="268872312"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1789,7 +1781,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="391766584"/>
+        <c:crossAx val="268870352"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2232,11 +2224,11 @@
         </c:dLbls>
         <c:gapWidth val="80"/>
         <c:overlap val="25"/>
-        <c:axId val="391764624"/>
-        <c:axId val="391765016"/>
+        <c:axId val="268872704"/>
+        <c:axId val="268866824"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="391764624"/>
+        <c:axId val="268872704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2279,7 +2271,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="391765016"/>
+        <c:crossAx val="268866824"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2287,7 +2279,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="391765016"/>
+        <c:axId val="268866824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2338,7 +2330,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="391764624"/>
+        <c:crossAx val="268872704"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3497,7 +3489,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3528,7 +3520,7 @@
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3564,7 +3556,7 @@
         <xdr:cNvPr id="9" name="Chart 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E6B9DD3-9AD8-A0F9-6222-3097CBAAF386}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9E6B9DD3-9AD8-A0F9-6222-3097CBAAF386}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3600,7 +3592,7 @@
         <xdr:cNvPr id="11" name="Chart 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90BC8AFB-4008-3DDD-F6BC-DD31737172DD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{90BC8AFB-4008-3DDD-F6BC-DD31737172DD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9470,6 +9462,10 @@
         <f t="shared" si="30"/>
         <v>1710.1850904150283</v>
       </c>
+      <c r="L32" s="25">
+        <f>J29/J37</f>
+        <v>1.1798152512364666</v>
+      </c>
       <c r="M32" s="7" t="s">
         <v>11</v>
       </c>
@@ -16897,13 +16893,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:Q51"/>
+  <dimension ref="B3:W51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="16.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:14">
+    <row r="3" spans="2:21">
       <c r="C3" s="18" t="s">
         <v>80</v>
       </c>
@@ -16932,7 +16928,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="4" spans="2:14">
+    <row r="4" spans="2:21">
       <c r="B4">
         <v>1</v>
       </c>
@@ -16971,8 +16967,32 @@
         <f>L4/$L$18</f>
         <v>0.97908737497017406</v>
       </c>
-    </row>
-    <row r="5" spans="2:14">
+      <c r="P4" s="7">
+        <f>F4/(AVERAGE(D4:F4))</f>
+        <v>1.0144314236111112</v>
+      </c>
+      <c r="Q4" s="7">
+        <f t="shared" ref="Q4:U4" si="0">G4/(AVERAGE(E4:G4))</f>
+        <v>1.015061314701269</v>
+      </c>
+      <c r="R4" s="7">
+        <f t="shared" si="0"/>
+        <v>1.013932323693735</v>
+      </c>
+      <c r="S4" s="7">
+        <f t="shared" si="0"/>
+        <v>1.0129971406290617</v>
+      </c>
+      <c r="T4" s="7">
+        <f t="shared" si="0"/>
+        <v>1.0137131523151632</v>
+      </c>
+      <c r="U4" s="7">
+        <f t="shared" si="0"/>
+        <v>1.0136147383338394</v>
+      </c>
+    </row>
+    <row r="5" spans="2:21">
       <c r="B5">
         <v>2</v>
       </c>
@@ -17004,18 +17024,42 @@
         <v>3394.4</v>
       </c>
       <c r="L5" s="7">
-        <f t="shared" ref="L5:L17" si="0">K5/AVERAGE(D5:K5)</f>
+        <f t="shared" ref="L5:L17" si="1">K5/AVERAGE(D5:K5)</f>
         <v>1.0721626690356332</v>
       </c>
       <c r="M5">
-        <f t="shared" ref="M5:M17" si="1">L5/$L$18</f>
+        <f t="shared" ref="M5:M17" si="2">L5/$L$18</f>
         <v>1.0010855169184307</v>
       </c>
       <c r="N5" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="6" spans="2:14">
+      <c r="P5" s="7">
+        <f t="shared" ref="P5:P17" si="3">F5/(AVERAGE(D5:F5))</f>
+        <v>1.0176527192487639</v>
+      </c>
+      <c r="Q5" s="7">
+        <f t="shared" ref="Q5:Q17" si="4">G5/(AVERAGE(E5:G5))</f>
+        <v>1.0192042405743893</v>
+      </c>
+      <c r="R5" s="7">
+        <f t="shared" ref="R5:R17" si="5">H5/(AVERAGE(F5:H5))</f>
+        <v>1.0193547699489485</v>
+      </c>
+      <c r="S5" s="7">
+        <f t="shared" ref="S5:S17" si="6">I5/(AVERAGE(G5:I5))</f>
+        <v>1.0199805628415872</v>
+      </c>
+      <c r="T5" s="7">
+        <f t="shared" ref="T5:T17" si="7">J5/(AVERAGE(H5:J5))</f>
+        <v>1.0208719519064346</v>
+      </c>
+      <c r="U5" s="7">
+        <f t="shared" ref="U5:U17" si="8">K5/(AVERAGE(I5:K5))</f>
+        <v>1.0213226887047921</v>
+      </c>
+    </row>
+    <row r="6" spans="2:21">
       <c r="B6">
         <v>3</v>
       </c>
@@ -17047,15 +17091,39 @@
         <v>2044</v>
       </c>
       <c r="L6" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0542875564152161</v>
       </c>
       <c r="M6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.98439540367872924</v>
       </c>
-    </row>
-    <row r="7" spans="2:14">
+      <c r="P6" s="7">
+        <f t="shared" si="3"/>
+        <v>1.0135330302219845</v>
+      </c>
+      <c r="Q6" s="7">
+        <f t="shared" si="4"/>
+        <v>1.0145546590729315</v>
+      </c>
+      <c r="R6" s="7">
+        <f t="shared" si="5"/>
+        <v>1.0130944535016824</v>
+      </c>
+      <c r="S6" s="7">
+        <f t="shared" si="6"/>
+        <v>1.0141249700742159</v>
+      </c>
+      <c r="T6" s="7">
+        <f t="shared" si="7"/>
+        <v>1.0160947822569772</v>
+      </c>
+      <c r="U6" s="7">
+        <f t="shared" si="8"/>
+        <v>1.0168311085316308</v>
+      </c>
+    </row>
+    <row r="7" spans="2:21">
       <c r="B7">
         <v>4</v>
       </c>
@@ -17087,18 +17155,42 @@
         <v>1507.4</v>
       </c>
       <c r="L7" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0769739133541123</v>
       </c>
       <c r="M7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.0055778081953857</v>
       </c>
       <c r="N7" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="8" spans="2:14">
+      <c r="P7" s="7">
+        <f t="shared" si="3"/>
+        <v>1.0198069575708828</v>
+      </c>
+      <c r="Q7" s="7">
+        <f t="shared" si="4"/>
+        <v>1.0213819435891118</v>
+      </c>
+      <c r="R7" s="7">
+        <f t="shared" si="5"/>
+        <v>1.0208685162846802</v>
+      </c>
+      <c r="S7" s="7">
+        <f t="shared" si="6"/>
+        <v>1.0222379603399434</v>
+      </c>
+      <c r="T7" s="7">
+        <f t="shared" si="7"/>
+        <v>1.0224280500762231</v>
+      </c>
+      <c r="U7" s="7">
+        <f t="shared" si="8"/>
+        <v>1.0216659512459616</v>
+      </c>
+    </row>
+    <row r="8" spans="2:21">
       <c r="B8">
         <v>5</v>
       </c>
@@ -17130,18 +17222,42 @@
         <v>3560.6</v>
       </c>
       <c r="L8" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.074196845078496</v>
       </c>
       <c r="M8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.0029848408122612</v>
       </c>
       <c r="N8" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="9" spans="2:14">
+      <c r="P8" s="7">
+        <f t="shared" si="3"/>
+        <v>1.0199993650995205</v>
+      </c>
+      <c r="Q8" s="7">
+        <f t="shared" si="4"/>
+        <v>1.0206701998568748</v>
+      </c>
+      <c r="R8" s="7">
+        <f t="shared" si="5"/>
+        <v>1.0180386411500779</v>
+      </c>
+      <c r="S8" s="7">
+        <f t="shared" si="6"/>
+        <v>1.0200317235462535</v>
+      </c>
+      <c r="T8" s="7">
+        <f t="shared" si="7"/>
+        <v>1.0216017993350284</v>
+      </c>
+      <c r="U8" s="7">
+        <f t="shared" si="8"/>
+        <v>1.022064451928965</v>
+      </c>
+    </row>
+    <row r="9" spans="2:21">
       <c r="B9">
         <v>6</v>
       </c>
@@ -17173,15 +17289,39 @@
         <v>1075.3</v>
       </c>
       <c r="L9" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0678649900070758</v>
       </c>
       <c r="M9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.99707274501720178</v>
       </c>
-    </row>
-    <row r="10" spans="2:14">
+      <c r="P9" s="7">
+        <f t="shared" si="3"/>
+        <v>1.0202062285178628</v>
+      </c>
+      <c r="Q9" s="7">
+        <f t="shared" si="4"/>
+        <v>1.0193212022081375</v>
+      </c>
+      <c r="R9" s="7">
+        <f t="shared" si="5"/>
+        <v>1.0169219450204001</v>
+      </c>
+      <c r="S9" s="7">
+        <f t="shared" si="6"/>
+        <v>1.0187545161926033</v>
+      </c>
+      <c r="T9" s="7">
+        <f t="shared" si="7"/>
+        <v>1.0204640670319047</v>
+      </c>
+      <c r="U9" s="7">
+        <f t="shared" si="8"/>
+        <v>1.0193383259076692</v>
+      </c>
+    </row>
+    <row r="10" spans="2:21">
       <c r="B10">
         <v>7</v>
       </c>
@@ -17213,18 +17353,42 @@
         <v>3066.1</v>
       </c>
       <c r="L10" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0768683680233913</v>
       </c>
       <c r="M10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.0054792598080797</v>
       </c>
       <c r="N10" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="11" spans="2:14">
+      <c r="P10" s="7">
+        <f t="shared" si="3"/>
+        <v>1.018976174906538</v>
+      </c>
+      <c r="Q10" s="7">
+        <f t="shared" si="4"/>
+        <v>1.0204639792818853</v>
+      </c>
+      <c r="R10" s="7">
+        <f t="shared" si="5"/>
+        <v>1.0203173925419868</v>
+      </c>
+      <c r="S10" s="7">
+        <f t="shared" si="6"/>
+        <v>1.0213603735451948</v>
+      </c>
+      <c r="T10" s="7">
+        <f t="shared" si="7"/>
+        <v>1.022328077216039</v>
+      </c>
+      <c r="U10" s="7">
+        <f t="shared" si="8"/>
+        <v>1.0226355520473167</v>
+      </c>
+    </row>
+    <row r="11" spans="2:21">
       <c r="B11">
         <v>8</v>
       </c>
@@ -17256,18 +17420,42 @@
         <v>4208.5</v>
       </c>
       <c r="L11" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0738092352442128</v>
       </c>
       <c r="M11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.0026229268951641</v>
       </c>
       <c r="N11" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="12" spans="2:14">
+      <c r="P11" s="7">
+        <f t="shared" si="3"/>
+        <v>1.0202314984736858</v>
+      </c>
+      <c r="Q11" s="7">
+        <f t="shared" si="4"/>
+        <v>1.0206907444456146</v>
+      </c>
+      <c r="R11" s="7">
+        <f t="shared" si="5"/>
+        <v>1.0188489332415691</v>
+      </c>
+      <c r="S11" s="7">
+        <f t="shared" si="6"/>
+        <v>1.0200313754596673</v>
+      </c>
+      <c r="T11" s="7">
+        <f t="shared" si="7"/>
+        <v>1.0212776510266839</v>
+      </c>
+      <c r="U11" s="7">
+        <f t="shared" si="8"/>
+        <v>1.0216458973944005</v>
+      </c>
+    </row>
+    <row r="12" spans="2:21">
       <c r="B12">
         <v>9</v>
       </c>
@@ -17299,18 +17487,42 @@
         <v>2877.1</v>
       </c>
       <c r="L12" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0814589979843163</v>
       </c>
       <c r="M12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.0097655619711157</v>
       </c>
       <c r="N12" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="13" spans="2:14">
+      <c r="P12" s="7">
+        <f t="shared" si="3"/>
+        <v>1.021639457224637</v>
+      </c>
+      <c r="Q12" s="7">
+        <f t="shared" si="4"/>
+        <v>1.0225716952756312</v>
+      </c>
+      <c r="R12" s="7">
+        <f t="shared" si="5"/>
+        <v>1.0206350414985152</v>
+      </c>
+      <c r="S12" s="7">
+        <f t="shared" si="6"/>
+        <v>1.0219170257416399</v>
+      </c>
+      <c r="T12" s="7">
+        <f t="shared" si="7"/>
+        <v>1.0229633679606343</v>
+      </c>
+      <c r="U12" s="7">
+        <f t="shared" si="8"/>
+        <v>1.0242678122181612</v>
+      </c>
+    </row>
+    <row r="13" spans="2:21">
       <c r="B13">
         <v>10</v>
       </c>
@@ -17342,15 +17554,39 @@
         <v>914</v>
       </c>
       <c r="L13" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0681781660409331</v>
       </c>
       <c r="M13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.99736515959270877</v>
       </c>
-    </row>
-    <row r="14" spans="2:14">
+      <c r="P13" s="7">
+        <f t="shared" si="3"/>
+        <v>1.0166605414675975</v>
+      </c>
+      <c r="Q13" s="7">
+        <f t="shared" si="4"/>
+        <v>1.0187793427230047</v>
+      </c>
+      <c r="R13" s="7">
+        <f t="shared" si="5"/>
+        <v>1.017973276575618</v>
+      </c>
+      <c r="S13" s="7">
+        <f t="shared" si="6"/>
+        <v>1.0193363755897595</v>
+      </c>
+      <c r="T13" s="7">
+        <f t="shared" si="7"/>
+        <v>1.0203710026175032</v>
+      </c>
+      <c r="U13" s="7">
+        <f t="shared" si="8"/>
+        <v>1.0196340919232485</v>
+      </c>
+    </row>
+    <row r="14" spans="2:21">
       <c r="B14">
         <v>11</v>
       </c>
@@ -17382,15 +17618,39 @@
         <v>3051.8</v>
       </c>
       <c r="L14" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0391980760635922</v>
       </c>
       <c r="M14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.97030625408035431</v>
       </c>
-    </row>
-    <row r="15" spans="2:14">
+      <c r="P14" s="7">
+        <f t="shared" si="3"/>
+        <v>1.0123995808592385</v>
+      </c>
+      <c r="Q14" s="7">
+        <f t="shared" si="4"/>
+        <v>1.0142617449664431</v>
+      </c>
+      <c r="R14" s="7">
+        <f t="shared" si="5"/>
+        <v>1.0126356861722039</v>
+      </c>
+      <c r="S14" s="7">
+        <f t="shared" si="6"/>
+        <v>0.99607192441840775</v>
+      </c>
+      <c r="T14" s="7">
+        <f t="shared" si="7"/>
+        <v>1.0077883018359743</v>
+      </c>
+      <c r="U14" s="7">
+        <f t="shared" si="8"/>
+        <v>1.0187721855631098</v>
+      </c>
+    </row>
+    <row r="15" spans="2:21">
       <c r="B15">
         <v>12</v>
       </c>
@@ -17422,15 +17682,39 @@
         <v>4061.5</v>
       </c>
       <c r="L15" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0697130816968181</v>
       </c>
       <c r="M15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.99879832069519325</v>
       </c>
-    </row>
-    <row r="16" spans="2:14">
+      <c r="P15" s="7">
+        <f t="shared" si="3"/>
+        <v>1.0167091449444716</v>
+      </c>
+      <c r="Q15" s="7">
+        <f t="shared" si="4"/>
+        <v>1.0181357695264801</v>
+      </c>
+      <c r="R15" s="7">
+        <f t="shared" si="5"/>
+        <v>1.0181869874636837</v>
+      </c>
+      <c r="S15" s="7">
+        <f t="shared" si="6"/>
+        <v>1.0192529036308466</v>
+      </c>
+      <c r="T15" s="7">
+        <f t="shared" si="7"/>
+        <v>1.0202006380049089</v>
+      </c>
+      <c r="U15" s="7">
+        <f t="shared" si="8"/>
+        <v>1.0209733371319401</v>
+      </c>
+    </row>
+    <row r="16" spans="2:21">
       <c r="B16">
         <v>13</v>
       </c>
@@ -17462,15 +17746,39 @@
         <v>1995.6</v>
       </c>
       <c r="L16" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0604247065778374</v>
       </c>
       <c r="M16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.99012570218695828</v>
       </c>
-    </row>
-    <row r="17" spans="2:15">
+      <c r="P16" s="7">
+        <f t="shared" si="3"/>
+        <v>1.0165577583342564</v>
+      </c>
+      <c r="Q16" s="7">
+        <f t="shared" si="4"/>
+        <v>1.0167598779779199</v>
+      </c>
+      <c r="R16" s="7">
+        <f t="shared" si="5"/>
+        <v>1.0150835492806718</v>
+      </c>
+      <c r="S16" s="7">
+        <f t="shared" si="6"/>
+        <v>1.0155876143560874</v>
+      </c>
+      <c r="T16" s="7">
+        <f t="shared" si="7"/>
+        <v>1.0170891335965093</v>
+      </c>
+      <c r="U16" s="7">
+        <f t="shared" si="8"/>
+        <v>1.018527024957893</v>
+      </c>
+    </row>
+    <row r="17" spans="2:23">
       <c r="B17">
         <v>14</v>
       </c>
@@ -17502,51 +17810,75 @@
         <v>3040.8</v>
       </c>
       <c r="L17" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.1302618618395377</v>
       </c>
       <c r="M17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.0553331251782436</v>
       </c>
       <c r="N17" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="18" spans="2:15">
+      <c r="P17" s="7">
+        <f t="shared" si="3"/>
+        <v>1.0176783035316062</v>
+      </c>
+      <c r="Q17" s="7">
+        <f t="shared" si="4"/>
+        <v>1.0223414828065991</v>
+      </c>
+      <c r="R17" s="7">
+        <f t="shared" si="5"/>
+        <v>1.0395061728395063</v>
+      </c>
+      <c r="S17" s="7">
+        <f t="shared" si="6"/>
+        <v>1.0560005906456496</v>
+      </c>
+      <c r="T17" s="7">
+        <f t="shared" si="7"/>
+        <v>1.042037737622483</v>
+      </c>
+      <c r="U17" s="7">
+        <f t="shared" si="8"/>
+        <v>1.0298719772403984</v>
+      </c>
+    </row>
+    <row r="18" spans="2:23">
       <c r="C18" s="7" t="s">
         <v>48</v>
       </c>
       <c r="D18" s="15">
-        <f t="shared" ref="D18:K18" si="2">SUM(D4:D17)</f>
+        <f t="shared" ref="D18:K18" si="9">SUM(D4:D17)</f>
         <v>32120.499999999993</v>
       </c>
       <c r="E18" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>32656.700000000004</v>
       </c>
       <c r="F18" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>33255.5</v>
       </c>
       <c r="G18" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>33905.199999999997</v>
       </c>
       <c r="H18" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>34558.9</v>
       </c>
       <c r="I18" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>35271.300000000003</v>
       </c>
       <c r="J18" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>36024.9</v>
       </c>
       <c r="K18" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>36799.800000000003</v>
       </c>
       <c r="L18" s="7">
@@ -17554,7 +17886,7 @@
         <v>1.0710000803287956</v>
       </c>
     </row>
-    <row r="19" spans="2:15">
+    <row r="19" spans="2:23">
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
       <c r="F19" s="15"/>
@@ -17565,7 +17897,7 @@
       <c r="K19" s="15"/>
       <c r="L19" s="7"/>
     </row>
-    <row r="20" spans="2:15">
+    <row r="20" spans="2:23">
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
       <c r="F20" s="15"/>
@@ -17576,10 +17908,10 @@
       <c r="K20" s="15"/>
       <c r="L20" s="7"/>
     </row>
-    <row r="21" spans="2:15">
+    <row r="21" spans="2:23">
       <c r="L21" s="7"/>
     </row>
-    <row r="22" spans="2:15">
+    <row r="22" spans="2:23">
       <c r="C22" s="18" t="s">
         <v>79</v>
       </c>
@@ -17609,7 +17941,7 @@
       </c>
       <c r="L22" s="7"/>
     </row>
-    <row r="23" spans="2:15">
+    <row r="23" spans="2:23">
       <c r="B23">
         <v>1</v>
       </c>
@@ -17641,19 +17973,41 @@
         <v>339.2</v>
       </c>
       <c r="L23" s="7">
-        <f>K23/AVERAGE(D23:K23)</f>
-        <v>1.0520276033186013</v>
-      </c>
-      <c r="M23" s="7">
-        <f>L23/L4</f>
-        <v>1.0032662000739572</v>
-      </c>
-      <c r="N23" s="7">
-        <f>L23/$L$37</f>
-        <v>0.95910326123969891</v>
-      </c>
-    </row>
-    <row r="24" spans="2:15">
+        <f>K23/$K$37</f>
+        <v>0.68607423031914128</v>
+      </c>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
+      <c r="P23" s="7">
+        <f>F23/(AVERAGE(D23:F23))</f>
+        <v>1.0123231890270037</v>
+      </c>
+      <c r="Q23" s="7">
+        <f t="shared" ref="Q23:T23" si="10">G23/(AVERAGE(E23:G23))</f>
+        <v>1.0141738946477683</v>
+      </c>
+      <c r="R23" s="7">
+        <f t="shared" si="10"/>
+        <v>1.0136700406970678</v>
+      </c>
+      <c r="S23" s="7">
+        <f t="shared" si="10"/>
+        <v>1.0150143973673385</v>
+      </c>
+      <c r="T23" s="7">
+        <f t="shared" si="10"/>
+        <v>1.0166092768887989</v>
+      </c>
+      <c r="U23" s="7">
+        <f>K23/(AVERAGE(I23:K23))</f>
+        <v>1.0147586757080176</v>
+      </c>
+      <c r="W23" s="7">
+        <f>U23/U4</f>
+        <v>1.0011285721595353</v>
+      </c>
+    </row>
+    <row r="24" spans="2:23">
       <c r="B24">
         <v>2</v>
       </c>
@@ -17685,19 +18039,41 @@
         <v>480.8</v>
       </c>
       <c r="L24" s="7">
-        <f t="shared" ref="L24:L36" si="3">K24/AVERAGE(D24:K24)</f>
-        <v>1.0736936132201875</v>
-      </c>
-      <c r="M24" s="7">
-        <f t="shared" ref="M24:M36" si="4">L24/L5</f>
-        <v>1.0014279029001554</v>
-      </c>
-      <c r="N24" s="7">
-        <f t="shared" ref="N24:N36" si="5">L24/$L$37</f>
-        <v>0.97885553835591999</v>
-      </c>
-    </row>
-    <row r="25" spans="2:15">
+        <f t="shared" ref="L24:L36" si="11">K24/$K$37</f>
+        <v>0.97247785948538656</v>
+      </c>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+      <c r="P24" s="7">
+        <f t="shared" ref="P24:P36" si="12">F24/(AVERAGE(D24:F24))</f>
+        <v>1.0143380347541495</v>
+      </c>
+      <c r="Q24" s="7">
+        <f t="shared" ref="Q24:Q36" si="13">G24/(AVERAGE(E24:G24))</f>
+        <v>1.0168828178957872</v>
+      </c>
+      <c r="R24" s="7">
+        <f t="shared" ref="R24:R36" si="14">H24/(AVERAGE(F24:H24))</f>
+        <v>1.0184067592033796</v>
+      </c>
+      <c r="S24" s="7">
+        <f t="shared" ref="S24:S36" si="15">I24/(AVERAGE(G24:I24))</f>
+        <v>1.0187379647459636</v>
+      </c>
+      <c r="T24" s="7">
+        <f t="shared" ref="T24:T36" si="16">J24/(AVERAGE(H24:J24))</f>
+        <v>1.0201220398082234</v>
+      </c>
+      <c r="U24" s="7">
+        <f t="shared" ref="U24:U36" si="17">K24/(AVERAGE(I24:K24))</f>
+        <v>1.0248685519397469</v>
+      </c>
+      <c r="W24" s="7">
+        <f t="shared" ref="W24:W36" si="18">U24/U5</f>
+        <v>1.003471834391001</v>
+      </c>
+    </row>
+    <row r="25" spans="2:23">
       <c r="B25">
         <v>3</v>
       </c>
@@ -17729,19 +18105,41 @@
         <v>294.5</v>
       </c>
       <c r="L25" s="7">
-        <f t="shared" si="3"/>
-        <v>1.0428931875525651</v>
-      </c>
-      <c r="M25" s="7">
-        <f t="shared" si="4"/>
-        <v>0.98919235194106425</v>
-      </c>
-      <c r="N25" s="7">
-        <f t="shared" si="5"/>
-        <v>0.95077567751177317</v>
-      </c>
-    </row>
-    <row r="26" spans="2:15">
+        <f t="shared" si="11"/>
+        <v>0.59566291517979686</v>
+      </c>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
+      <c r="P25" s="7">
+        <f t="shared" si="12"/>
+        <v>1.0038544928932787</v>
+      </c>
+      <c r="Q25" s="7">
+        <f t="shared" si="13"/>
+        <v>1.007430488974113</v>
+      </c>
+      <c r="R25" s="7">
+        <f t="shared" si="14"/>
+        <v>1.0052430886558625</v>
+      </c>
+      <c r="S25" s="7">
+        <f t="shared" si="15"/>
+        <v>1.0073355418835779</v>
+      </c>
+      <c r="T25" s="7">
+        <f t="shared" si="16"/>
+        <v>1.0156871926949191</v>
+      </c>
+      <c r="U25" s="7">
+        <f t="shared" si="17"/>
+        <v>1.018443804034582</v>
+      </c>
+      <c r="W25" s="7">
+        <f t="shared" si="18"/>
+        <v>1.0015860013422289</v>
+      </c>
+    </row>
+    <row r="26" spans="2:23">
       <c r="B26">
         <v>4</v>
       </c>
@@ -17773,19 +18171,41 @@
         <v>195.8</v>
       </c>
       <c r="L26" s="7">
-        <f t="shared" si="3"/>
-        <v>1.0831892676854993</v>
-      </c>
-      <c r="M26" s="7">
-        <f t="shared" si="4"/>
-        <v>1.00577112802299</v>
-      </c>
-      <c r="N26" s="7">
-        <f t="shared" si="5"/>
-        <v>0.98751245300013368</v>
-      </c>
-    </row>
-    <row r="27" spans="2:15">
+        <f t="shared" si="11"/>
+        <v>0.3960298770533251</v>
+      </c>
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
+      <c r="P26" s="7">
+        <f t="shared" si="12"/>
+        <v>1.0145433391506691</v>
+      </c>
+      <c r="Q26" s="7">
+        <f t="shared" si="13"/>
+        <v>1.0166189111747852</v>
+      </c>
+      <c r="R26" s="7">
+        <f t="shared" si="14"/>
+        <v>1.0172834867555891</v>
+      </c>
+      <c r="S26" s="7">
+        <f t="shared" si="15"/>
+        <v>1.0226519337016575</v>
+      </c>
+      <c r="T26" s="7">
+        <f t="shared" si="16"/>
+        <v>1.031586503948313</v>
+      </c>
+      <c r="U26" s="7">
+        <f t="shared" si="17"/>
+        <v>1.0260262008733625</v>
+      </c>
+      <c r="W26" s="7">
+        <f t="shared" si="18"/>
+        <v>1.0042677840267491</v>
+      </c>
+    </row>
+    <row r="27" spans="2:23">
       <c r="B27">
         <v>5</v>
       </c>
@@ -17817,19 +18237,41 @@
         <v>295.60000000000002</v>
       </c>
       <c r="L27" s="7">
-        <f t="shared" si="3"/>
-        <v>1.063596293964199</v>
-      </c>
-      <c r="M27" s="7">
-        <f t="shared" si="4"/>
-        <v>0.99013164936867559</v>
-      </c>
-      <c r="N27" s="7">
-        <f t="shared" si="5"/>
-        <v>0.96965010325360146</v>
-      </c>
-    </row>
-    <row r="28" spans="2:15">
+        <f t="shared" si="11"/>
+        <v>0.59788780212953474</v>
+      </c>
+      <c r="M27" s="7"/>
+      <c r="N27" s="7"/>
+      <c r="P27" s="7">
+        <f t="shared" si="12"/>
+        <v>1.0119626168224298</v>
+      </c>
+      <c r="Q27" s="7">
+        <f t="shared" si="13"/>
+        <v>1.0141416625676341</v>
+      </c>
+      <c r="R27" s="7">
+        <f t="shared" si="14"/>
+        <v>1.0133511348464623</v>
+      </c>
+      <c r="S27" s="7">
+        <f t="shared" si="15"/>
+        <v>1.0157819225251075</v>
+      </c>
+      <c r="T27" s="7">
+        <f t="shared" si="16"/>
+        <v>1.019167450611477</v>
+      </c>
+      <c r="U27" s="7">
+        <f t="shared" si="17"/>
+        <v>1.0220122162037573</v>
+      </c>
+      <c r="W27" s="7">
+        <f t="shared" si="18"/>
+        <v>0.99994889194599312</v>
+      </c>
+    </row>
+    <row r="28" spans="2:23">
       <c r="B28">
         <v>6</v>
       </c>
@@ -17861,22 +18303,44 @@
         <v>161.30000000000001</v>
       </c>
       <c r="L28" s="7">
-        <f t="shared" si="3"/>
-        <v>1.1075444167882587</v>
-      </c>
-      <c r="M28" s="7">
-        <f t="shared" si="4"/>
-        <v>1.0371577185809977</v>
-      </c>
-      <c r="N28" s="7">
-        <f t="shared" si="5"/>
-        <v>1.0097163408627237</v>
-      </c>
+        <f t="shared" si="11"/>
+        <v>0.32624933181154919</v>
+      </c>
+      <c r="M28" s="7"/>
+      <c r="N28" s="7"/>
       <c r="O28" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="29" spans="2:15">
+      <c r="P28" s="7">
+        <f t="shared" si="12"/>
+        <v>1.0076335877862594</v>
+      </c>
+      <c r="Q28" s="7">
+        <f t="shared" si="13"/>
+        <v>1.0394041326285439</v>
+      </c>
+      <c r="R28" s="7">
+        <f t="shared" si="14"/>
+        <v>1.0308771929824563</v>
+      </c>
+      <c r="S28" s="7">
+        <f t="shared" si="15"/>
+        <v>1.0228661987774506</v>
+      </c>
+      <c r="T28" s="7">
+        <f t="shared" si="16"/>
+        <v>1.0319735391400222</v>
+      </c>
+      <c r="U28" s="7">
+        <f t="shared" si="17"/>
+        <v>1.0341953408848046</v>
+      </c>
+      <c r="W28" s="7">
+        <f t="shared" si="18"/>
+        <v>1.0145751558629035</v>
+      </c>
+    </row>
+    <row r="29" spans="2:23">
       <c r="B29">
         <v>7</v>
       </c>
@@ -17908,19 +18372,41 @@
         <v>696.5</v>
       </c>
       <c r="L29" s="7">
-        <f t="shared" si="3"/>
-        <v>1.0905603507329771</v>
-      </c>
-      <c r="M29" s="7">
-        <f t="shared" si="4"/>
-        <v>1.0127146298620673</v>
-      </c>
-      <c r="N29" s="7">
-        <f t="shared" si="5"/>
-        <v>0.99423245708310981</v>
-      </c>
-    </row>
-    <row r="30" spans="2:15">
+        <f t="shared" si="11"/>
+        <v>1.4087579640839678</v>
+      </c>
+      <c r="M29" s="7"/>
+      <c r="N29" s="7"/>
+      <c r="P29" s="7">
+        <f t="shared" si="12"/>
+        <v>1.018861644291579</v>
+      </c>
+      <c r="Q29" s="7">
+        <f t="shared" si="13"/>
+        <v>1.0216480826760945</v>
+      </c>
+      <c r="R29" s="7">
+        <f t="shared" si="14"/>
+        <v>1.0272423132069459</v>
+      </c>
+      <c r="S29" s="7">
+        <f t="shared" si="15"/>
+        <v>1.026552795031056</v>
+      </c>
+      <c r="T29" s="7">
+        <f t="shared" si="16"/>
+        <v>1.0254523461519076</v>
+      </c>
+      <c r="U29" s="7">
+        <f t="shared" si="17"/>
+        <v>1.0263778367226644</v>
+      </c>
+      <c r="W29" s="7">
+        <f t="shared" si="18"/>
+        <v>1.0036594509821759</v>
+      </c>
+    </row>
+    <row r="30" spans="2:23">
       <c r="B30">
         <v>8</v>
       </c>
@@ -17952,19 +18438,41 @@
         <v>585.20000000000005</v>
       </c>
       <c r="L30" s="7">
-        <f t="shared" si="3"/>
-        <v>1.0617558342594062</v>
-      </c>
-      <c r="M30" s="7">
-        <f t="shared" si="4"/>
-        <v>0.98877510027927329</v>
-      </c>
-      <c r="N30" s="7">
-        <f t="shared" si="5"/>
-        <v>0.96797220915702198</v>
-      </c>
-    </row>
-    <row r="31" spans="2:15">
+        <f t="shared" si="11"/>
+        <v>1.1836398572604998</v>
+      </c>
+      <c r="M30" s="7"/>
+      <c r="N30" s="7"/>
+      <c r="P30" s="7">
+        <f t="shared" si="12"/>
+        <v>1.0144508670520231</v>
+      </c>
+      <c r="Q30" s="7">
+        <f t="shared" si="13"/>
+        <v>1.0153645994671952</v>
+      </c>
+      <c r="R30" s="7">
+        <f t="shared" si="14"/>
+        <v>1.0115511551155116</v>
+      </c>
+      <c r="S30" s="7">
+        <f t="shared" si="15"/>
+        <v>1.0153039705970959</v>
+      </c>
+      <c r="T30" s="7">
+        <f t="shared" si="16"/>
+        <v>1.0190961926224646</v>
+      </c>
+      <c r="U30" s="7">
+        <f t="shared" si="17"/>
+        <v>1.0208757341396755</v>
+      </c>
+      <c r="W30" s="7">
+        <f t="shared" si="18"/>
+        <v>0.99924615440957654</v>
+      </c>
+    </row>
+    <row r="31" spans="2:23">
       <c r="B31">
         <v>9</v>
       </c>
@@ -17996,22 +18504,44 @@
         <v>201.6</v>
       </c>
       <c r="L31" s="7">
-        <f t="shared" si="3"/>
-        <v>1.1685263005361541</v>
-      </c>
-      <c r="M31" s="7">
-        <f t="shared" si="4"/>
-        <v>1.0805091110380687</v>
-      </c>
-      <c r="N31" s="7">
-        <f t="shared" si="5"/>
-        <v>1.0653117676316106</v>
-      </c>
+        <f t="shared" si="11"/>
+        <v>0.40776109915194242</v>
+      </c>
+      <c r="M31" s="7"/>
+      <c r="N31" s="7"/>
       <c r="O31" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="32" spans="2:15">
+      <c r="P31" s="7">
+        <f t="shared" si="12"/>
+        <v>1.0099767981438514</v>
+      </c>
+      <c r="Q31" s="7">
+        <f t="shared" si="13"/>
+        <v>1.1500533617929563</v>
+      </c>
+      <c r="R31" s="7">
+        <f t="shared" si="14"/>
+        <v>1.0805911330049263</v>
+      </c>
+      <c r="S31" s="7">
+        <f t="shared" si="15"/>
+        <v>1.0300779126653379</v>
+      </c>
+      <c r="T31" s="7">
+        <f t="shared" si="16"/>
+        <v>1.0336267605633802</v>
+      </c>
+      <c r="U31" s="7">
+        <f t="shared" si="17"/>
+        <v>1.0306748466257669</v>
+      </c>
+      <c r="W31" s="7">
+        <f t="shared" si="18"/>
+        <v>1.0062552335738546</v>
+      </c>
+    </row>
+    <row r="32" spans="2:23">
       <c r="B32">
         <v>10</v>
       </c>
@@ -18043,19 +18573,41 @@
         <v>99.3</v>
       </c>
       <c r="L32" s="7">
-        <f t="shared" si="3"/>
-        <v>1.0803753569971439</v>
-      </c>
-      <c r="M32" s="7">
-        <f t="shared" si="4"/>
-        <v>1.0114186858934013</v>
-      </c>
-      <c r="N32" s="7">
-        <f t="shared" si="5"/>
-        <v>0.98494709168306793</v>
-      </c>
-    </row>
-    <row r="33" spans="2:17">
+        <f t="shared" si="11"/>
+        <v>0.20084661282632879</v>
+      </c>
+      <c r="M32" s="7"/>
+      <c r="N32" s="7"/>
+      <c r="P32" s="7">
+        <f t="shared" si="12"/>
+        <v>1.0086890819795995</v>
+      </c>
+      <c r="Q32" s="7">
+        <f t="shared" si="13"/>
+        <v>1.0134529147982063</v>
+      </c>
+      <c r="R32" s="7">
+        <f t="shared" si="14"/>
+        <v>1.0118212042851864</v>
+      </c>
+      <c r="S32" s="7">
+        <f t="shared" si="15"/>
+        <v>1.0185387131952017</v>
+      </c>
+      <c r="T32" s="7">
+        <f t="shared" si="16"/>
+        <v>1.0274118903524387</v>
+      </c>
+      <c r="U32" s="7">
+        <f t="shared" si="17"/>
+        <v>1.0311526479750777</v>
+      </c>
+      <c r="W32" s="7">
+        <f t="shared" si="18"/>
+        <v>1.0112967545348575</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23">
       <c r="B33">
         <v>11</v>
       </c>
@@ -18087,22 +18639,44 @@
         <v>56.2</v>
       </c>
       <c r="L33" s="7">
-        <f t="shared" si="3"/>
-        <v>1.252367688022284</v>
-      </c>
-      <c r="M33" s="7">
-        <f t="shared" si="4"/>
-        <v>1.2051289517068422</v>
-      </c>
-      <c r="N33" s="7">
-        <f t="shared" si="5"/>
-        <v>1.1417475454678085</v>
-      </c>
+        <f t="shared" si="11"/>
+        <v>0.11367149688660301</v>
+      </c>
+      <c r="M33" s="7"/>
+      <c r="N33" s="7"/>
       <c r="O33" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="34" spans="2:17">
+      <c r="P33" s="7">
+        <f t="shared" si="12"/>
+        <v>1.5078206465067778</v>
+      </c>
+      <c r="Q33" s="7">
+        <f t="shared" si="13"/>
+        <v>1.0103734439834022</v>
+      </c>
+      <c r="R33" s="7">
+        <f t="shared" si="14"/>
+        <v>1.0397842211732973</v>
+      </c>
+      <c r="S33" s="7">
+        <f t="shared" si="15"/>
+        <v>1.0346858638743455</v>
+      </c>
+      <c r="T33" s="7">
+        <f t="shared" si="16"/>
+        <v>1.0259165613147916</v>
+      </c>
+      <c r="U33" s="7">
+        <f t="shared" si="17"/>
+        <v>1.0343558282208589</v>
+      </c>
+      <c r="W33" s="7">
+        <f t="shared" si="18"/>
+        <v>1.0152964940332911</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23">
       <c r="B34">
         <v>12</v>
       </c>
@@ -18134,22 +18708,44 @@
         <v>321.8</v>
       </c>
       <c r="L34" s="7">
-        <f>K34/AVERAGE(D34:K34)</f>
-        <v>1.0933956253981738</v>
-      </c>
-      <c r="M34" s="7">
-        <f t="shared" si="4"/>
-        <v>1.0221391549814363</v>
-      </c>
-      <c r="N34" s="7">
-        <f t="shared" si="5"/>
-        <v>0.99681729532245111</v>
-      </c>
+        <f t="shared" si="11"/>
+        <v>0.65088056402328909</v>
+      </c>
+      <c r="M34" s="7"/>
+      <c r="N34" s="7"/>
       <c r="O34" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="35" spans="2:17">
+      <c r="P34" s="7">
+        <f t="shared" si="12"/>
+        <v>1.0174474187380498</v>
+      </c>
+      <c r="Q34" s="7">
+        <f t="shared" si="13"/>
+        <v>1.0179767359887206</v>
+      </c>
+      <c r="R34" s="7">
+        <f t="shared" si="14"/>
+        <v>1.0166262556286803</v>
+      </c>
+      <c r="S34" s="7">
+        <f t="shared" si="15"/>
+        <v>1.0180394826412527</v>
+      </c>
+      <c r="T34" s="7">
+        <f t="shared" si="16"/>
+        <v>1.0401278800573255</v>
+      </c>
+      <c r="U34" s="7">
+        <f t="shared" si="17"/>
+        <v>1.0320718409236691</v>
+      </c>
+      <c r="W34" s="7">
+        <f t="shared" si="18"/>
+        <v>1.0108705128607045</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23">
       <c r="B35">
         <v>13</v>
       </c>
@@ -18181,19 +18777,41 @@
         <v>153.1</v>
       </c>
       <c r="L35" s="7">
-        <f t="shared" si="3"/>
-        <v>1.0562262849258366</v>
-      </c>
-      <c r="M35" s="7">
-        <f t="shared" si="4"/>
-        <v>0.99604081117126197</v>
-      </c>
-      <c r="N35" s="7">
-        <f t="shared" si="5"/>
-        <v>0.96293107831379798</v>
-      </c>
-    </row>
-    <row r="36" spans="2:17">
+        <f t="shared" si="11"/>
+        <v>0.30966381091350392</v>
+      </c>
+      <c r="M35" s="7"/>
+      <c r="N35" s="7"/>
+      <c r="P35" s="7">
+        <f t="shared" si="12"/>
+        <v>1.0092592592592591</v>
+      </c>
+      <c r="Q35" s="7">
+        <f t="shared" si="13"/>
+        <v>1.0129229323308271</v>
+      </c>
+      <c r="R35" s="7">
+        <f t="shared" si="14"/>
+        <v>1.0106877323420074</v>
+      </c>
+      <c r="S35" s="7">
+        <f t="shared" si="15"/>
+        <v>1.0107946715663758</v>
+      </c>
+      <c r="T35" s="7">
+        <f t="shared" si="16"/>
+        <v>1.0183423913043477</v>
+      </c>
+      <c r="U35" s="7">
+        <f t="shared" si="17"/>
+        <v>1.0213475650433621</v>
+      </c>
+      <c r="W35" s="7">
+        <f t="shared" si="18"/>
+        <v>1.0027692344104326</v>
+      </c>
+    </row>
+    <row r="36" spans="2:23">
       <c r="B36">
         <v>14</v>
       </c>
@@ -18225,34 +18843,51 @@
         <v>3040.8</v>
       </c>
       <c r="L36" s="7">
-        <f t="shared" si="3"/>
-        <v>1.1302618618395377</v>
-      </c>
-      <c r="M36" s="7">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="N36" s="7">
-        <f t="shared" si="5"/>
-        <v>1.0304271811172803</v>
-      </c>
+        <f t="shared" si="11"/>
+        <v>6.1503965788751325</v>
+      </c>
+      <c r="M36" s="7"/>
+      <c r="N36" s="7"/>
       <c r="O36" t="s">
         <v>111</v>
       </c>
-      <c r="Q36" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="37" spans="2:17">
-      <c r="L37" s="7">
-        <f>AVERAGE(L23:L36)</f>
-        <v>1.0968866918029161</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="38" spans="2:17">
+      <c r="P36" s="7">
+        <f t="shared" si="12"/>
+        <v>1.0176783035316062</v>
+      </c>
+      <c r="Q36" s="7">
+        <f t="shared" si="13"/>
+        <v>1.0223414828065991</v>
+      </c>
+      <c r="R36" s="7">
+        <f t="shared" si="14"/>
+        <v>1.0395061728395063</v>
+      </c>
+      <c r="S36" s="7">
+        <f t="shared" si="15"/>
+        <v>1.0560005906456496</v>
+      </c>
+      <c r="T36" s="7">
+        <f t="shared" si="16"/>
+        <v>1.042037737622483</v>
+      </c>
+      <c r="U36" s="7">
+        <f t="shared" si="17"/>
+        <v>1.0298719772403984</v>
+      </c>
+      <c r="W36" s="7">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23">
+      <c r="K37" s="15">
+        <f>AVERAGE(K23:K36)</f>
+        <v>494.40714285714284</v>
+      </c>
+      <c r="L37" s="7"/>
+    </row>
+    <row r="38" spans="2:23">
       <c r="C38" s="7" t="s">
         <v>28</v>
       </c>
@@ -18261,371 +18896,377 @@
         <v>0.16913342503438789</v>
       </c>
       <c r="E38" s="7">
-        <f t="shared" ref="E38:K38" si="6">E23/E4</f>
+        <f t="shared" ref="E38:K38" si="19">E23/E4</f>
         <v>0.16875644574716386</v>
       </c>
       <c r="F38" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="19"/>
         <v>0.1684137340892074</v>
       </c>
       <c r="G38" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="19"/>
         <v>0.16836116525312123</v>
       </c>
       <c r="H38" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="19"/>
         <v>0.168321463845714</v>
       </c>
       <c r="I38" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="19"/>
         <v>0.16884783166538364</v>
       </c>
       <c r="J38" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="19"/>
         <v>0.16931484667543772</v>
       </c>
       <c r="K38" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="19"/>
         <v>0.16937134867928297</v>
       </c>
-      <c r="Q38" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="39" spans="2:17">
+    </row>
+    <row r="39" spans="2:23">
       <c r="C39" s="7" t="s">
         <v>29</v>
       </c>
       <c r="D39" s="7">
-        <f t="shared" ref="D39:K39" si="7">D24/D5</f>
+        <f t="shared" ref="D39:K39" si="20">D24/D5</f>
         <v>0.14241350210970463</v>
       </c>
       <c r="E39" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v>0.14194640900488098</v>
       </c>
       <c r="F39" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v>0.14147836577651698</v>
       </c>
       <c r="G39" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v>0.14122198420564633</v>
       </c>
       <c r="H39" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v>0.14114990119506918</v>
       </c>
       <c r="I39" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v>0.1409251575226679</v>
       </c>
       <c r="J39" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v>0.14087940530291632</v>
       </c>
       <c r="K39" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v>0.14164506245580957</v>
       </c>
     </row>
-    <row r="40" spans="2:17">
+    <row r="40" spans="2:23">
       <c r="C40" s="7" t="s">
         <v>30</v>
       </c>
       <c r="D40" s="7">
-        <f t="shared" ref="D40:K40" si="8">D25/D6</f>
+        <f t="shared" ref="D40:K40" si="21">D25/D6</f>
         <v>0.14971521562245729</v>
       </c>
       <c r="E40" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="21"/>
         <v>0.14779168003422091</v>
       </c>
       <c r="F40" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="21"/>
         <v>0.14661177960734642</v>
       </c>
       <c r="G40" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="21"/>
         <v>0.14564166536722281</v>
       </c>
       <c r="H40" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="21"/>
         <v>0.14441990652765652</v>
       </c>
       <c r="I40" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="21"/>
         <v>0.14356535815459329</v>
       </c>
       <c r="J40" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="21"/>
         <v>0.14390207493655768</v>
       </c>
       <c r="K40" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="21"/>
         <v>0.1440802348336595</v>
       </c>
-    </row>
-    <row r="41" spans="2:17">
+      <c r="Q40" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="41" spans="2:23">
       <c r="C41" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D41" s="7">
-        <f t="shared" ref="D41:K41" si="9">D26/D7</f>
+        <f t="shared" ref="D41:K41" si="22">D26/D7</f>
         <v>0.13036126056879324</v>
       </c>
       <c r="E41" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>0.12958490566037734</v>
       </c>
       <c r="F41" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>0.12895593019816623</v>
       </c>
       <c r="G41" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>0.12835540120107083</v>
       </c>
       <c r="H41" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>0.12796880538816022</v>
       </c>
       <c r="I41" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>0.12823888042122764</v>
       </c>
       <c r="J41" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>0.1298542866824805</v>
       </c>
       <c r="K41" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>0.12989253018442351</v>
       </c>
-    </row>
-    <row r="42" spans="2:17">
+      <c r="Q41" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23">
       <c r="C42" s="7" t="s">
         <v>32</v>
       </c>
       <c r="D42" s="7">
-        <f t="shared" ref="D42:K42" si="10">D27/D8</f>
+        <f t="shared" ref="D42:K42" si="23">D27/D8</f>
         <v>8.5534835534835527E-2</v>
       </c>
       <c r="E42" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="23"/>
         <v>8.4995553296912718E-2</v>
       </c>
       <c r="F42" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="23"/>
         <v>8.4248856244748066E-2</v>
       </c>
       <c r="G42" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="23"/>
         <v>8.3800756005365185E-2</v>
       </c>
       <c r="H42" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="23"/>
         <v>8.3438268273670332E-2</v>
       </c>
       <c r="I42" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="23"/>
         <v>8.3091277176304892E-2</v>
       </c>
       <c r="J42" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="23"/>
         <v>8.2962409901501874E-2</v>
       </c>
       <c r="K42" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="23"/>
         <v>8.3019715778239633E-2</v>
       </c>
-    </row>
-    <row r="43" spans="2:17">
+      <c r="Q42" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23">
       <c r="C43" s="7" t="s">
         <v>33</v>
       </c>
       <c r="D43" s="7">
-        <f t="shared" ref="D43:K43" si="11">D28/D9</f>
+        <f t="shared" ref="D43:K43" si="24">D28/D9</f>
         <v>0.14223589308442935</v>
       </c>
       <c r="E43" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="24"/>
         <v>0.14154488517745303</v>
       </c>
       <c r="F43" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="24"/>
         <v>0.13925472179683512</v>
       </c>
       <c r="G43" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="24"/>
         <v>0.14461939624912243</v>
       </c>
       <c r="H43" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="24"/>
         <v>0.14492896606156275</v>
       </c>
       <c r="I43" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="24"/>
         <v>0.14566205629171097</v>
       </c>
       <c r="J43" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="24"/>
         <v>0.14779725248697301</v>
       </c>
       <c r="K43" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="24"/>
         <v>0.15000464986515394</v>
       </c>
     </row>
-    <row r="44" spans="2:17">
+    <row r="44" spans="2:23">
       <c r="C44" s="7" t="s">
         <v>34</v>
       </c>
       <c r="D44" s="7">
-        <f t="shared" ref="D44:K44" si="12">D29/D10</f>
+        <f t="shared" ref="D44:K44" si="25">D29/D10</f>
         <v>0.222515457698688</v>
       </c>
       <c r="E44" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="25"/>
         <v>0.22232923396058679</v>
       </c>
       <c r="F44" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="25"/>
         <v>0.22238366813178831</v>
       </c>
       <c r="G44" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="25"/>
         <v>0.22274797210758501</v>
       </c>
       <c r="H44" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="25"/>
         <v>0.22486486486486484</v>
       </c>
       <c r="I44" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="25"/>
         <v>0.22554672307324897</v>
       </c>
       <c r="J44" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="25"/>
         <v>0.22625521267723103</v>
       </c>
       <c r="K44" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="25"/>
         <v>0.22716154071948078</v>
       </c>
     </row>
-    <row r="45" spans="2:17">
+    <row r="45" spans="2:23">
       <c r="C45" s="7" t="s">
         <v>35</v>
       </c>
       <c r="D45" s="7">
-        <f t="shared" ref="D45:K45" si="13">D30/D11</f>
+        <f t="shared" ref="D45:K45" si="26">D30/D11</f>
         <v>0.14344004162444887</v>
       </c>
       <c r="E45" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="26"/>
         <v>0.14236176446869708</v>
       </c>
       <c r="F45" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="26"/>
         <v>0.14167258943378347</v>
       </c>
       <c r="G45" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="26"/>
         <v>0.1408933821633053</v>
       </c>
       <c r="H45" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="26"/>
         <v>0.13975226081009198</v>
       </c>
       <c r="I45" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="26"/>
         <v>0.13933470592612807</v>
       </c>
       <c r="J45" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="26"/>
         <v>0.13908989364285368</v>
       </c>
       <c r="K45" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="26"/>
         <v>0.13905191873589165</v>
       </c>
     </row>
-    <row r="46" spans="2:17">
+    <row r="46" spans="2:23">
       <c r="C46" s="7" t="s">
         <v>36</v>
       </c>
       <c r="D46" s="7">
-        <f t="shared" ref="D46:K46" si="14">D31/D12</f>
+        <f t="shared" ref="D46:K46" si="27">D31/D12</f>
         <v>5.7710270884944966E-2</v>
       </c>
       <c r="E46" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="27"/>
         <v>5.7195131652215424E-2</v>
       </c>
       <c r="F46" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="27"/>
         <v>5.6461340908206543E-2</v>
       </c>
       <c r="G46" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="27"/>
         <v>6.8312350233920349E-2</v>
       </c>
       <c r="H46" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="27"/>
         <v>6.8188600417785739E-2</v>
       </c>
       <c r="I46" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="27"/>
         <v>6.9079906678331873E-2</v>
       </c>
       <c r="J46" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="27"/>
         <v>6.9730981649741661E-2</v>
       </c>
       <c r="K46" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="27"/>
         <v>7.0070557158249627E-2</v>
       </c>
     </row>
-    <row r="47" spans="2:17">
+    <row r="47" spans="2:23">
       <c r="C47" s="7" t="s">
         <v>37</v>
       </c>
       <c r="D47" s="7">
-        <f t="shared" ref="D47:K47" si="15">D32/D13</f>
+        <f t="shared" ref="D47:K47" si="28">D32/D13</f>
         <v>0.10895280786950566</v>
       </c>
       <c r="E47" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="28"/>
         <v>0.10810148302488051</v>
       </c>
       <c r="F47" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="28"/>
         <v>0.10724183636582721</v>
       </c>
       <c r="G47" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="28"/>
         <v>0.10681791326952618</v>
       </c>
       <c r="H47" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="28"/>
         <v>0.10605180624927402</v>
       </c>
       <c r="I47" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="28"/>
         <v>0.10630548600045528</v>
       </c>
       <c r="J47" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="28"/>
         <v>0.10729422261878206</v>
       </c>
       <c r="K47" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="28"/>
         <v>0.10864332603938731</v>
       </c>
     </row>
-    <row r="48" spans="2:17">
+    <row r="48" spans="2:23">
       <c r="C48" s="7" t="s">
         <v>39</v>
       </c>
@@ -18634,31 +19275,31 @@
         <v>0</v>
       </c>
       <c r="E48" s="7">
-        <f t="shared" ref="E48:K48" si="16">E33/E14</f>
+        <f t="shared" ref="E48:K48" si="29">E33/E14</f>
         <v>1.6671326716063192E-2</v>
       </c>
       <c r="F48" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="29"/>
         <v>1.6629291012592723E-2</v>
       </c>
       <c r="G48" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="29"/>
         <v>1.655392773377749E-2</v>
       </c>
       <c r="H48" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="29"/>
         <v>1.7272085755569742E-2</v>
       </c>
       <c r="I48" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="29"/>
         <v>1.7916029236783954E-2</v>
       </c>
       <c r="J48" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="29"/>
         <v>1.8073094140442305E-2</v>
       </c>
       <c r="K48" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="29"/>
         <v>1.8415361426043646E-2</v>
       </c>
     </row>
@@ -18667,35 +19308,35 @@
         <v>100</v>
       </c>
       <c r="D49" s="7">
-        <f t="shared" ref="D49:K49" si="17">D34/D15</f>
+        <f t="shared" ref="D49:K49" si="30">D34/D15</f>
         <v>7.7002917414721719E-2</v>
       </c>
       <c r="E49" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="30"/>
         <v>7.6929451411524227E-2</v>
       </c>
       <c r="F49" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="30"/>
         <v>7.7050471044986829E-2</v>
       </c>
       <c r="G49" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="30"/>
         <v>7.697228144989339E-2</v>
       </c>
       <c r="H49" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="30"/>
         <v>7.683246073298429E-2</v>
       </c>
       <c r="I49" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="30"/>
         <v>7.6763165999384056E-2</v>
       </c>
       <c r="J49" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="30"/>
         <v>7.9093629756306114E-2</v>
       </c>
       <c r="K49" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="30"/>
         <v>7.9231810907300262E-2</v>
       </c>
     </row>
@@ -18704,35 +19345,35 @@
         <v>40</v>
       </c>
       <c r="D50" s="7">
-        <f t="shared" ref="D50:K50" si="18">D35/D16</f>
+        <f t="shared" ref="D50:K50" si="31">D35/D16</f>
         <v>7.8403782293015145E-2</v>
       </c>
       <c r="E50" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="31"/>
         <v>7.7673130193905815E-2</v>
       </c>
       <c r="F50" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="31"/>
         <v>7.7191262188810797E-2</v>
       </c>
       <c r="G50" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="31"/>
         <v>7.6989016876506819E-2</v>
       </c>
       <c r="H50" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="31"/>
         <v>7.6585855384777898E-2</v>
       </c>
       <c r="I50" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="31"/>
         <v>7.6239476145930768E-2</v>
       </c>
       <c r="J50" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="31"/>
         <v>7.6553802155150411E-2</v>
       </c>
       <c r="K50" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="31"/>
         <v>7.6718781318901585E-2</v>
       </c>
     </row>
